--- a/mistral_translate_work/split_by_prompt/excel/skill_description/lang_multi_text/lang_multi_text__skill_description__part_0030.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/skill_description/lang_multi_text/lang_multi_text__skill_description__part_0030.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;Shotgun Mô-đun&lt;/color&gt; được nâng cấp: số lượng đạn giờ đây tăng lên &lt;color=Highlight&gt;{0}&lt;/color&gt;, nhưng sát thương mỗi viên đạn giảm &lt;color=Highlight&gt;{1}&lt;/color&gt;.</t>
+          <t>&lt;color=Highlight&gt;Shotgun Module&lt;/color&gt; được nâng cấp: số lượng đạn giờ đây tăng lên &lt;color=Highlight&gt;{0}&lt;/color&gt;, nhưng sát thương mỗi viên đạn giảm &lt;color=Highlight&gt;{1}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -639,7 +639,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;Orbital Strike Protocol&lt;/color&gt; được nâng cấp: &lt;color=Highlight&gt;Hỗ Trợ Droid's number cannot be further increased&lt;/color&gt;. &lt;color=Highlight&gt;For every Hỗ Trợ Droid currently deployed&lt;/color&gt; sẽ tăng Tấn Công thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;.</t>
+          <t>&lt;color=Highlight&gt;Giao Thức ATK Quỹ Đạo&lt;/color&gt; được nâng cấp: &lt;color=Highlight&gt;Không thể triển khai thêm Droid Hỗ Trợ&lt;/color&gt;. &lt;color=Highlight&gt;Mỗi Droid Hỗ Trợ đang triển khai&lt;/color&gt; sẽ tăng ATK thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;Sustained Combustion Protocol&lt;/color&gt; được nâng cấp: Cooldown chiêu giảm tối đa &lt;color=Highlight&gt;{0}&lt;/color&gt;.</t>
+          <t>&lt;color=Highlight&gt;Giao Thức Đốt Cháy Liên Tục&lt;/color&gt; được nâng cấp: Thời gian hồi chiêu giảm tối đa &lt;color=Highlight&gt;{0}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -769,7 +769,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;Guided Missile Protocol&lt;/color&gt; được nâng cấp: Sát thương của Hỗ Trợ Droid tăng thêm &lt;color=Highlight&gt;{1}&lt;/color&gt;, và Cooldown chiêu tăng thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;.</t>
+          <t>&lt;color=Highlight&gt;Giao Thức Tên Lửa Điều Khiển&lt;/color&gt; được nâng cấp: DMG của Droid Hỗ Trợ tăng thêm &lt;color=Highlight&gt;{1}&lt;/color&gt;, và Thời gian hồi chiêu tăng thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;Zap Mô-đun&lt;/color&gt; đã được nâng cấp: giờ đây nó tăng &lt;color=Highlight&gt;{0}&lt;/color&gt; Tấn Công, và cứ mỗi &lt;color=Highlight&gt;{1}&lt;/color&gt; giây, nó sẽ bắn thêm một tia laser, gây &lt;color=Highlight&gt;{2}&lt;/color&gt; Sát Thương.</t>
+          <t>&lt;color=Highlight&gt;Mô-đun Tia Điện&lt;/color&gt; đã được nâng cấp: giờ đây nó tăng &lt;color=Highlight&gt;{0}&lt;/color&gt; ATK, và cứ mỗi &lt;color=Highlight&gt;{1}&lt;/color&gt; giây, nó sẽ bắn thêm một tia laser, gây &lt;color=Highlight&gt;{2}&lt;/color&gt; Sát Thương.</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;Repeater Mô-đun&lt;/color&gt; được nâng cấp: Equip thêm &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; &lt;color=Highlight&gt;{Cus:Sap,S=Repeater Mô-đun P=Repeater Modules SapTag=0}&lt;/color&gt;. &lt;color=Highlight&gt;Repeater Mô-đun&lt;/color&gt; giờ đây tăng &lt;color=Highlight&gt;{1}&lt;/color&gt; Tốc Độ Tấn Công, nhưng Hệ Số Sát Thương của đạn giảm &lt;color=Highlight&gt;{2}&lt;/color&gt;.</t>
+          <t>&lt;color=Highlight&gt;Mô-đun Lặp Lại&lt;/color&gt; được nâng cấp: Trang bị thêm &lt;SapTag=0&gt;{0}&lt;/SapTag&gt; &lt;color=Highlight&gt;{Cus:Sap,S=Mô-đun Lặp Lại P=Mô-đun Lặp Lại SapTag=0}&lt;/color&gt;. &lt;color=Highlight&gt;Mô-đun Lặp Lại&lt;/color&gt; giờ đây tăng &lt;color=Highlight&gt;{1}&lt;/color&gt; Tốc Độ ATK, nhưng Hệ Số Sát Thương của đạn giảm &lt;color=Highlight&gt;{2}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;Shotgun Mô-đun&lt;/color&gt; được nâng cấp: số lượng đạn giờ đây tăng lên &lt;color=Highlight&gt;{0}&lt;/color&gt;, nhưng sát thương mỗi viên đạn giảm &lt;color=Highlight&gt;{1}&lt;/color&gt;.</t>
+          <t>&lt;color=Highlight&gt;Shotgun Module&lt;/color&gt; được nâng cấp: số lượng đạn giờ đây tăng lên &lt;color=Highlight&gt;{0}&lt;/color&gt;, nhưng sát thương mỗi viên đạn giảm &lt;color=Highlight&gt;{1}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;Orbital Strike Protocol&lt;/color&gt; được nâng cấp: &lt;color=Highlight&gt;Hỗ Trợ Droid's number cannot be further increased&lt;/color&gt;. &lt;color=Highlight&gt;For every Hỗ Trợ Droid currently deployed&lt;/color&gt; sẽ tăng Tấn Công thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;.</t>
+          <t>&lt;color=Highlight&gt;Giao Thức ATK Quỹ Đạo&lt;/color&gt; được nâng cấp: &lt;color=Highlight&gt;Không thể triển khai thêm Droid Hỗ Trợ&lt;/color&gt;. &lt;color=Highlight&gt;Mỗi Droid Hỗ Trợ đang triển khai&lt;/color&gt; sẽ tăng ATK thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;Sustained Combustion Protocol&lt;/color&gt; được nâng cấp: Cooldown chiêu giảm tối đa &lt;color=Highlight&gt;{0}&lt;/color&gt;.</t>
+          <t>&lt;color=Highlight&gt;Giao Thức Đốt Cháy Liên Tục&lt;/color&gt; được nâng cấp: Thời gian hồi chiêu giảm tối đa &lt;color=Highlight&gt;{0}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>&lt;color=Highlight&gt;Guided Missile Protocol&lt;/color&gt; được nâng cấp: Sát thương của Hỗ Trợ Droid tăng thêm &lt;color=Highlight&gt;{1}&lt;/color&gt;, và Cooldown chiêu tăng thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;.</t>
+          <t>&lt;color=Highlight&gt;Giao Thức Tên Lửa Điều Khiển&lt;/color&gt; được nâng cấp: DMG của Droid Hỗ Trợ tăng thêm &lt;color=Highlight&gt;{1}&lt;/color&gt;, và Thời gian hồi chiêu tăng thêm &lt;color=Highlight&gt;{0}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Vũ Khí Main nhận hiệu ứng ngẫu nhiên sau: Tăng &lt;color=Highlight&gt;{0}&lt;/color&gt; Tấn Công, nhưng Tốc Độ Tấn Công giảm &lt;color=Highlight&gt;{1}&lt;/color&gt;.</t>
+          <t>Vũ Khí Chính nhận hiệu ứng ngẫu nhiên sau: Tăng &lt;color=Highlight&gt;{0}&lt;/color&gt; ATK, nhưng Tốc Độ ATK giảm &lt;color=Highlight&gt;{1}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Vũ Khí Main nhận hiệu ứng ngẫu nhiên sau: Tăng &lt;color=Highlight&gt;{0}&lt;/color&gt; Tốc Độ Tấn Công, nhưng Tấn Công giảm &lt;color=Highlight&gt;{1}&lt;/color&gt;.</t>
+          <t>Vũ Khí Chính nhận hiệu ứng ngẫu nhiên sau: Tăng &lt;color=Highlight&gt;{0}&lt;/color&gt; Tốc Độ ATK, nhưng ATK giảm &lt;color=Highlight&gt;{1}&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -1354,7 +1354,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Nhận Vũ Khí Main của &lt;color=Highlight&gt;Mourning Aix Projection&lt;/color&gt;, định kỳ phóng các tia sét về phía trước. Nhận lại Vật Phẩm Hỗ Trợ này sẽ nâng cấp mô-đun, tăng số lượng tia sét phóng ra. Mô-đun này không bị ảnh hưởng bởi Tốc Độ Tấn Công.</t>
+          <t>Nhận Vũ Khí Chính của &lt;color=Highlight&gt;Mourning Aix Projection&lt;/color&gt;, định kỳ phóng các tia sét về phía trước. Nhận lại Vật Phẩm Hỗ Trợ này sẽ nâng cấp mô-đun, tăng số lượng tia sét phóng ra. Mô-đun này không bị ảnh hưởng bởi Tốc Độ ATK.</t>
         </is>
       </c>
     </row>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Nhận được Vũ Khí Main của &lt;color=Highlight&gt;Lampylumen Myriad Projection&lt;/color&gt;, định kỳ bắn ra các mũi nhọn băng về phía trước. Nhận lại vật phẩm hỗ trợ này sẽ nâng cấp mô-đun, tăng số lượng mũi nhọn băng bắn ra. Mô-đun này không bị ảnh hưởng bởi Tốc Độ Tấn Công.</t>
+          <t>Nhận được Vũ Khí Chính của &lt;color=Highlight&gt;Lampylumen Myriad Projection&lt;/color&gt;, định kỳ bắn ra các mũi nhọn băng về phía trước. Nhận lại vật phẩm hỗ trợ này sẽ nâng cấp mô-đun, tăng số lượng mũi nhọn băng bắn ra. Mô-đun này không bị ảnh hưởng bởi Tốc Độ ATK.</t>
         </is>
       </c>
     </row>
@@ -1484,7 +1484,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Nhận Vũ Khí Main của &lt;color=Highlight&gt;Sentry Construct Projection&lt;/color&gt;, định kỳ bắn đạn về phía trước. Nhận lại Vật Phẩm Hỗ Trợ này sẽ nâng cấp mô-đun, tăng số lượng đạn bắn ra. Mô-đun này không bị ảnh hưởng bởi Tốc Độ Tấn Công.</t>
+          <t>Nhận Vũ Khí Chính của &lt;color=Highlight&gt;Sentry Construct Projection&lt;/color&gt;, định kỳ bắn đạn về phía trước. Nhận lại Vật Phẩm Hỗ Trợ này sẽ nâng cấp mô-đun, tăng số lượng đạn bắn ra. Mô-đun này không bị ảnh hưởng bởi Tốc Độ ATK.</t>
         </is>
       </c>
     </row>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Tấn Công +{0}</t>
+          <t>ATK +{0}</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>ATK SPD +{0}</t>
+          <t>Tốc Độ ATK +{0}</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Crit. Rate Bonus +{0}</t>
+          <t>Thêm Crit. Rate +{0}</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Tấn Công +{0}</t>
+          <t>ATK +{0}</t>
         </is>
       </c>
     </row>
@@ -1939,7 +1939,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Cooldown -{0}</t>
+          <t>Thời gian hồi -{0}</t>
         </is>
       </c>
     </row>
@@ -2004,7 +2004,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Crit. Rate Bonus +{0}</t>
+          <t>Thêm Crit. Rate +{0}</t>
         </is>
       </c>
     </row>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Phục hồi HP</t>
+          <t>Hồi Phục HP</t>
         </is>
       </c>
     </row>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Main Weapon ATK +{0}</t>
+          <t>ATK Vũ Khí Chính +{0}</t>
         </is>
       </c>
     </row>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Main Weapon ATK SPD +{0}</t>
+          <t>Tốc Độ ATK Vũ Khí Chính +{0}</t>
         </is>
       </c>
     </row>
@@ -2459,7 +2459,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Main Weapon Crit. DMG +{0}</t>
+          <t>Crit. DMG vũ khí chính +{0}</t>
         </is>
       </c>
     </row>
@@ -2524,7 +2524,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Tấn Công của Hỗ Trợ Droid +{0}</t>
+          <t>ATK của Droid Hỗ Trợ +{0}</t>
         </is>
       </c>
     </row>
@@ -2589,7 +2589,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Thời Gian Cooldown của Hỗ Trợ Droid -{0}</t>
+          <t>Thời gian hồi Chiêu của Droid Hỗ Trợ -{0}</t>
         </is>
       </c>
     </row>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Rover Hỗ Trợ Tăng Crit. Rate +{0}</t>
+          <t>Vận Mệnh Giả Hỗ Trợ Tăng Crit. Rate +{0}</t>
         </is>
       </c>
     </row>
@@ -2719,7 +2719,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Rover Hỗ Trợ Tăng Crit. DMG +{0}</t>
+          <t>Vận Mệnh Giả Hỗ Trợ Tăng Crit. DMG +{0}</t>
         </is>
       </c>
     </row>
@@ -2784,7 +2784,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Tấn Công vũ khí chính tăng trong {0}s</t>
+          <t>ATK vũ khí chính tăng trong {0}s</t>
         </is>
       </c>
     </row>
@@ -2849,7 +2849,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Tốc Độ Tấn Công Vũ Khí Main tăng trong {0} giây</t>
+          <t>Tốc Độ ATK Vũ Khí Chính tăng trong {0} giây</t>
         </is>
       </c>
     </row>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Thời Gian Cooldown của Hỗ Trợ Droid giảm trong {0} giây.</t>
+          <t>Thời gian hồi Chiêu của Droid Hỗ Trợ giảm trong {0} giây.</t>
         </is>
       </c>
     </row>
@@ -3044,7 +3044,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>HP Tối Đa</t>
+          <t>Tối đa HP</t>
         </is>
       </c>
     </row>
@@ -3304,7 +3304,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>ATK Bonus</t>
+          <t>Tăng ATK</t>
         </is>
       </c>
     </row>
@@ -3369,7 +3369,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Crit. Rate Bonus</t>
+          <t>Thêm Crit. Rate</t>
         </is>
       </c>
     </row>
@@ -3434,7 +3434,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Tăng DMG Chung</t>
+          <t>Tăng Sát Thương Tổng Hợp</t>
         </is>
       </c>
     </row>
@@ -3499,7 +3499,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Giảm DMG Chung</t>
+          <t>Giảm Sát Thương Tổng Hợp</t>
         </is>
       </c>
     </row>
@@ -3564,7 +3564,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Giảm DMG Ramming</t>
+          <t>Giảm Sát Thương Đâm</t>
         </is>
       </c>
     </row>
@@ -3629,7 +3629,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>SPD TẤN CÔNG</t>
+          <t>Tốc Độ ATK</t>
         </is>
       </c>
     </row>
@@ -3694,7 +3694,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>ATK SPD Bonus</t>
+          <t>Tăng Tốc Độ ATK</t>
         </is>
       </c>
     </row>
@@ -3759,7 +3759,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Cooldown chiêu</t>
+          <t>Thời gian hồi</t>
         </is>
       </c>
     </row>
@@ -3889,7 +3889,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Sát thương gây ra lên kẻ địch với mỗi đòn tấn công. Weapon Main và Hỗ Trợ Droid gây sát thương dựa trên 100% Tấn Công theo mặc định.</t>
+          <t>Sát thương gây ra lên kẻ địch với mỗi đòn tấn công. Vũ khí Chính và Droid Hỗ Trợ gây sát thương dựa trên 100% ATK theo mặc định.</t>
         </is>
       </c>
     </row>
@@ -4019,7 +4019,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Tăng Tấn Công theo tỷ lệ dựa trên chỉ số hiện tại.</t>
+          <t>Tăng ATK theo tỷ lệ dựa trên chỉ số hiện tại.</t>
         </is>
       </c>
     </row>
@@ -4149,7 +4149,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Tăng sát thương từ cả Vũ Khí Main và Hỗ Trợ Droid.</t>
+          <t>Tăng sát thương từ cả Vũ Khí Chính và Droid Hỗ Trợ.</t>
         </is>
       </c>
     </row>
@@ -4279,7 +4279,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Hồi phục HP theo tỷ lệ sát thương gây ra bởi Vũ Khí Main.</t>
+          <t>Hồi phục HP theo tỷ lệ sát thương gây ra bởi Vũ Khí Chính.</t>
         </is>
       </c>
     </row>
@@ -4409,7 +4409,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Tăng Tốc Độ Tấn Công theo tỷ lệ dựa trên chỉ số hiện tại.</t>
+          <t>Tăng Tốc Độ ATK theo tỷ lệ dựa trên chỉ số hiện tại.</t>
         </is>
       </c>
     </row>
@@ -4474,7 +4474,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Hạ nhiệt Hỗ Trợ Droid. Giảm Thời Gian Hạ Nhiệt không thể vượt quá 75%, ngoại trừ hiệu ứng của Sustained Combustion Protocol.</t>
+          <t>Hạ nhiệt Hỗ Trợ Droid. Giảm Thời Gian Hạ Nhiệt không thể vượt quá 75%, ngoại trừ hiệu ứng của Giao Thức Đốt Cháy Liên Tục.</t>
         </is>
       </c>
     </row>
@@ -4539,7 +4539,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Số lượng Hỗ Trợ Droid đã triển khai. Khi Giao Thức Attack Quỹ Đạo kích hoạt, thuộc tính này sẽ không tăng số lượng Hỗ Trợ Droid mà chuyển đổi thành thưởng Attack.</t>
+          <t>Số lượng Droid Hỗ Trợ đã triển khai. Khi Giao Thức Tấn Công Quỹ Đạo kích hoạt, thuộc tính này sẽ không tăng số lượng Droid Hỗ Trợ mà chuyển đổi thành thưởng Tấn Công.</t>
         </is>
       </c>
     </row>
@@ -4605,8 +4605,8 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Mở khóa Vũ Khí Chính: Zap Mô-đun
-Bắn thêm một tia laser theo chu kỳ đều đặn, gây sát thương lớn.</t>
+          <t>Mở khóa Vũ Khí Chính: Mô-đun Tia Điện
+Thỉnh thoảng bắn thêm một tia laser gây sát thương cực lớn.</t>
         </is>
       </c>
     </row>
@@ -4673,8 +4673,8 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Chest Mimic có thể xuất hiện trong cuộc đua. Hạ gục chúng để nhận thêm hiệu ứng tăng cường.
-Unlock Hỗ Trợ Droid: Giao Thức Tấn Công Quỹ Đạo.
+          <t>Rương Biến Hình có thể xuất hiện trong cuộc đua. Hạ gục chúng để nhận thêm hiệu ứng tăng cường.
+Mở khóa Droid Hỗ Trợ: Giao Thức Tấn Công Quỹ Đạo.
 Khóa mục tiêu và gọi một cuộc tấn công laser từ quỹ đạo, gây sát thương diện rộng.</t>
         </is>
       </c>
@@ -4742,9 +4742,9 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Mỗi khi Vũ Khí Main trúng kẻ địch, cộng dồn 5% Tăng Sát Thương, tối đa 500%. Nếu không gây sát thương trong 0.5 giây, hiệu ứng này sẽ bị loại bỏ.
-Unlock Vũ Khí Main: Repeater Mô-đun
-Weapon bắn nhiều đạn trong một loạt ngắn. Lựa chọn tốt để tập trung hỏa lực vào một mục tiêu.</t>
+          <t>Mỗi khi Vũ Khí Chính trúng kẻ địch, cộng dồn 5% Tăng Sát Thương, tối đa 500%. Nếu không gây DMG trong 0.5 giây, hiệu ứng này sẽ bị loại bỏ.
+Mở khóa Vũ Khí Chính: Repeater Module
+Vũ khí bắn nhiều đạn trong một loạt ngắn. Lựa chọn tốt để tập trung hỏa lực vào một mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -4812,8 +4812,8 @@
       <c r="M67" t="inlineStr">
         <is>
           <t>Tốc độ hồi Boost nhanh gấp đôi, nhưng thời gian duy trì giảm 50%.
-Unlock Hỗ Trợ Droid: Giao Thức Duy Trì Đốt Cháy
-Bắn đạn gây hiệu ứng bỏng, liên tục gây sát thương lên mục tiêu.</t>
+Mở khóa Droid Hỗ Trợ: Giao Thức Duy Trì Đốt Cháy
+Bắn đạn gây hiệu ứng bỏng, liên tục gây DMG lên mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -4879,8 +4879,8 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Mở khóa Vũ Khí Chính: Shotgun Mô-đun
-Bắn nhiều đạn cùng lúc trong phạm vi rộng hình quạt phía trước, rất hiệu quả khi đối phó với nhóm kẻ địch.</t>
+          <t>Mở khóa Vũ Khí Chính: Mô-đun Súng Ngắn
+Bắn nhiều đạn cùng lúc theo hình quạt rộng phía trước, lý tưởng để đối phó với nhóm địch.</t>
         </is>
       </c>
     </row>
@@ -4948,7 +4948,7 @@
       <c r="M69" t="inlineStr">
         <is>
           <t>Nhận một lượng hồi máu sau khi lao vào kẻ địch.
-Unlock Bộ Hỗ Trợ Droid: Guided Missile Protocol
+Mở khóa Bộ Hỗ Trợ Droid: Giao Thức Tên Lửa Điều Khiển
 Tự động bắn một tên lửa dẫn đường khóa mục tiêu gần nhất và tấn công.</t>
         </is>
       </c>
@@ -5081,7 +5081,7 @@
       <c r="M71" t="inlineStr">
         <is>
           <t>Tất cả kẻ địch chuyển đổi 20% HP tối đa thành lá chắn, ngăn chặn một số đòn tấn công.
-Hãy nghiền nát chúng bằng tổ hợp Mô-đun Lặp Lại và Giao Thức Đốt Cháy Duy Trì!</t>
+Hãy nghiền nát chúng bằng tổ hợp Module Lặp Lại và Giao Thức Đốt Cháy Duy Trì!</t>
         </is>
       </c>
     </row>
@@ -5146,7 +5146,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Cooldown năng lượng sau khi Boost dừng lại nếu năng lượng chưa cạn kiệt hoàn toàn.</t>
+          <t>Thời gian hồi năng lượng sau khi Boost dừng lại nếu năng lượng chưa cạn kiệt hoàn toàn.</t>
         </is>
       </c>
     </row>
@@ -5276,7 +5276,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Resonance Beacon</t>
+          <t>Điểm Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -5342,8 +5342,8 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Dưới Học viện là một dãy máy in nhỏ. Khi Void Storm gây gián đoạn nghiêm trọng, chúng triển khai Cube Chặn để bảo vệ các bộ phận lõi.
-Sau khi Void Storm qua đi, các máy bị ảnh hưởng nặng cần được thiết lập lại thủ công. Người vận hành phải vô hiệu hóa Cube Chặn để khôi phục hoạt động bình thường.</t>
+          <t>Dưới Học viện là một dãy máy in nhỏ. Khi Bão Hư Không gây gián đoạn nghiêm trọng, chúng triển khai Khối Lập Phương Chặn để bảo vệ các bộ phận lõi.
+Sau khi Bão Hư Không qua đi, các máy bị ảnh hưởng nặng cần được thiết lập lại thủ công. Người vận hành phải vô hiệu hóa Khối Lập Phương Chặn để khôi phục hoạt động bình thường.</t>
         </is>
       </c>
     </row>
@@ -5546,7 +5546,7 @@
           <t>Trung tâm của mạng lưới thông tin sinh thái được thiết kế dựa trên nguyên lý Khoa học Wutherium. Thường đặt tại các thị trấn trung bình và lớn, nó phát hiện và mô hình hóa dao động năng lượng, hoạt động của Tacet Discord, cùng các tín hiệu bất thường khác để đưa ra cảnh báo sớm về Hiện tượng Waveworn.
 Tại Roya Frostlands và Lahai-Roi, Resonance Nexus được gọi là Mảng Thấu kính Solis. Những thấu kính này tập trung và chuyển đổi ánh sáng từ Reactor Drive thành năng lượng sử dụng cho các cơ sở địa phương.
 Là một phần của hệ thống này, các Resonance Beacon nhỏ hơn ghi lại dữ liệu môi trường trong phạm vi của chúng và truyền về Nexus.
-Cậu có thể dịch chuyển nhanh đến bất kỳ Resonance Beacon nào đã kích hoạt để hồi phục Resonators bị thương hoặc bất tỉnh.</t>
+Cậu có thể dịch chuyển nhanh đến bất kỳ Resonance Beacon nào đã kích hoạt để hồi phục các Resonator bị thương hoặc bất tỉnh.</t>
         </is>
       </c>
     </row>
@@ -5613,7 +5613,7 @@
       <c r="M79" t="inlineStr">
         <is>
           <t>Hiệu ứng nâng cấp:
-Xuống xe và gây Sát Thương bằng 1200% Tấn Công của xe lên mục tiêu trong phạm vi, đồng thời tăng nhẹ Mức Độ Tần Số Lệch của chúng. Hồi chiêu: 10 giây.</t>
+Xuống xe và gây Sát Thương bằng 1200% ATK của xe lên mục tiêu trong phạm vi, đồng thời tăng nhẹ Mức Độ Tần Số Lệch của chúng. Thời gian hồi: 10 giây.</t>
         </is>
       </c>
     </row>
@@ -5680,7 +5680,7 @@
       <c r="M80" t="inlineStr">
         <is>
           <t>Hiệu ứng nâng cấp:
-Khi chịu ảnh hưởng của Void Storm, Resonators trong đội giảm 20% Sát Thương nhận vào.</t>
+Khi chịu ảnh hưởng của Bão Hư Không, Resonator trong đội giảm 20% Sát Thương nhận vào.</t>
         </is>
       </c>
     </row>
@@ -5747,7 +5747,7 @@
       <c r="M81" t="inlineStr">
         <is>
           <t>Hiệu ứng nâng cấp:
-Sau khi kích hoạt Ram Dynamics, Resonators trong đội tăng 20% Crit. Rate trong 30 giây.</t>
+Sau khi kích hoạt Ram Dynamics, Resonator trong đội tăng 20% Crit. Rate trong 30 giây.</t>
         </is>
       </c>
     </row>
@@ -5812,7 +5812,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Khi ở trong Echo, Resonators trong đội nhận được cộng dồn 20% sát thương toàn thuộc tính.</t>
+          <t>Khi ở trong Tổ Tacet, Resonator trong đội nhận được cộng dồn 20% DMG toàn thuộc tính.</t>
         </is>
       </c>
     </row>
@@ -5877,7 +5877,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>Khi ở trong Echo, Resonators trong đội nhận được cộng dồn 20% sát thương toàn thuộc tính. Tiêu diệt một Discord sẽ cộng thêm 2% sát thương toàn thuộc tính trong 40 giây, tối đa 15 tầng. Thời gian hiệu ứng sẽ được làm mới với mỗi tầng mới.</t>
+          <t>Khi ở trong Tổ Tacet, Resonator trong đội nhận được cộng dồn 20% DMG toàn thuộc tính. Tiêu diệt một Tacet Discord sẽ cộng thêm 2% DMG toàn thuộc tính trong 40 giây, tối đa 15 tầng. Thời gian hiệu ứng sẽ được làm mới với mỗi tầng mới.</t>
         </is>
       </c>
     </row>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>Xuống xe và kéo mục tiêu gần trong phạm vi về phía mình, gây Sát Thương Physical bằng 1200% Tấn Công của xe máy, đồng thời tăng nhẹ Off-Tune Level của mục tiêu. Hồi chiêu: 10 giây.</t>
+          <t>Xuống xe và kéo mục tiêu gần trong phạm vi về phía mình, gây Sát Thương Vật Lý bằng 1200% ATK của xe máy, đồng thời tăng nhẹ Mức Lệch Tần của mục tiêu. Thời gian hồi: 10 giây.</t>
         </is>
       </c>
     </row>
@@ -6007,7 +6007,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Xuống xe và kéo mục tiêu gần trong phạm vi về phía mình, gây Sát Thương Physical bằng 1600% Tấn Công của xe máy, đồng thời tăng vừa Off-Tune Level của mục tiêu. Hồi chiêu: 10 giây.</t>
+          <t>Xuống xe và kéo mục tiêu gần trong phạm vi về phía mình, gây Sát Thương Vật Lý bằng 1600% ATK của xe máy, đồng thời tăng vừa Mức Lệch Tần của mục tiêu. Thời gian hồi: 10 giây.</t>
         </is>
       </c>
     </row>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Xuống xe và kéo mục tiêu gần trong phạm vi về phía mình, gây Sát Thương Physical bằng 2000% Tấn Công của xe máy, đồng thời tăng vừa Off-Tune Level của mục tiêu. Hồi chiêu: 10 giây.</t>
+          <t>Xuống xe và kéo mục tiêu gần trong phạm vi về phía mình, gây Sát Thương Vật Lý bằng 2000% ATK của xe máy, đồng thời tăng vừa Mức Lệch Tần của mục tiêu. Thời gian hồi: 10 giây.</t>
         </is>
       </c>
     </row>
@@ -6137,7 +6137,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Các Resonators trong đội chịu ít hơn 5% sát thương.</t>
+          <t>Các Resonator trong đội chịu ít hơn 5% DMG.</t>
         </is>
       </c>
     </row>
@@ -6202,7 +6202,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Các Resonators trong đội chịu ít hơn 10% sát thương.</t>
+          <t>Các Resonator trong đội chịu ít hơn 10% DMG.</t>
         </is>
       </c>
     </row>
@@ -6267,7 +6267,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>Khi chịu ảnh hưởng của Void Storm, Resonators trong đội nhận ít hơn 10% Sát Thương sau khi gây Sát Thương Phá Vỡ Tần Số, đồng thời nhận một Lớp Shield tương đương 80% Strength Trường Lực của xe máy trong 30 giây, kích hoạt mỗi 20 giây một lần.</t>
+          <t>Khi chịu ảnh hưởng của Bão Hư Không, Resonator trong đội nhận ít hơn 10% Sát Thương sau khi gây Sát Thương Phá Vỡ Tần Số, đồng thời nhận một Lớp Khiên tương đương 80% Sức Mạnh Trường Lực của xe máy trong 30 giây, kích hoạt mỗi 20 giây một lần.</t>
         </is>
       </c>
     </row>
@@ -6332,7 +6332,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Khi chịu ảnh hưởng của Void Storm, Resonators trong đội nhận ít hơn 10% Sát Thương sau khi gây Sát Thương Phá Vỡ Tần Số, đồng thời nhận một Lớp Shield tương đương 150% Strength Trường Lực của xe máy trong 30 giây, kích hoạt mỗi 20 giây một lần.</t>
+          <t>Khi chịu ảnh hưởng của Bão Hư Không, Resonator trong đội nhận ít hơn 10% Sát Thương sau khi gây Sát Thương Phá Vỡ Tần Số, đồng thời nhận một Lớp Khiên tương đương 150% Sức Mạnh Trường Lực của xe máy trong 30 giây, kích hoạt mỗi 20 giây một lần.</t>
         </is>
       </c>
     </row>
@@ -6397,7 +6397,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>Sau khi sử dụng Gravity Well, Resonators trong đội gây thêm 20% sát thương Tune Rupture trong 120 giây.</t>
+          <t>Sau khi sử dụng Gravity Well, Resonator trong đội gây thêm 20% DMG Tune Rupture trong 120 giây.</t>
         </is>
       </c>
     </row>
@@ -6462,7 +6462,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Sau khi sử dụng Gravity Well, khi Resonators trong đội sử dụng Tune Break lên mục tiêu bị ảnh hưởng bởi Tune Strain - Shifting, họ cũng sẽ áp dụng thêm 1 lớp Tune Strain - Interfered kéo dài 120 giây.</t>
+          <t>Sau khi sử dụng Gravity Well, khi Resonator trong đội sử dụng Tune Break lên mục tiêu bị ảnh hưởng bởi Tune Strain - Shifting, họ cũng sẽ áp dụng thêm 1 lớp Tune Strain - Interfered kéo dài 120 giây.</t>
         </is>
       </c>
     </row>
@@ -6592,7 +6592,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Các Resonators trong đội chịu ít sát thương hơn.</t>
+          <t>Các Resonator trong đội chịu ít DMG hơn.</t>
         </is>
       </c>
     </row>
@@ -6657,7 +6657,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Khi chịu ảnh hưởng của Void Storm, Resonators trong đội nhận ít sát thương hơn và nhận Shield sau khi gây sát thương Vỡ Tần Số.</t>
+          <t>Khi chịu ảnh hưởng của Bão Hư Không, Resonator trong đội nhận ít DMG hơn và nhận Khiên sau khi gây DMG Vỡ Tần Số.</t>
         </is>
       </c>
     </row>
@@ -6722,7 +6722,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Khi sử dụng Gravity Well, sát thương Tune Rupture gây ra bởi Resonators trong đội sẽ tăng lên.</t>
+          <t>Khi sử dụng Gravity Well, DMG Tune Rupture gây ra bởi các Resonator trong đội sẽ tăng lên.</t>
         </is>
       </c>
     </row>
@@ -6787,7 +6787,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Sau khi sử dụng Gravity Well, khi Resonators trong đội sử dụng Tune Break lên mục tiêu bị ảnh hưởng bởi Tune Strain - Shifting, họ cũng sẽ áp dụng thêm 1 lớp Tune Strain - Interfered.</t>
+          <t>Sau khi sử dụng Gravity Well, khi Resonator trong đội sử dụng Tune Break lên mục tiêu bị ảnh hưởng bởi Tune Strain - Shifting, họ cũng sẽ áp dụng thêm 1 lớp Tune Strain - Interfered.</t>
         </is>
       </c>
     </row>
@@ -6852,7 +6852,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>Khi ở trong Echo, Resonators trong đội nhận thêm Tăng Sát Thương Thuộc Tính Chung.</t>
+          <t>Khi ở trong Tổ Tacet, các Resonator trong đội nhận thêm Tăng Sát Thương Thuộc Tính Chung.</t>
         </is>
       </c>
     </row>
@@ -6919,7 +6919,7 @@
       <c r="M99" t="inlineStr">
         <is>
           <t>Hiệu ứng Nâng cấp:
-Xuống xe và kéo các mục tiêu gần đó vào, gây Sát Thương Physical bằng 1200% Tấn Công của xe máy, đồng thời tăng nhẹ Mức Độ Mistune của mục tiêu. Cooldown chiêu: 10 giây.</t>
+Xuống xe và kéo các mục tiêu gần đó vào, gây Sát Thương Vật Lý bằng 1200% ATK của xe máy, đồng thời tăng nhẹ Mức Độ Lệch Tần của mục tiêu. Thời gian hồi chiêu: 10 giây.</t>
         </is>
       </c>
     </row>
@@ -6986,7 +6986,7 @@
       <c r="M100" t="inlineStr">
         <is>
           <t>Hiệu ứng Nâng cấp:
-Resonators trong đội chịu ít hơn 5% Sát Thương.</t>
+Resonator trong đội chịu ít hơn 5% Sát Thương.</t>
         </is>
       </c>
     </row>
@@ -7053,7 +7053,7 @@
       <c r="M101" t="inlineStr">
         <is>
           <t>Hiệu ứng nâng cấp:
-Khi chịu ảnh hưởng của Void Storm, Resonators trong đội giảm 10% Sát Thương nhận vào sau khi gây Sát Thương Vỡ Pha và nhận một Lớp Shield tương đương 80% Strength Trường Lực của xe máy trong 30 giây, kích hoạt mỗi 20 giây một lần.</t>
+Khi chịu ảnh hưởng của Bão Hư Không, Resonator trong đội giảm 10% Sát Thương nhận vào sau khi gây Sát Thương Vỡ Pha và nhận một Lớp Khiên tương đương 80% Sức Mạnh Trường Lực của xe máy trong 30 giây, kích hoạt mỗi 20 giây một lần.</t>
         </is>
       </c>
     </row>
@@ -7120,7 +7120,7 @@
       <c r="M102" t="inlineStr">
         <is>
           <t>Hiệu ứng nâng cấp:
-Sau khi sử dụng Gravity Well, Resonators trong đội gây thêm 20% Sát Thương Vỡ Tần Số trong 120 giây.</t>
+Sau khi sử dụng Gravity Well, Resonator trong đội gây thêm 20% Sát Thương Vỡ Tần Số trong 120 giây.</t>
         </is>
       </c>
     </row>
@@ -7187,7 +7187,7 @@
       <c r="M103" t="inlineStr">
         <is>
           <t>Hiệu ứng nâng cấp:
-Sau khi sử dụng Gravity Well, khi Resonators trong đội tung chiêu Vỡ Tần Số lên mục tiêu bị ảnh hưởng bởi Tần Số Méo - Dịch Chuyển, họ cũng sẽ áp dụng thêm 1 lớp Tần Số Méo - Giao Thoa kéo dài 120 giây.</t>
+Sau khi sử dụng Gravity Well, khi Resonator trong đội tung chiêu Vỡ Tần Số lên mục tiêu bị ảnh hưởng bởi Tần Số Méo - Dịch Chuyển, họ cũng sẽ áp dụng thêm 1 lớp Tần Số Méo - Giao Thoa kéo dài 120 giây.</t>
         </is>
       </c>
     </row>
@@ -7252,7 +7252,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>Khi ở trong Echo, Resonators trong đội nhận được cộng dồn 20% sát thương toàn thuộc tính.</t>
+          <t>Khi ở trong Tổ Tacet, Resonator trong đội nhận được cộng dồn 20% DMG toàn thuộc tính.</t>
         </is>
       </c>
     </row>
@@ -7318,7 +7318,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>&lt;color=RedA&gt;Bạn have not locked any Substats.&lt;/color&gt; Việc chỉnh sửa này sẽ tiêu tốn &lt;color=HighlightB&gt;x{0}&lt;/color&gt; Bộ Chuyển Hóa. Tiếp tục?
+          <t>&lt;color=RedA&gt;Bạn chưa khóa bất kỳ Thuộc tính phụ nào.&lt;/color&gt; Việc chỉnh sửa này sẽ tiêu tốn &lt;color=HighlightB&gt;x{0}&lt;/color&gt; Bộ Chuyển Hóa. Tiếp tục?
 (Nếu khóa 2 Thuộc tính phụ trở xuống, sẽ tiêu tốn 1 Bộ Chuyển Hóa)</t>
         </is>
       </c>
@@ -7385,8 +7385,8 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>Bạn đã khóa &lt;color=HighlightB&gt;&lt;SapTag=0&gt;{0}&lt;/SapTag&gt; {Cus:Sap,S=Thuộc tính phụ P=Thuộc tính phụ SapTag=0}&lt;/color&gt;. Thao tác này sẽ tiêu tốn &lt;color=HighlightB&gt;x{1}&lt;/color&gt; Transducer. Tiếp tục?
-(Sẽ tiêu tốn 1 Transducer nếu khóa 2 hoặc ít hơn Thuộc tính phụ)</t>
+          <t>Bạn đã khóa &lt;color=HighlightB&gt;&lt;SapTag=0&gt;{0}&lt;/SapTag&gt; {Cus:Sap,S=Thuộc tính phụ P=Thuộc tính phụ SapTag=0}&lt;/color&gt;. Thao tác này sẽ tiêu tốn &lt;color=HighlightB&gt;x{1}&lt;/color&gt; Bộ chuyển đổi. Tiếp tục?
+(Sẽ tiêu tốn 1 Bộ chuyển đổi nếu khóa 2 hoặc ít hơn Thuộc tính phụ)</t>
         </is>
       </c>
     </row>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>Danh sách này không có Echoes nào có Chỉ số Chính có thể điều chỉnh thành Chỉ số Chính mục tiêu.</t>
+          <t>Danh sách này không có Echo nào có Chỉ số Chính có thể điều chỉnh thành Chỉ số Chính mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -7588,14 +7588,14 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>[Trích từ Archive &lt;te href=851071&gt;Spacetrek Collective&lt;/te&gt;: Hồ Sơ Học Sinh - &lt;te href=851069&gt;Startorch Academy&lt;/te&gt;]
-[Báo Cáo Đánh Giá Năng Lực Resonance RA2362-G]
-Name Học Sinh: Aemeath
+          <t>[Trích từ Lưu Trữ &lt;te href=851071&gt;Spacetrek Collective&lt;/te&gt;: Hồ Sơ Học Sinh - &lt;te href=851069&gt;Học Viện Startorch&lt;/te&gt;]
+[Báo Cáo Đánh Giá Năng Lực Cộng Hưởng RA2362-G]
+Tên Học Sinh: Aemeath
 Trình Độ Đồng Bộ Hóa: Đạt
-Tổng Quan Năng Lực: Kiểm tra cho thấy &lt;te href=850067&gt;Rabelle's Curve&lt;/te&gt; có xu hướng tăng ổn định, hội tụ thành trạng thái dao động ổn định. Dựa trên các thông số hiện tại, đối tượng được phân loại là &lt;te href=850070&gt;Natural Resonator&lt;/te&gt;. &lt;te href=850072&gt;Tacet Mark&lt;/te&gt; của cô nằm ở vùng ngực.
-Theo hồ sơ cá nhân trước khi nhập học và lời khai của đối tượng, cá nhân ▇▇▂▇▋▌▏▉█... Được rồi, báo cáo này chẳng còn giá trị tham khảo nữa. Nó đã quá cũ. Nó nói về tôi khi tôi còn có thân xác. Để tôi chỉnh lại cho đúng. Current, tôi đã là Đồng Bộ Hóa Viên của Exostrider. Tacet Mark của tôi đã thay đổi so với trước. Giờ nó không còn... ổn định nhất nữa. Còn về khả năng của tôi, tôi có thể triệu hồi Vũ Khí Exostrider và đồng bộ trực tiếp với nó. Tạm dịch—Phải, tôi có thể biến hình! Và vì tôi thích chiến đấu hiệu quả, tôi đã lập trình chế độ lái tự động tùy chỉnh cho cỗ máy. Kết quả mô phỏng hiện tại khá khả quan. Cho phép tôi phủ kín chiến trường bằng màn trình diễn ánh sáng laser. À, và cái vụ hồn ma kỹ thuật số cho phép tôi xâm nhập vào bất kỳ hệ thống dữ liệu nào. Không chắc đó có thực sự là một phần trong Năng Lực của tôi hay chỉ là đặc quyền từ tình trạng Resonance độc đáo của tôi... ▇▉▇▇▂▇
+Tổng Quan Năng Lực: Kiểm tra cho thấy &lt;te href=850067&gt;Đường Cong Rabelle&lt;/te&gt; có xu hướng tăng ổn định, hội tụ thành trạng thái dao động ổn định. Dựa trên các thông số hiện tại, đối tượng được phân loại là &lt;te href=850070&gt;Resonator Tự Nhiên&lt;/te&gt;. &lt;te href=850072&gt;Dấu Tacet&lt;/te&gt; của cô nằm ở vùng ngực.
+Theo hồ sơ cá nhân trước khi nhập học và lời khai của đối tượng, cá nhân ▇▇▂▇▋▌▏▉█... Được rồi, báo cáo này chẳng còn giá trị tham khảo nữa. Nó đã quá cũ. Nó nói về tôi khi tôi còn có thân xác. Để tôi chỉnh lại cho đúng. Hiện tại, tôi đã là Đồng Bộ Hóa Viên của Exostrider. Dấu Tacet của tôi đã thay đổi so với trước. Giờ nó không còn... ổn định nhất nữa. Còn về khả năng của tôi, tôi có thể triệu hồi Vũ Khí Exostrider và đồng bộ trực tiếp với nó. Tạm dịch—Phải, tôi có thể biến hình! Và vì tôi thích chiến đấu hiệu quả, tôi đã lập trình chế độ lái tự động tùy chỉnh cho cỗ máy. Kết quả mô phỏng hiện tại khá khả quan. Cho phép tôi phủ kín chiến trường bằng màn trình diễn ánh sáng laser. À, và cái vụ hồn ma kỹ thuật số cho phép tôi xâm nhập vào bất kỳ hệ thống dữ liệu nào. Không chắc đó có thực sự là một phần trong Năng Lực của tôi hay chỉ là đặc quyền từ tình trạng Cộng Hưởng độc đáo của tôi... ▇▉▇▇▂▇
 &lt;i&gt;"Kỳ lạ... tại sao hồ sơ học sinh này lại bị hỏng? Toàn là lỗi dữ liệu."&lt;/i&gt;
-&lt;i&gt;"Đồng Bộ Hóa Viên mất tích? Tôi hiểu rồi... Report lại với Hiệu Trưởng Lucilla."&lt;/i&gt;</t>
+&lt;i&gt;"Đồng Bộ Hóa Viên mất tích? Tôi hiểu rồi... Báo cáo lại với Hiệu Trưởng Lucilla."&lt;/i&gt;</t>
         </is>
       </c>
     </row>
@@ -7667,14 +7667,14 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>["Hồ sơ do &lt;te href=851071&gt;Spacetrek Collective&lt;/te&gt; lưu trữ: Hồ sơ giảng viên &lt;te href=851069&gt;Startorch Academy&lt;/te&gt;]
-[Report Khảo sát Forte RA2462-G]
-Name: Luuk Herssen
-Overview Forte: Kiểm tra xác nhận &lt;te href=850072&gt;Tacet Mark&lt;/te&gt; của đối tượng nằm ở trung tâm lòng bàn tay phải, biểu hiện dưới dạng một vết thương mãn tính không lành. Dấu hiệu thể chất và xét nghiệm máu cho thấy sự hiện diện của một chất lỏng năng lượng dị thường—“Dịch Thần”—lưu thông trong cơ thể. Chất này có thể nhanh chóng thay đổi trạng thái pha theo ý chí. Khi kích hoạt, kèm theo cảm giác bỏng rát và nhiệt độ cao tạm thời. Việc sử dụng lâu dài đã dẫn đến mù màu. Hiện tại, đối tượng chỉ nhìn thấy màu vàng, các màu khác đều chuyển thành thang độ xám.
+          <t>["Hồ sơ do &lt;te href=851071&gt;Tập Đoàn Spacetrek&lt;/te&gt; lưu trữ: Hồ sơ giảng viên &lt;te href=851069&gt;Học viện Startorch&lt;/te&gt;]
+[Báo cáo Khảo sát Forte RA2462-G]
+Tên: Luuk Herssen
+Tổng quan Forte: Kiểm tra xác nhận &lt;te href=850072&gt;Dấu Tacet&lt;/te&gt; của đối tượng nằm ở trung tâm lòng bàn tay phải, biểu hiện dưới dạng một vết thương mãn tính không lành. Dấu hiệu thể chất và xét nghiệm máu cho thấy sự hiện diện của một chất lỏng năng lượng dị thường—“Dịch Thần”—lưu thông trong cơ thể. Chất này có thể nhanh chóng thay đổi trạng thái pha theo ý chí. Khi kích hoạt, kèm theo cảm giác bỏng rát và nhiệt độ cao tạm thời. Việc sử dụng lâu dài đã dẫn đến mù màu. Hiện tại, đối tượng chỉ nhìn thấy màu vàng, các màu khác đều chuyển thành thang độ xám.
 Đối tượng báo cáo triệu chứng ổn định và từ chối điều trị thêm.
 &lt;i&gt;“Việc kiểm tra và báo cáo được đối tượng tự thực hiện để đảm bảo tính chính xác của hồ sơ.”&lt;/i&gt;
-&lt;i&gt;“Địa điểm: Startorch Academy - Đơn vị Điều dưỡng Resonator.
-Recorder: Luuk Herssen.”&lt;/i&gt;</t>
+&lt;i&gt;“Địa điểm: Học viện Startorch - Đơn vị Điều dưỡng Resonator.
+Người ghi chép: Luuk Herssen.”&lt;/i&gt;</t>
         </is>
       </c>
     </row>
@@ -7753,11 +7753,11 @@
       <c r="M111" t="inlineStr">
         <is>
           <t>Một bông tuyết rơi nhẹ trên mũi Aemeath, lạnh và ẩm ướt, ngứa ngáy. Cô bé nhìn hồ nước một lúc, rồi quyết định không xuống chơi.
-Trước đây, cô từng vất vả kéo mấy thân Foxtail Kelp to tướng từ dưới nước lên, giả vờ chúng là những thanh kiếm oai phong. Cô và lũ Snowfluff Seals đã có những trận chiến đỉnh cao. Dĩ nhiên, cô là anh hùng, còn chúng là kẻ ác. Nhưng thực ra, những sinh vật hiền lành, ngoan ngoãn ấy chẳng bao giờ chống trả gì nhiều, và Aemeath luôn thắng. Thế nhưng có lần, cô đã quá tay. Những mảnh tảo vương vãi khắp cabin, bừa bộn kinh khủng. Khi người đó về nhà và thấy cảnh tượng ấy, {Male=anh;Female=cô} chỉ đứng im lặng ở cửa, im lặng rất lâu.
+Trước đây, cô từng vất vả kéo mấy thân Foxtail Kelp to tướng từ dưới nước lên, giả vờ chúng là những thanh kiếm oai phong. Cô và lũ Snowfluff Seals đã có những trận chiến đỉnh cao. Dĩ nhiên, cô là anh hùng, còn chúng là kẻ ác. Nhưng thực ra, những sinh vật hiền lành, ngoan ngoãn ấy chẳng bao giờ chống trả gì nhiều, và Aemeath luôn thắng. Thế nhưng có lần, cô đã quá tay. Những mảnh tảo vương vãi khắp cabin, bừa bộn kinh khủng. Khi người đó về nhà và thấy cảnh tượng ấy, {Male=he;Female=she} chỉ đứng im lặng ở cửa, im lặng rất lâu.
 Aemeath đương nhiên bị mắng cho một trận. Nhưng sau đó, có lẽ thấy mình quá nghiêm khắc, người đó đã mang về một chồng băng trò chơi để xin lỗi và đánh lạc hướng. Kế hoạch thành công mỹ mãn. Những trò chơi điện tử cuốn hút Aemeath đến mức cô quên luôn cả những trận chiến với lũ hải cẩu.
-Trong số đó, cô thích nhất là series Space Fantasy: Katya. Được du hành vũ trụ và cứu lấy cả vũ trụ ư? Of course! Ai mà chẳng muốn hóa thân thành người hùng điềm tĩnh, lôi cuốn và hơi u sầu ấy chứ?
+Trong số đó, cô thích nhất là series Space Fantasy: Katya. Được du hành vũ trụ và cứu lấy cả vũ trụ ư? Tất nhiên rồi! Ai mà chẳng muốn hóa thân thành người hùng điềm tĩnh, lôi cuốn và hơi u sầu ấy chứ?
 Một hôm, Aemeath đẩy cửa bước vào thì thấy người đó đang đọc sách trên sofa. Cô bé vui vẻ chen vào bên cạnh {Male=anh ấy;Female:cô ấy} và giơ chiếc tay cầm lên.
-"Play với con đi," cả tư thế của Aemeath như đang hét lên.
+"Chơi với con đi," cả tư thế của Aemeath như đang hét lên.
 Người đó mỉm cười, chạm nhẹ vào mũi cô bé rồi đồng ý.
 Bên ngoài, mùa đông kéo dài vô tận. Nhưng bên trong, lò sưởi rực hồng, bao trùm căn phòng trong hơi ấm và sự yên bình.
 Sau một hồi chơi, Aemeath lên tiếng: "Hôm nay chơi đến đây thôi. À! Con tìm thấy một căn phòng bí mật ở bên phải bản đồ đấy! Mật khẩu là 9072. Ở đó có thể chơi Lahai-Roi Blocks. Vui lắm!"
@@ -7841,14 +7841,14 @@
       <c r="M112" t="inlineStr">
         <is>
           <t>Aemeath bước đến trước gương, nhưng không có bóng dáng nào hiện lên.
-Sau khi chết, thế giới đã lệch nhịp. Những người bạn &lt;te href=700009&gt;Synchronist&lt;/te&gt; của cô từng tranh luận về bản chất của nhân loại. Alara nói đó là tình yêu, Nova tin đó là ký ức, Celeste cho rằng là cái tôi, còn Lynn khẳng định đó là niềm tin... "Không," Aemeath nghĩ. "Bản chất của nhân loại là tần số." Với những gì cô đã trở thành, đó là cách duy nhất để lý giải.
-Phải chăng sự Resonance với &lt;te href=700008&gt;Exostrider&lt;/te&gt; đã thay đổi trạng thái tồn tại của cô? Thể xác cô đã bị xé nát trong buồng mô phỏng. Lẽ ra cô phải chết. Nhưng cô vẫn ở đây. Dù là một bóng ma kỹ thuật số, cô có cả thời gian trên đời để suy ngẫm, nhưng giờ đây cô không còn bận tâm đến bản chất của sự tồn tại nữa.
+Sau khi chết, thế giới đã lệch nhịp. Những người bạn &lt;te href=700009&gt;Đồng Bộ Giả&lt;/te&gt; của cô từng tranh luận về bản chất của nhân loại. Alara nói đó là tình yêu, Nova tin đó là ký ức, Celeste cho rằng là cái tôi, còn Lynn khẳng định đó là niềm tin... "Không," Aemeath nghĩ. "Bản chất của nhân loại là tần số." Với những gì cô đã trở thành, đó là cách duy nhất để lý giải.
+Phải chăng sự Cộng Hưởng với &lt;te href=700008&gt;Exostrider&lt;/te&gt; đã thay đổi trạng thái tồn tại của cô? Thể xác cô đã bị xé nát trong buồng mô phỏng. Lẽ ra cô phải chết. Nhưng cô vẫn ở đây. Dù là một bóng ma kỹ thuật số, cô có cả thời gian trên đời để suy ngẫm, nhưng giờ đây cô không còn bận tâm đến bản chất của sự tồn tại nữa.
 Điều cô hiểu ra giờ đây quan trọng hơn nhiều.
 Khi bước vào &lt;te href=700010&gt;Reactor Drive&lt;/te&gt; của Exostrider lơ lửng trên bầu trời, cô đã nhìn thấy thông điệp ẩn giấu trong đó.
-"Thì ra là như vậy," cô nhận ra. Thông điệp đó chưa bao giờ được đọc vì ngay từ đầu, nó đã được đặt ở nơi không ai có thể tiếp cận. Chỉ đến bây giờ, khi là một Synchronist cộng hưởng với Exostrider, cô mới nhìn thấy. Toàn bộ hang động ngầm này dựa vào "mặt trời" này để tồn tại, nên dĩ nhiên, người dân &lt;te href=260004&gt;Lahai-Roi&lt;/te&gt; chẳng bao giờ có cơ hội biết.
+"Thì ra là như vậy," cô nhận ra. Thông điệp đó chưa bao giờ được đọc vì ngay từ đầu, nó đã được đặt ở nơi không ai có thể tiếp cận. Chỉ đến bây giờ, khi là một Đồng Bộ Giả cộng hưởng với Exostrider, cô mới nhìn thấy. Toàn bộ hang động ngầm này dựa vào "mặt trời" này để tồn tại, nên dĩ nhiên, người dân &lt;te href=260004&gt;Lahai-Roi&lt;/te&gt; chẳng bao giờ có cơ hội biết.
 Liệu cô có nên vui mừng? Nội dung thông điệp cho cô cơ hội thực hiện tầm nhìn vĩ đại nhất của mình, nhưng theo cách mà cô chưa từng tưởng tượng. Một trò đùa cay nghiệt của vũ trụ. Nhưng đây là nhiệm vụ chỉ có cô mới có thể hoàn thành.
 "Nếu có thể giúp được, tôi sẽ làm. Tôi phải làm."
-…Yes. Đó là cách nó phải thế.
+…Đúng vậy. Đó là cách nó phải thế.
 Aemeath nghĩ về người đó và lặng lẽ tự cổ vũ bản thân. Cô có thể dũng cảm hơn. Kiên định hơn. Cô chưa sẵn sàng, nhưng không sao. Vẫn còn thời gian để chuẩn bị. Xét cho cùng, số phận đã ưu ái cô. Mải mê suy nghĩ, cô bất giác ngân nga một giai điệu. Thật tiếc khi Fleet Snowfluff không thể phát hành bài hát mới của cô. Nếu biết ngày mai sẽ ra sao, có lẽ cô đã hoàn thành nó.
 Tấm gương không phản chiếu khuôn mặt cô, nên Aemeath không thấy nụ cười của chính mình. Nó giống như một vệt màu sáp bị kéo lệch, đột ngột đứt đoạn ở cuối.</t>
         </is>
@@ -7941,23 +7941,23 @@
 Luuk chợt nhớ lại lời cha mình: "Con nên cảm thấy may mắn. Dòng Ichor đã chọn con."
 Dù mù màu và những cơn đau thiêu đốt đến bất chợt, Luuk vẫn là người duy nhất thực sự được chữa lành bởi Ichor. Không ngoại lệ, tất cả những người khác đều đi theo cùng một quỹ đạo bi thảm như Rhein.
 Luuk kéo chiếc ghế bên giường. Căn phòng im lặng, chỉ có tiếng bíp đều đặn của máy theo dõi. Anh cố phá vỡ bầu không khí ngột ngạt.
-"Tớ từng học tâm lý học một thời gian," anh nói. "Tớ nghĩ... có thể nó sẽ giúp tớ hiểu mọi thứ rõ hơn. Help người khác tốt hơn." Sau một lúc ngừng lại, anh tiếp, "Tớ cũng nấu ăn giỏi hơn nhiều rồi. Không còn làm cháy bánh nữa. Cậu muốn ăn gì không? Tớ có thể làm cho."
-Silence. Luuk không bỏ cuộc. Anh chuyển chủ đề.
-"Tớ... mới gặp một người gần đây. Một người bạn. Thông minh, đáng tin cậy. {Male=Anh ấy;Female=Cô ấy} đã thách thức rất nhiều quan điểm cũ cứng nhắc của tớ. Có lẽ tớ nên thử thay đổi..."
+"Tớ từng học tâm lý học một thời gian," anh nói. "Tớ nghĩ... có thể nó sẽ giúp tớ hiểu mọi thứ rõ hơn. Giúp đỡ người khác tốt hơn." Sau một lúc ngừng lại, anh tiếp, "Tớ cũng nấu ăn giỏi hơn nhiều rồi. Không còn làm cháy bánh nữa. Cậu muốn ăn gì không? Tớ có thể làm cho."
+Im lặng. Luuk không bỏ cuộc. Anh chuyển chủ đề.
+"Tớ... mới gặp một người gần đây. Một người bạn. Thông minh, đáng tin cậy. {Male=he;Female=she} đã thách thức rất nhiều quan điểm cũ cứng nhắc của tớ. Có lẽ tớ nên thử thay đổi..."
 "Cậu có thực sự cần phải làm thế không?" Giọng Rhein cắt ngang, khàn khàn và sắc lạnh như lưỡi dao băng. "Chẳng phải cậu luôn là người đặc biệt sao? Không giống như chúng ta, những kẻ tầm thường."
 Luuk nghẹn thở. Sự bình tĩnh mà anh cố duy trì đổ vỡ tan tành. Anh nhìn vào đôi mắt Rhein, từng sáng rực và tràn đầy sức sống, giờ đây mờ đục gần như trống rỗng. Và bên dưới bề mặt tĩnh lặng ấy, một thứ gì đó không thể nhầm lẫn đang sục sôi—sự căm ghét.
 ...
 "Anh ấy không chịu nói chuyện với tớ nữa," Luuk thì thầm.
-Câu trả lời từ Terminal vẫn như mọi khi, điềm tĩnh. "Điều anh ấy căm ghét không phải là cậu. Mà là tất cả những gì cái tên 'Herssen' đại diện. Cậu chỉ là mục tiêu an toàn duy nhất để trút giận thôi."
+Câu trả lời từ Thiết bị đầu cuối vẫn như mọi khi, điềm tĩnh. "Điều anh ấy căm ghét không phải là cậu. Mà là tất cả những gì cái tên 'Herssen' đại diện. Cậu chỉ là mục tiêu an toàn duy nhất để trút giận thôi."
 Luuk im lặng một lúc. "...Cảm ơn."
 "Cậu đã tìm ra điều gì chưa?"
 "Các manh mối đang dần nối liền với nhau," Luuk đáp, nhìn ra ngoài cửa sổ. Những đám mây đen cuộn xoáy, báo hiệu một cơn bão. "Tối nay... tớ sẽ xác nhận sự thật."
 Đêm đó, mưa trút xuống như muốn đóng đinh cả thế giới vào lòng đất. Luuk một mình bước vào nghĩa trang hoang vắng. Tia chớp trắng xé toạc bầu trời, chiếu sáng tấm bia mộ phía trước. Đó là mộ của cha anh.
 Và rồi anh nhìn thấy.
-Xuyên qua màn mưa, một bóng người đứng lặng lẽ trước mộ, tay cầm ô, như thể đã đợi sẵn. Những hạt mưa nổ tung trên vải, chảy xuống rìa ô như thác nước. Nhưng xuyên qua màn sương mù xám xịt, Luuk vẫn thấy đôi mắt nhìn lại mình với độ sắc Dodget hoàn hảo.
+Xuyên qua màn mưa, một bóng người đứng lặng lẽ trước mộ, tay cầm ô, như thể đã đợi sẵn. Những hạt mưa nổ tung trên vải, chảy xuống rìa ô như thác nước. Nhưng xuyên qua màn sương mù xám xịt, Luuk vẫn thấy đôi mắt nhìn lại mình với độ sắc nét hoàn hảo.
 ...Vàng. Như Ichor nóng chảy. Như tia nắng đầu tiên chiếu lên vùng đất băng giá.
 Màu sắc rực rỡ duy nhất trong thế giới tro tàn này.
-"Nếu cậu thực sự đã phát hiện ra điều gì," {Male=anh ấy;Female=cô ấy} nói, bước qua vũng nước tiến về phía anh, "thì cậu sẽ cần một nhân chứng."</t>
+"Nếu cậu thực sự đã phát hiện ra điều gì," {Male=he;Female=she} nói, bước qua vũng nước tiến về phía anh, "thì cậu sẽ cần một nhân chứng."</t>
         </is>
       </c>
     </row>
@@ -8477,7 +8477,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>Khi ở trong [Divined Dream], Sát Thương Đứt Giai Tune và Vỡ Giai Tune sẽ bỏ qua PHÒNG NGỰ của mục tiêu. Khi bước vào [Divined Dream], các mục tiêu xung quanh sẽ bị ảnh hưởng bởi Mistune.</t>
+          <t>Khi ở trong [Divined Dream], Sát Thương Đứt Giai Điệu và Vỡ Giai Điệu sẽ bỏ qua PHÒNG NGỰ của mục tiêu. Khi bước vào [Divined Dream], các mục tiêu xung quanh sẽ bị ảnh hưởng bởi Mistune.</t>
         </is>
       </c>
     </row>
@@ -8609,7 +8609,7 @@
       <c r="M123" t="inlineStr">
         <is>
           <t>Khi Resonator chủ động gây Sát Thương Phá Nhịp lên mục tiêu đang chịu hiệu ứng Phá Nhịp - Giao Thoa, gây thêm 6000% Sát Thương thuộc tính của Resonator đó, được tính là Sát Thương Phá Nhịp. Hiệu ứng này chỉ có thể kích hoạt mỗi 3 giây một lần.
-Khi Resonator chủ động gây Sát Thương Phá Nhịp lên mục tiêu đang chịu hiệu ứng Căng Nhịp - Giao Thoa, Movement Speed của Resonator tăng 30% và Sát Thương gây ra được Khuếch Đại thêm 60% trong 4 giây. Hiệu ứng này chỉ có thể kích hoạt mỗi 3 giây một lần.</t>
+Khi Resonator chủ động gây Sát Thương Phá Nhịp lên mục tiêu đang chịu hiệu ứng Căng Nhịp - Giao Thoa, Tốc Độ Di Chuyển của Resonator tăng 30% và Sát Thương gây ra được Khuếch Đại thêm 60% trong 4 giây. Hiệu ứng này chỉ có thể kích hoạt mỗi 3 giây một lần.</t>
         </is>
       </c>
     </row>
@@ -8675,8 +8675,8 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>Khi Resonators gây Sát Thương Phá Nhịp trong [Divined Dream], áp 1 tầng [Dấu Hiệu Loạn Nhịp], và tăng Hiệu Ứng Phá Nhịp cho tất cả Resonators lên 50. Hiệu ứng này có thể kích hoạt mỗi 3 giây, tối đa 3 tầng. Tất cả các tầng sẽ bị xóa khi kết thúc [Divined Dream].
-Khi mục tiêu tích đủ 3 tầng [Dấu Hiệu Loạn Nhịp], Sát Thương Phá Nhịp tiếp theo sẽ xóa toàn bộ tầng và khiến mục tiêu mất 30% HP tối đa. Nếu mục tiêu là kẻ địch Loại Common, mỗi lần nhận [Dấu Hiệu Loạn Nhịp] cũng khiến nó mất 30% HP tối đa.</t>
+          <t>Khi Resonator gây Sát Thương Phá Nhịp trong [Giấc Mộng Tiên Tri], áp 1 tầng [Dấu Hiệu Loạn Nhịp], và tăng Hiệu Ứng Phá Nhịp cho tất cả Resonator lên 50. Hiệu ứng này có thể kích hoạt mỗi 3 giây, tối đa 3 tầng. Tất cả các tầng sẽ bị xóa khi kết thúc [Giấc Mộng Tiên Tri].
+Khi mục tiêu tích đủ 3 tầng [Dấu Hiệu Loạn Nhịp], Sát Thương Phá Nhịp tiếp theo sẽ xóa toàn bộ tầng và khiến mục tiêu mất 30% HP tối đa. Nếu mục tiêu là kẻ địch Loại Thường, mỗi lần nhận [Dấu Hiệu Loạn Nhịp] cũng khiến nó mất 30% HP tối đa.</t>
         </is>
       </c>
     </row>
@@ -8742,8 +8742,8 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>Trong [Giấc Mơ Tiên Tri], khi Resonator chủ động gây sát thương lên mục tiêu đang chịu hiệu ứng Tune Rupture - Interfered, gây thêm 1000% sát thương thuộc tính của Resonator đó, được tính là sát thương Tune Rupture. Hiệu ứng này có thể kích hoạt mỗi 0.5 giây.
-Trong [Giấc Mơ Tiên Tri], khi Resonator chủ động gây sát thương lên mục tiêu đang chịu hiệu ứng Tune Strain - Interfered, tổng sát thương của Resonator trong [Giấc Mơ Tiên Tri] sẽ tăng 1% trong 30 giây, có thể chồng chất lên đến 300 lần.</t>
+          <t>Trong [Giấc Mơ Tiên Tri], khi Resonator chủ động gây DMG lên mục tiêu đang chịu hiệu ứng Tune Rupture - Interfered, gây thêm 1000% DMG thuộc tính của Resonator đó, được tính là DMG Tune Rupture. Hiệu ứng này có thể kích hoạt mỗi 0.5 giây.
+Trong [Giấc Mơ Tiên Tri], khi Resonator chủ động gây DMG lên mục tiêu đang chịu hiệu ứng Tune Strain - Interfered, tổng DMG của Resonator trong [Giấc Mơ Tiên Tri] sẽ tăng 1% trong 30 giây, có thể chồng chất lên đến 300 lần.</t>
         </is>
       </c>
     </row>
@@ -8808,7 +8808,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>Khi ở trong [Divined Dream], liên tục gây hiệu ứng Mistune lên tất cả mục tiêu xung quanh. Gây Sát Thương Vỡ Giai Tune sẽ kéo dài thời gian của Divined Dream.</t>
+          <t>Khi ở trong [Divined Dream], liên tục gây hiệu ứng Mistune lên tất cả mục tiêu xung quanh. Gây Sát Thương Vỡ Giai Điệu sẽ kéo dài thời gian của Divined Dream.</t>
         </is>
       </c>
     </row>
@@ -8873,7 +8873,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>Gây Sát Thương Đột Tune Break sẽ kích hoạt sát thương bổ sung lên mục tiêu đang chịu hiệu ứng Tune Rupture - Interfered. Gây sát thương lên mục tiêu đang chịu Đè Dodgen Giai Tune - Nhiễu Loạn sẽ giúp Resonator nhận hiệu ứng DMG Amplification.</t>
+          <t>Gây Sát Thương Đột Phá Giai Điệu sẽ kích hoạt DMG bổ sung lên mục tiêu đang chịu hiệu ứng Đứt Giai Điệu - Nhiễu Loạn. Gây DMG lên mục tiêu đang chịu Đè Nén Giai Điệu - Nhiễu Loạn sẽ giúp Resonator nhận hiệu ứng Khuếch Đại Sát Thương.</t>
         </is>
       </c>
     </row>
@@ -9003,7 +9003,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>Khi ở trong [Divined Dream], Resonator gây thêm sát thương lên mục tiêu đang chịu hiệu ứng Tune Rupture - Interfered. Gây sát thương lên mục tiêu chịu Đè Dodgen Giai Tune - Nhiễu Loạn sẽ làm tăng tổng sát thương của Resonator.</t>
+          <t>Khi ở trong [Giấc Mộng Tiên Tri], Resonator gây thêm DMG lên mục tiêu đang chịu hiệu ứng Đứt Giai Điệu - Nhiễu Loạn. Gây DMG lên mục tiêu chịu Đè Nén Giai Điệu - Nhiễu Loạn sẽ làm tăng tổng DMG của Resonator.</t>
         </is>
       </c>
     </row>
@@ -9072,9 +9072,9 @@
       <c r="M130" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Heavy Attack]&lt;/color&gt;
-- Khi Năng Lực đạt {0} điểm, giữ Normal Attack hoặc {Cus:Ipt,Touch=tap PC=press Gamepad=press} giữa không trung để tiêu hao {0} điểm Năng Lực và thực hiện Heavy Attack - Thunderoar: Uppercut.
-- Thực hiện Heavy Attack - Thunderoar: Uppercut sẽ hồi phục thêm {1} Ascendancy và tăng {2} Sát Thương Bonus trong {4} giây, có thể cộng dồn tối đa {3} lần.
-- Khi Năng Lực đạt {0} điểm, giữ Normal Attack sau khi thực hiện Stage 2 Basic Attack để tiêu hao {0} điểm Năng Lực và thực hiện Heavy Attack - Thunderoar: Backstep.</t>
+- Khi Năng Lực đạt {0} điểm, giữ Normal Attack hoặc {Cus: Ipt,Touch=tap PC=press Gamepad=press} it in mid-air to consume {0} points Prowess and perform Heavy Attack - Thunderoar: Uppercut.
+- Performing Heavy Attack - Thunderoar: Uppercut additionally restores {1} of Ascendancy and grants {2} DMG Bonus for {4}s, stacking up to {3} times.
+- When Prowess reaches {0} points, hold Normal Attack after performing Basic Attack Stage 2 to consume {0} points Prowess and perform Heavy Attack - Thunderoar: Backstep.</t>
         </is>
       </c>
     </row>
@@ -9146,9 +9146,9 @@
         <is>
           <t>&lt;color=#c49e55&gt;[Resonance Liberation]&lt;/color&gt;
 - Thực hiện Heavy Attack - Tiếng Sấm Ngân: Uppercut hoặc Heavy Attack - Tiếng Sấm Ngân: Lùi Bước sẽ nhận được {0} tầng Sao Mai, tối đa {1} tầng.
-- Khi Sao Mai đạt {2} tầng trở lên, {Cus:Ipt,Touch=tấn PC=press Gamepad=press} Resonance Liberation để tiêu hao {2} tầng Sao Mai và thực hiện Đòn Phá Tan.
-- Sau khi thực hiện {3} Đòn Phá Tan liên tiếp, nếu có từ {4} tầng Sao Mai trở lên, {Cus:Ipt,Touch=tấn PC=press Gamepad=press} Resonance Liberation để tiêu hao {2} tầng Sao Mai và thực hiện Eclipse.
-- Sao Mai và Nhật Thực gây Electro DMG tương đương {5} và {6} Attack, cả hai đều được tính là Sát Thương Heavy Attack.
+- Khi Sao Mai đạt {2} tầng trở lên, {Cus:Ipt,Touch=tap PC=press Gamepad=press} Resonance Liberation để tiêu hao {2} tầng Sao Mai và thực hiện Đòn Phá Tan.
+- Sau khi thực hiện {3} Đòn Phá Tan liên tiếp, nếu có từ {4} tầng Sao Mai trở lên, {Cus:Ipt,Touch=tap PC=press Gamepad=press} Resonance Liberation để tiêu hao {2} tầng Sao Mai và thực hiện Nhật Thực.
+- Sao Mai và Nhật Thực gây Sát Thương Electro tương đương {5} và {6} ATK, cả hai đều được tính là Sát Thương Heavy Attack.
 - Thực hiện Heavy Attack - Tiếng Sấm Ngân: Uppercut, Heavy Attack - Tiếng Sấm Ngân: Lùi Bước, Đòn Phá Tan hoặc Nhật Thực sẽ hồi phục thêm {7} điểm Resonance Energy và tăng {8} Sát Thương Bonus trong {10} giây, tối đa {9} tầng.</t>
         </is>
       </c>
@@ -9217,8 +9217,8 @@
       <c r="M132" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Resonance Liberation]&lt;/color&gt;
-- Tổng sát thương của Resonance Liberation - Kiếm Lời Thề Vĩnh Cửu, Sublime is the Sun - Sunborne và Sublime is the Sun - Everbright Protector được tăng thêm {0}.
-- Cooldown chiêu của Resonance Liberation - Kiếm Lời Thề Vĩnh Cửu giảm {1} giây. Sử dụng Resonance Liberation này sẽ phục hồi {2} Năng Lượng Thăng Hoa.</t>
+- Tổng DMG của Resonance Liberation - Kiếm Lời Thề Vĩnh Cửu, Sublime is the Sun - Sunborne và Sublime is the Sun - Everbright Protector được tăng thêm {0}.
+- Thời gian hồi chiêu của Resonance Liberation - Kiếm Lời Thề Vĩnh Cửu giảm {1} giây. Sử dụng Resonance Liberation này sẽ phục hồi {2} Năng Lượng Thăng Hoa.</t>
         </is>
       </c>
     </row>
@@ -9285,7 +9285,7 @@
       <c r="M133" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt;
-Electro DMG tăng thêm {0}. Khi Năng Lượng Thăng Hoa đầy và trạng thái Resonance Skill - Ánh Dương Bất Tử chưa kích hoạt, {Cus:Ipt,Touch=tap PC=press Gamepad=press} Normal Attack trên không để tiêu hao toàn bộ Năng Lượng Thăng Hoa và thi triển Resonance Skill - Ánh Dương Bất Tử: Lao Xuống.</t>
+DMG Electro tăng thêm {0}. Khi Năng Lượng Thăng Hoa đầy và trạng thái Resonance Skill - Ánh Dương Bất Tử chưa kích hoạt, {Cus: Ipt,Touch=tap PC=press Gamepad=press} Normal Attack in mid-air to consume all Ascendancy and cast Resonance Skill - Undying Sunlight: Plunge.</t>
         </is>
       </c>
     </row>
@@ -9352,7 +9352,7 @@
       <c r="M134" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt;
-Nhận Shield sẽ tăng {0} Sát Thương Heavy Attack và giảm {1} Sát Thương nhận vào trong {3} giây, có thể tích lũy tối đa {2} lần.</t>
+Nhận Khiên sẽ tăng {0} Sát Thương Đòn Tấn Công Mạnh và giảm {1} Sát Thương nhận vào trong {3} giây, có thể tích lũy tối đa {2} lần.</t>
         </is>
       </c>
     </row>
@@ -9421,7 +9421,7 @@
         <is>
           <t>&lt;color=#c49e55&gt;[Basic Attack]&lt;/color&gt;
 - Thực hiện Basic Attack với Moonring sẽ hồi phục {0} điểm Resonance Energy.
-- Khi tiêu hao Sentience, Basic Attack với Moonbow bắn thêm {1} Mũi Tên Ánh Trăng. Mỗi mũi tên gây Aero DMG bằng {2} Attack và được tính là sát thương Resonance Liberation.</t>
+- Khi tiêu hao Sentience, Basic Attack với Moonbow bắn thêm {1} Mũi Tên Ánh Trăng. Mỗi mũi tên gây DMG Aero bằng {2} ATK và được tính là DMG Resonance Liberation.</t>
         </is>
       </c>
     </row>
@@ -9488,7 +9488,7 @@
       <c r="M136" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Resonance Liberation]&lt;/color&gt;
-Giảm Cooldown chiêu của Resonance Liberation - Dưới Ánh Trăng {0} giây. Đòn tấn công này cũng bắn ra {1} Mũi Tên Minh Triết, mỗi mũi tên gây Aero DMG bằng {2} Tấn Công và được tính là sát thương Resonance Liberation.</t>
+Giảm Thời gian hồi chiêu của Resonance Liberation - Dưới Ánh Trăng {0} giây. Đòn tấn công này cũng bắn ra {1} Mũi Tên Minh Triết, mỗi mũi tên gây DMG Aero bằng {2} ATK và được tính là DMG Resonance Liberation.</t>
         </is>
       </c>
     </row>
@@ -9624,7 +9624,7 @@
       <c r="M138" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt;
-Trong Lãnh Địa Full Moon, Crit. DMG của tất cả Resonators trong đội tăng {0}. Trong {3} giây, họ cũng nhận được Shield mỗi {1} giây bằng {2} Tấn Công của Iuno.</t>
+Trong Lãnh Địa Trăng Tròn, Crit. DMG của tất cả Resonator trong đội tăng {0}. Trong {3} giây, họ cũng nhận được Khiên mỗi {1} giây bằng {2} ATK của Iuno.</t>
         </is>
       </c>
     </row>
@@ -9692,8 +9692,8 @@
       <c r="M139" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt;
-- Iuno nhận &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; {Cus:Sap,S=stack P=stacks SapTag=1} Blessing Ánh Sáng Vô Tận mỗi {0} giây.
-- Thi triển Heavy Attack - Thăng Giáng sẽ tăng Aero DMG thêm {2} trong {3} giây và làm đình trệ kẻ địch xung quanh trong {4} giây.</t>
+- Iuno nhận &lt;SapTag=1&gt;{1}&lt;/SapTag&gt; {Cus:Sap,S=stack P=stacks SapTag=1} Phước Lành Ánh Sáng Vô Tận mỗi {0} giây.
+- Thi triển Đòn Heavy Attack - Thăng Giáng sẽ tăng Sát Thương Aero thêm {2} trong {3} giây và làm đình trệ kẻ địch xung quanh trong {4} giây.</t>
         </is>
       </c>
     </row>
@@ -9760,7 +9760,7 @@
       <c r="M140" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt;
-Khi ở trạng thái Bản Thể Ác Quỷ, nhận thêm {0} Sát Thương Kỹ Năng Echo và tăng tổng Sát Thương Basic Attack và Heavy Attack lên {1}.</t>
+Khi ở trạng thái Bản Thể Ác Quỷ, nhận thêm {0} Sát Thương Kỹ Năng Echo và tăng tổng Sát Thương Đòn Basic Attack và Đòn Heavy Attack lên {1}.</t>
         </is>
       </c>
     </row>
@@ -9828,8 +9828,8 @@
       <c r="M141" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt;
-- Khi kích hoạt Hellstride trong Threshold State, Galbrena sẽ gây thêm Fusion DMG bằng {0} Attack của bản thân (được tính là sát thương của Heavy Attack) và khiến kẻ địch xung quanh bị trì trệ trong {1} giây. {Cus:Ipt,Touch=Touch PC=press Gamepad=press} Normal Attack lần tiếp theo sẽ kích hoạt Giai Đoạn 3 và 4 của Basic Attack và phục hồi {2} điểm Sinflame.
-- Mỗi lần kích hoạt Hellstride sẽ tăng {3} Fusion DMG trong {4} giây, có thể cộng dồn tối đa {5} lần.</t>
+- Khi kích hoạt Hellstride trong Trạng Thái Ngưỡng, Galbrena sẽ gây thêm Sát Thương Fusion bằng {0} ATK của bản thân (được tính là DMG của Đòn Heavy Attack) và khiến kẻ địch xung quanh bị trì trệ trong {1} giây. {Cus:Ipt,Touch=Tapping PC=Pressing Gamepad=Pressing} Đòn Normal Attack lần tiếp theo sẽ kích hoạt Giai Đoạn 3 và 4 của Đòn Basic Attack và phục hồi {2} điểm Sinflame.
+- Mỗi lần kích hoạt Hellstride sẽ tăng {3} Sát Thương Fusion trong {4} giây, có thể cộng dồn tối đa {5} lần.</t>
         </is>
       </c>
     </row>
@@ -9895,8 +9895,8 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Mid-air Attack]&lt;/color&gt;
-Resonance Skill - Demon Arisen giảm Fusion RES của kẻ địch {0} trong {1} giây khi trúng mục tiêu.</t>
+          <t>&lt;color=#c49e55&gt;[Đòn Tấn Công Giữa Không]&lt;/color&gt;
+Resonance Skill - Demon Arisen giảm Kháng Fusion của kẻ địch {0} trong {1} giây khi trúng mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -10033,8 +10033,8 @@
       <c r="M144" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Resonance Liberation]&lt;/color&gt;
-- Cooldown chiêu của Resonance Liberation - Ân Xá Hỏa Ngục giảm {0} giây.
-- Trong quá trình sử dụng Resonance Liberation này, mỗi {1} điểm Ngọn Sinflame hoặc Ngọn Purging Flame nhận được sẽ hồi phục {2} điểm Ngọn Lửa Dư và tăng {3} Sát Thương Bonus trong {4} giây.</t>
+- Thời gian hồi chiêu của Resonance Liberation - Ân Xá Hỏa Ngục giảm {0} giây.
+- Trong quá trình sử dụng Resonance Liberation này, mỗi {1} điểm Ngọn Lửa Tội hoặc Ngọn Lửa Thanh Tẩy nhận được sẽ hồi phục {2} điểm Ngọn Lửa Dư và tăng {3} Sát Thương Bonus trong {4} giây.</t>
         </is>
       </c>
     </row>
@@ -10169,8 +10169,8 @@
       <c r="M146" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt;
-- Crit. Rate tăng thêm {0}. Khi Crit. Rate vượt quá {1}, mỗi {2} Crit. Rate dư sẽ chuyển hóa thành {3} Attack.
-- Gây Crit. DMG sẽ kích hoạt {4} đòn Zephyr Slash, tổng cộng gây Aero DMG bằng {5} Attack, được tính là sát thương của Heavy Attack. Hiệu ứng này có thể kích hoạt &lt;SapTag=7&gt;{7}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=7} mỗi {6} giây.</t>
+- Crit. Rate tăng thêm {0}. Khi Crit. Rate vượt quá {1}, mỗi {2} Crit. Rate dư sẽ chuyển hóa thành {3} ATK.
+- Gây Sát Thương Bạo Kích sẽ kích hoạt {4} đòn Zephyr Slash, tổng cộng gây Sát Thương Aero bằng {5} ATK, được tính là DMG của Đòn Heavy Attack. Hiệu ứng này có thể kích hoạt &lt;SapTag=7&gt;{7}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=7} mỗi {6} giây.</t>
         </is>
       </c>
     </row>
@@ -10238,8 +10238,8 @@
       <c r="M147" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Basic Attack]&lt;/color&gt;
-- Basic Attack được thay thế bằng Lưỡi Kiếm Lên Tiếng - Mực Tàu, và đòn tấn công Giai Đoạn {0} sẽ hồi phục thêm {1} điểm Swordster's Soliloquy.
-- Khi Heavy Attack hoặc Lưỡi Kiếm Lên Tiếng - Mực Tàu Giai Đoạn {2} trúng mục tiêu, tạo ra Hú Gió hút các mục tiêu xung quanh vào và Aero DMG Bonus của chúng lên {3} trong {4}s. Hiệu ứng này có thể kích hoạt {6} lần mỗi {5}s.</t>
+- Basic Attack được thay thế bằng Lưỡi Kiếm Lên Tiếng - Mực Tàu, và đòn tấn công Giai Đoạn {0} sẽ hồi phục thêm {1} điểm Độc Thoại Kiếm Khách.
+- Khi Heavy Attack hoặc Lưỡi Kiếm Lên Tiếng - Mực Tàu Giai Đoạn {2} trúng mục tiêu, tạo ra Hú Gió hút các mục tiêu xung quanh vào và Tăng Sát Thương Aero của chúng lên {3} trong {4}s. Hiệu ứng này có thể kích hoạt {6} lần mỗi {5}s.</t>
         </is>
       </c>
     </row>
@@ -10307,7 +10307,7 @@
       <c r="M148" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt;
-- Cooldown chiêu của Resonance Skill - Through the Groves giảm {0} giây và tổng Sát Thương tăng thêm {1}. Thi triển kỹ năng này sẽ tăng {2} Aero DMG trong {3} giây.
+- Thời gian hồi chiêu của Resonance Skill - Through the Groves giảm {0} giây và tổng Sát Thương tăng thêm {1}. Thi triển kỹ năng này sẽ tăng {2} Sát Thương Aero trong {3} giây.
 - Resonance Skill - Through the Groves sẽ tự động thi triển khi Qiuyuan bị tấn công, làm chậm kẻ địch xung quanh trong {4} giây và khôi phục {5} điểm Swordster's Soliloquy.</t>
         </is>
       </c>
@@ -10375,7 +10375,7 @@
       <c r="M149" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Resonance Liberation]&lt;/color&gt;
-Tổng sát thương của Resonance Liberation - Đòn Phá Hủy tăng thêm {0} và Cooldown chiêu giảm {1} giây.</t>
+Tổng DMG của Resonance Liberation - Đòn Phá Hủy tăng thêm {0} và Thời gian hồi chiêu giảm {1} giây.</t>
         </is>
       </c>
     </row>
@@ -10442,7 +10442,7 @@
       <c r="M150" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt;
-Mỗi {0} lần đánh sẽ kích hoạt Số Phận Tan Nát, gây Havoc DMG bằng {1} Tấn Công của Chisa (được tính là Sát Thương Resonance Liberation) và gây hiệu ứng Havoc Bane. Hiệu ứng này có thể kích hoạt tối đa &lt;SapTag=2&gt;{2}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=2} mỗi giây.</t>
+Mỗi {0} lần đánh sẽ kích hoạt Số Phận Tan Nát, gây Sát Thương Havoc bằng {1} ATK của Chisa (được tính là Sát Thương Resonance Liberation) và gây hiệu ứng Havoc Bane. Hiệu ứng này có thể kích hoạt tối đa &lt;SapTag=2&gt;{2}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=2} mỗi giây.</t>
         </is>
       </c>
     </row>
@@ -10509,7 +10509,7 @@
       <c r="M151" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Basic Attack]&lt;/color&gt;
-Nhận tăng {4} Crit. Rate trong {5} giây khi &lt;color=#c49e55&gt;Basic Attack&lt;/color&gt; trúng mục tiêu bị ảnh hưởng bởi Havoc Bane. Total sát thương của Basic Attack - Cú Bắn Tử Thần tăng thêm {0}. Thi triển chiêu này sẽ hồi phục {1} Resonance Energy, kích hoạt &lt;SapTag=3&gt;{3}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=3} mỗi {2} giây.</t>
+Nhận tăng {4} Crit. Rate trong {5} giây khi &lt;color=#c49e55&gt;Basic Attack&lt;/color&gt; trúng mục tiêu bị ảnh hưởng bởi Havoc Bane. Tổng DMG của Basic Attack - Cú Bắn Tử Thần tăng thêm {0}. Thi triển chiêu này sẽ hồi phục {1} Resonance Energy, kích hoạt &lt;SapTag=3&gt;{3}&lt;/SapTag&gt; {Cus:Sap,S=lần P=lần SapTag=3} mỗi {2} giây.</t>
         </is>
       </c>
     </row>
@@ -10576,7 +10576,7 @@
       <c r="M152" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt;
-Khi ở Chế Độ Chainsaw và sau khi sử dụng Chainsaw - Diệt Trừ, {Cus:Ipt,Touch=tap PC=press Gamepad=press} Normal Attack trong thời gian ngắn để thi triển Chainsaw - Trừng Phạt, gây Havoc DMG bằng {0} Attack của Chisa (được tính là Sát Thương Resonance Liberation) và phục hồi {1} điểm Resonance Energy.</t>
+Khi ở Chế Độ Cưa Xích và sau khi sử dụng Cưa Xích - Diệt Trừ, {Cus:Ipt,Touch=tap PC=press Gamepad=press} Đòn Thường trong thời gian ngắn để thi triển Cưa Xích - Trừng Phạt, gây Sát Thương Havoc bằng {0} ATK của Chisa (được tính là Sát Thương Resonance Liberation) và phục hồi {1} điểm Resonance Energy.</t>
         </is>
       </c>
     </row>
@@ -10645,9 +10645,9 @@
       <c r="M153" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt;
-- Cooldown chiêu của Resonance Skill - Eye of Unraveling giảm {0} giây.
+- Thời gian hồi chiêu của Resonance Skill - Eye of Unraveling giảm {0} giây.
 - Thi triển Resonance Skill - Eye of Unraveling sẽ khôi phục {1} điểm Resonance Energy và nhận {4} điểm Ring of Chainsaw.
-- Thi triển Resonance Skill - Serrated Loop sẽ tăng {2} Havoc DMG trong {3} giây.</t>
+- Thi triển Resonance Skill - Serrated Loop sẽ tăng {2} Sát Thương Havoc trong {3} giây.</t>
         </is>
       </c>
     </row>
@@ -10714,7 +10714,7 @@
       <c r="M154" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Resonance Liberation]&lt;/color&gt;
-Tổng sát thương của Resonance Liberation - Khoảnh Khắc Hư Vô tăng thêm {0} và Cooldown chiêu giảm {1} giây.</t>
+Tổng DMG của Resonance Liberation - Khoảnh Khắc Hư Vô tăng thêm {0} và Thời gian hồi chiêu giảm {1} giây.</t>
         </is>
       </c>
     </row>
@@ -10781,9 +10781,9 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Heavy Attack]&lt;/color&gt;
-- Giữ Basic Attack hoặc {Cus:Ipt,Touch=tap PC=press Gamepad=press} trong không trung để sử dụng Đòn Trọng - Sấm Gầm: Attack Thượng Đoạn, tiêu hao Năng Lực và nhận hiệu ứng tăng cường.
-- Giữ Basic Attack sau khi sử dụng Basic Attack Stage 2 để sử dụng Đòn Trọng - Sấm Gầm: Lùi Bước, tiêu hao Năng Lực.</t>
+          <t>&lt;color=#c49e55&gt;[Đòn Trọng]&lt;/color&gt;
+- Giữ Đòn Cơ Bản hoặc {Cus: Ipt,Touch=tap PC=press Gamepad=press} it in mid-air to cast Heavy Attack - Thunderoar: Uppercut at the cost of Prowess and gain enhancements.
+- Hold Basic Attack after casting Basic Attack Stage 2 to cast Heavy Attack - Thunderoar: Backstep at the cost of Prowess.</t>
         </is>
       </c>
     </row>
@@ -10922,8 +10922,8 @@
       <c r="M157" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Resonance Liberation]&lt;/color&gt;
-- Tổng sát thương của Resonance Liberation được tăng lên.
-- Cooldown chiêu của Resonance Liberation - Kiếm Lời Thề Vĩnh Cửu được giảm. Sử dụng kỹ năng này sẽ phục hồi toàn bộ Năng Lượng Thăng Hoa.</t>
+- Tổng DMG của Resonance Liberation được tăng lên.
+- Thời gian hồi chiêu của Resonance Liberation - Kiếm Lời Thề Vĩnh Cửu được giảm. Sử dụng kỹ năng này sẽ phục hồi toàn bộ Năng Lượng Thăng Hoa.</t>
         </is>
       </c>
     </row>
@@ -10990,7 +10990,7 @@
       <c r="M158" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Resonance Skill]&lt;/color&gt;
-Electro DMG tăng lên. Khi Năng Lượng Thăng Hoa đầy, {Cus:Ipt,Touch=tap PC=press Gamepad=press} Normal Attack trên không để tiêu hao toàn bộ Năng Lượng Thăng Hoa và thi triển Resonance Skill - Ánh Dương Bất Tử: Lao Xuống.</t>
+DMG Electro tăng lên. Khi Năng Lượng Thăng Hoa đầy, {Cus: Ipt,Touch=tap PC=press Gamepad=press} Normal Attack in mid-air to consume all Ascendancy and cast Resonance Skill - Undying Sunlight: Plunge.</t>
         </is>
       </c>
     </row>
@@ -11057,7 +11057,7 @@
       <c r="M159" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt;
-Mỗi lần nhận Shield sẽ tăng Sát Thương Heavy Attack và tăng Giảm Sát Thương Nhận Vào.</t>
+Mỗi lần nhận Khiên sẽ tăng Sát Thương Heavy Attack và tăng Giảm Sát Thương Nhận Vào.</t>
         </is>
       </c>
     </row>
@@ -11193,7 +11193,7 @@
       <c r="M161" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Resonance Liberation]&lt;/color&gt;
-Resonance Liberation có Cooldown chiêu ngắn hơn và giờ đây có thể bắn thêm Mũi Tên Minh Triết.</t>
+Resonance Liberation có Thời gian hồi chiêu ngắn hơn và giờ đây có thể bắn thêm Mũi Tên Minh Triết.</t>
         </is>
       </c>
     </row>
@@ -11329,7 +11329,7 @@
       <c r="M163" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt;
-Trong Lãnh Địa Full Moon, Crit. DMG của tất cả Resonators trong đội được tăng cường, và họ định kỳ nhận được Shield.</t>
+Trong Lãnh Địa Trăng Tròn, Crit. DMG của tất cả Resonator trong đội được tăng cường, và họ định kỳ nhận được Khiên.</t>
         </is>
       </c>
     </row>
@@ -11397,8 +11397,8 @@
       <c r="M164" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt;
-- Iuno liên tục nhận Blessing Light Vô Tận.
-- Heavy Attack - Thăng Giáng được tăng cường.</t>
+- Iuno liên tục nhận Phước Lành Ánh Sáng Vô Tận.
+- Đòn Heavy Attack - Thăng Giáng được tăng cường.</t>
         </is>
       </c>
     </row>
@@ -11534,7 +11534,7 @@
         <is>
           <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt;
 - Hellstride được tăng cường.
-- Khi ở Threshold State, sử dụng Basic Attack sau khi thi triển Hellstride sẽ khôi phục Sinflame.</t>
+- Khi ở Trạng Thái Ngưỡng, sử dụng Đòn Basic Attack sau khi thi triển Hellstride sẽ khôi phục Sinflame.</t>
         </is>
       </c>
     </row>
@@ -11600,7 +11600,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>&lt;color=#c49e55&gt;[Mid-air Attack]&lt;/color&gt;
+          <t>&lt;color=#c49e55&gt;[Đòn Tấn Công Giữa Không]&lt;/color&gt;
 Resonance Skill - Demon Arisen được tăng cường đặc biệt.</t>
         </is>
       </c>
@@ -11738,7 +11738,7 @@
       <c r="M169" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Resonance Liberation]&lt;/color&gt;
-- Cooldown chiêu của Resonance Liberation được rút ngắn.
+- Thời gian hồi chiêu của Resonance Liberation được rút ngắn.
 - Sử dụng Resonance Liberation sẽ hồi phục thêm Ngọn Lửa Dư và tăng Sát Thương gây ra.</t>
         </is>
       </c>
@@ -11874,8 +11874,8 @@
       <c r="M171" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt;
-- Tỷ Lệ Critical Hit được tăng. Phần Tỷ Lệ Critical Hit vượt quá giá trị nhất định sẽ được chuyển hóa thành Tấn Công.
-- Hit Critical Hit sẽ tạo ra Zephyr Slash gây Aero DMG.</t>
+- Crit. Rate được tăng. Phần Crit. Rate vượt quá giá trị nhất định sẽ được chuyển hóa thành ATK.
+- Đòn đánh Bạo Kích sẽ tạo ra Zephyr Slash gây Sát Thương Aero.</t>
         </is>
       </c>
     </row>
@@ -11944,7 +11944,7 @@
         <is>
           <t>&lt;color=#c49e55&gt;[Basic Attack]&lt;/color&gt;
 - Basic Attack được tăng cường.
-- Heavy Attack hoặc Basic Attack Stage 3 tạo ra Hú Gió.</t>
+- Đòn Heavy Attack hoặc Basic Attack Giai Đoạn 3 tạo ra Hú Gió.</t>
         </is>
       </c>
     </row>
@@ -12080,7 +12080,7 @@
       <c r="M174" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Resonance Liberation]&lt;/color&gt;
-Resonance Liberation - Đòn Phá Hủy có tổng sát thương cao hơn và Cooldown chiêu ngắn hơn.</t>
+Resonance Liberation - Đòn Phá Hủy có tổng DMG cao hơn và Thời gian hồi chiêu ngắn hơn.</t>
         </is>
       </c>
     </row>
@@ -12147,7 +12147,7 @@
       <c r="M175" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt;
-Khi tấn công kẻ địch đủ số lần nhất định sẽ kích hoạt Số Phận Tan Nát, gây Havoc DMG và áp dụng hiệu ứng Havoc Bane.</t>
+Khi tấn công kẻ địch đủ số lần nhất định sẽ kích hoạt Số Phận Tan Nát, gây DMG Havoc và áp dụng hiệu ứng Havoc Bane.</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       <c r="M176" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Basic Attack]&lt;/color&gt;
-Nhận tăng Crit. Rate khi Basic Attack trúng mục tiêu bị ảnh hưởng bởi Havoc Bane. Tổng sát thương của Basic Attack - Cú Bắn Tử Thần được tăng lên. Thi triển chiêu này sẽ hồi phục Resonance Energy.</t>
+Nhận tăng Crit. Rate khi Basic Attack trúng mục tiêu bị ảnh hưởng bởi Havoc Bane. Tổng DMG của Basic Attack - Cú Bắn Tử Thần được tăng lên. Thi triển chiêu này sẽ hồi phục Resonance Energy.</t>
         </is>
       </c>
     </row>
@@ -12281,7 +12281,7 @@
       <c r="M177" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt;
-Khi ở Chế Độ Chainsaw và sau khi sử dụng Chainsaw - Diệt Trừ, {Cus:Ipt,Touch=tap PC=press Gamepad=press} Normal Attack trong thời gian ngắn để thi triển Chainsaw - Trừng Phạt.</t>
+Khi ở Chế Độ Cưa Xích và sau khi sử dụng Cưa Xích - Diệt Trừ, {Cus:Ipt,Touch=tap PC=press Gamepad=press} Đòn Thường trong thời gian ngắn để thi triển Cưa Xích - Trừng Phạt.</t>
         </is>
       </c>
     </row>
@@ -12350,9 +12350,9 @@
       <c r="M178" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt;
-- Cooldown chiêu của Resonance Skill - Eye of Unraveling được giảm.
+- Thời gian hồi chiêu của Resonance Skill - Eye of Unraveling được giảm.
 - Kích hoạt Resonance Skill - Eye of Unraveling sẽ phục hồi Resonance Energy và tạo ra Ring of Chainsaw.
-- Kích hoạt Resonance Skill - Serrated Loop sẽ tăng Havoc DMG.</t>
+- Kích hoạt Resonance Skill - Serrated Loop sẽ tăng Sát Thương Havoc.</t>
         </is>
       </c>
     </row>
@@ -12419,7 +12419,7 @@
       <c r="M179" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Resonance Liberation]&lt;/color&gt;
-Tổng sát thương của Resonance Liberation - Khoảnh Khắc Hư Vô được tăng lên và Cooldown chiêu giảm đi.</t>
+Tổng DMG của Resonance Liberation - Khoảnh Khắc Hư Vô được tăng lên và Thời gian hồi chiêu giảm đi.</t>
         </is>
       </c>
     </row>
@@ -12487,7 +12487,7 @@
       <c r="M180" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt;
-- Hồi chiêu của Forte Circuit - Learn My True Name giảm còn {0} giây. {Cus:Ipt,Touch=tap PC=press Gamepad=press} nút Normal Attack trên mặt đất để thực hiện Giai Đoạn Basic Attack 3.
+- Thời gian hồi của Forte Circuit - Learn My True Name giảm còn {0} giây. {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} nút Normal Attack trên mặt đất để thực hiện Giai Đoạn Basic Attack 3.
 - Nhận trạng thái Concurrent. Nhận được một Rune sẽ nhận thêm một Rune cùng loại. Khi Sigrika có Concurrent, cả Divergent và Convergent đều không có hiệu lực. Dùng Kỹ Năng Echo sẽ nhận được {1} điểm Soliskin Vitality.</t>
         </is>
       </c>
@@ -12556,8 +12556,8 @@
       <c r="M181" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Normal Attack]&lt;/color&gt;
-- Giảm {0} tiêu hao STA của Đòn Lao Xuống và Dodge Phản Công Giữa Không.
-- Đánh trúng mục tiêu bằng Đòn Lao Xuống Giữa Không hoặc Dodge Phản Công Giữa Không sẽ tạo thêm một Runic Soliskin.</t>
+- Giảm {0} tiêu hao STA của Tấn Công Lao Xuống và Né Tránh Phản Công Giữa Không.
+- Đánh trúng mục tiêu bằng Tấn Công Lao Xuống Giữa Không hoặc Né Tránh Phản Công Giữa Không sẽ tạo thêm một Runic Soliskin.</t>
         </is>
       </c>
     </row>
@@ -12624,7 +12624,7 @@
       <c r="M182" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Normal Attack]&lt;/color&gt;
-Stage 3 của Basic Attack giờ có thể duy trì lâu hơn trên không. Di chuyển trên không trong Stage 3 của Basic Attack sẽ kích hoạt thêm một Runic Outburst.</t>
+Giai Đoạn 3 của Basic Attack giờ có thể duy trì lâu hơn trên không. Di chuyển trên không trong Giai Đoạn 3 của Basic Attack sẽ kích hoạt thêm một Runic Outburst.</t>
         </is>
       </c>
     </row>
@@ -12693,7 +12693,7 @@
         <is>
           <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt;
 - Khi kích hoạt Schemata of Runes, Runic Soliskin, Runic Chain Whip và Runic Outburst sẽ được tạo ra theo thứ tự.
-- Sát thương của Runic Soliskin, Runic Chain Whip và Runic Outburst được Khuếch Đại thêm {0}.</t>
+- DMG của Runic Soliskin, Runic Chain Whip và Runic Outburst được Khuếch Đại thêm {0}.</t>
         </is>
       </c>
     </row>
@@ -12761,8 +12761,8 @@
       <c r="M184" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Resonance Liberation]&lt;/color&gt;
-- Kích hoạt Resonance Liberation sẽ đưa Sigrika vào trạng thái Giải Mã trong {0} giây. Nếu Giải Mã được kích hoạt theo cách này, sử dụng Basic Attack - Giải Thích, Dodge Phản Công - Giải Mã, Resonance Skill - Big Boomy Boom hoặc Resonance Skill - Soliskin to the Aid sẽ không kết thúc Giải Mã.
-- Kích hoạt Forte Circuit - Learn My True Name sẽ đặt lại Cooldown chiêu Resonance Liberation và phục hồi toàn bộ Resonance Energy.</t>
+- Kích hoạt Resonance Liberation sẽ đưa Sigrika vào trạng thái Giải Mã trong {0} giây. Nếu Giải Mã được kích hoạt theo cách này, sử dụng Basic Attack - Giải Thích, Né Tránh Phản Công - Giải Mã, Resonance Skill - Big Boomy Boom hoặc Resonance Skill - Soliskin to the Aid sẽ không kết thúc Giải Mã.
+- Kích hoạt Forte Circuit - Learn My True Name sẽ đặt lại Thời gian hồi chiêu Resonance Liberation và phục hồi toàn bộ Resonance Energy.</t>
         </is>
       </c>
     </row>
@@ -12830,7 +12830,7 @@
       <c r="M185" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Forte Circuit]&lt;/color&gt;
-- Hồi chiêu của Forte Circuit - Learn My True Name giảm còn {0} giây.
+- Thời gian hồi của Forte Circuit - Learn My True Name giảm còn {0} giây.
 - Nhận được một Rune sẽ nhận thêm một Rune cùng loại. Dùng Kỹ Năng Echo sẽ hồi đầy Soliskin Vitality.</t>
         </is>
       </c>
@@ -12899,8 +12899,8 @@
       <c r="M186" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Normal Attack]&lt;/color&gt;
-- Giảm tiêu hao STA của Đòn Lao Xuống.
-- Thực hiện Đòn Lao Xuống sẽ kích hoạt hiệu ứng đặc biệt.</t>
+- Giảm tiêu hao STA của Tấn Công Lao Xuống.
+- Thực hiện Tấn Công Lao Xuống sẽ kích hoạt hiệu ứng đặc biệt.</t>
         </is>
       </c>
     </row>
@@ -12967,7 +12967,7 @@
       <c r="M187" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Normal Attack]&lt;/color&gt;
-Di chuyển trên không trong Stage 3 của Basic Attack sẽ kích hoạt thêm một Runic Outburst.</t>
+Di chuyển trên không trong Giai Đoạn 3 của Basic Attack sẽ kích hoạt thêm một Runic Outburst.</t>
         </is>
       </c>
     </row>
@@ -13169,8 +13169,8 @@
       <c r="M190" t="inlineStr">
         <is>
           <t>&lt;color=#c49e55&gt;[Resonance Liberation]&lt;/color&gt;
-- Tổng sát thương của Resonance Liberation - Kiếm Lời Thề Vĩnh Cửu, Sublime is the Sun - Sunborne và Sublime is the Sun - Everbright Protector được tăng thêm {0}.
-- Cooldown chiêu của Resonance Liberation - Kiếm Lời Thề Vĩnh Cửu giảm {1} giây. Sử dụng Resonance Liberation này sẽ phục hồi {2} điểm Năng Lượng Thăng Hoa.</t>
+- Tổng DMG của Resonance Liberation - Kiếm Lời Thề Vĩnh Cửu, Sublime is the Sun - Sunborne và Sublime is the Sun - Everbright Protector được tăng thêm {0}.
+- Thời gian hồi chiêu của Resonance Liberation - Kiếm Lời Thề Vĩnh Cửu giảm {1} giây. Sử dụng Resonance Liberation này sẽ phục hồi {2} điểm Năng Lượng Thăng Hoa.</t>
         </is>
       </c>
     </row>
@@ -13407,8 +13407,8 @@
       <c r="M193" t="inlineStr">
         <is>
           <t>…
-Sau buổi diện kiến với Solsworn, các giả thuyết của Viện Nghiên Cứu đã được xác nhận. Trong đó, thông tin liên quan đến ▇▇ đã thu hút sự chú ý của các nhà nghiên cứu từ Huanglong. Một nhóm học giả sau đó bắt đầu nghiên cứu về khả năng tái sinh của ▇▇. Đáng tiếc, hệ thống ▇▇▇ vẫn là một chiều không gian nằm ngoài tầm hiểu biết và khả năng tiếp cận hiện tại của chúng ta.
-Không lâu sau, hướng nghiên cứu này bị đình chỉ. Mục tiêu chính của chúng ta vẫn là phát triển một phương pháp Resonance Tăng Cường ổn định, đảm bảo Exostrider có thể kích hoạt khi ▇▇ đến.
+Sau buổi diện kiến với Solsworn, các giả thuyết của Viện Nghiên cứu đã được xác nhận. Trong đó, thông tin liên quan đến ▇▇ đã thu hút sự chú ý của các nhà nghiên cứu từ Huanglong. Một nhóm học giả sau đó bắt đầu nghiên cứu về khả năng tái sinh của ▇▇. Đáng tiếc, hệ thống ▇▇▇ vẫn là một chiều không gian nằm ngoài tầm hiểu biết và khả năng tiếp cận hiện tại của chúng ta.
+Không lâu sau, hướng nghiên cứu này bị đình chỉ. Mục tiêu chính của chúng ta vẫn là phát triển một phương pháp Cộng Hưởng Tăng Cường ổn định, đảm bảo Exostrider có thể kích hoạt khi ▇▇ đến.
 …
 Hơn nữa, lữ khách từng được nhắc đến trong cuộc thảo luận đã mất tích kể từ đó. Những nỗ lực xác định danh tính của người này cuối cùng cũng bị từ bỏ.
 Với sự thành lập của Spacetrek Collective, những thách thức chúng ta phải đối mặt không còn giới hạn trong học thuật nữa. Nhiều tổ chức đang tìm cách xâm nhập hoặc thậm chí phá hoại công việc của chúng ta. Nền văn minh đang phủ bóng đen theo nhiều cách hơn cả Threnodian. Trước cuộc khủng hoảng hiện tại, chúng ta buộc phải bỏ ngỏ một số bí ẩn nhỏ.</t>
@@ -13541,7 +13541,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>Khôi phục tất cả Cây Già Voidbane tại Dimmr Plains.</t>
+          <t>Khôi phục tất cả Cây Già Voidbane tại Đồng Bằng Dimmr.</t>
         </is>
       </c>
     </row>
@@ -13677,11 +13677,11 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>["Hồ sơ do &lt;te href=851071&gt;Spacetrek Collective&lt;/te&gt; lưu trữ: Hồ sơ học viên &lt;te href=851069&gt;Startorch Academy&lt;/te&gt;]
-[Report Khảo sát Forte: RA2326-G]
-Name học viên: Sigrika
+          <t>["Hồ sơ do &lt;te href=851071&gt;Tập Đoàn Spacetrek&lt;/te&gt; lưu trữ: Hồ sơ học viên &lt;te href=851069&gt;Học viện Startorch&lt;/te&gt;]
+[Báo cáo Khảo sát Forte: RA2326-G]
+Tên học viên: Sigrika
 Kết quả Đồng Bộ Hóa: Âm tính
-Overview Forte: Kiểm tra cho thấy &lt;te href=850067&gt;Đường cong Rabelle&lt;/te&gt; có dạng sóng tuần hoàn rõ rệt. Do đó, học viên được xếp loại là &lt;te href=850068&gt;Resonator Bẩm Sinh&lt;/te&gt;. &lt;te href=850072&gt;Tacet Mark&lt;/te&gt; của cô nằm ở lưng.
+Tổng quan Forte: Kiểm tra cho thấy &lt;te href=850067&gt;Đường cong Rabelle&lt;/te&gt; có dạng sóng tuần hoàn rõ rệt. Do đó, học viên được xếp loại là &lt;te href=850068&gt;Resonator Bẩm Sinh&lt;/te&gt;. &lt;te href=850072&gt;Dấu Tacet&lt;/te&gt; của cô nằm ở lưng.
 Theo hồ sơ cá nhân trước nhập học và lời khai của học viên, cô thể hiện năng khiếu đặc biệt trong việc giải mã tần số ký tự và chuyển hóa chúng thành năng lượng sử dụng được. Tuy nhiên, cô cho biết khả năng này vẫn chưa ổn định và phụ thuộc nhiều vào trạng thái tinh thần cũng như mức độ hiểu biết về các ký tự cụ thể.
 &lt;i&gt;“Trong lĩnh vực giải mã ký tự, Sigrika sở hữu tài năng hiếm có, nhưng cũng tiềm ẩn nguy cơ đáng kể nếu không được kiểm soát cẩn thận.”&lt;/i&gt;</t>
         </is>
@@ -13749,7 +13749,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>Giảm đáng kể Năng Lượng và Speed trong thời gian ngắn.
+          <t>Giảm đáng kể Năng Lượng và Tốc Độ trong thời gian ngắn.
 Món ăn đặc trưng của Royan với hàm lượng protein cao, calo thấp mà ít ai dám thưởng thức. Mùi tanh nồng nặc từ lọ cá nứt khiến ai cũng phải tránh xa.</t>
         </is>
       </c>
@@ -13816,7 +13816,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>Hồi phục Năng Lượng cực mạnh và tạo ra lượng lớn Gourmet Points.
+          <t>Hồi phục Năng Lượng cực mạnh và tạo ra lượng lớn Điểm Ẩm Thực.
 Món ăn giàu dinh dưỡng cho những ai không thích ngọt. Hương vị đậm đà, dễ ăn.</t>
         </is>
       </c>
@@ -13884,7 +13884,7 @@
       <c r="M200" t="inlineStr">
         <is>
           <t>Một bậc thầy ẩm thực, chấm điểm với độ chính xác như dao mổ.
-Kỹ năng của anh tạm thời làm giảm Speed nhưng lại tăng mạnh việc tạo ra Điểm Ẩm Thực.</t>
+Kỹ năng của anh tạm thời làm giảm Tốc Độ nhưng lại tăng mạnh việc tạo ra Điểm Ẩm Thực.</t>
         </is>
       </c>
     </row>
@@ -13951,7 +13951,7 @@
       <c r="M201" t="inlineStr">
         <is>
           <t>Chuyên gia sử dụng năng lượng với hiệu suất đỉnh cao.
-Kỹ năng của cô tăng nhẹ Speed và Tạo Điểm Ẩm Thực trong thời gian khá dài.</t>
+Kỹ năng của cô tăng nhẹ Tốc Độ và Tạo Điểm Ẩm Thực trong thời gian khá dài.</t>
         </is>
       </c>
     </row>
@@ -14217,7 +14217,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>Giảm Cooldown chiêu của Bước Nhảy Tích Năng thứ 2 và thứ 3 sau khi hạ cánh.</t>
+          <t>Giảm thời gian hồi chiêu của Bước Nhảy Tích Năng thứ 2 và thứ 3 sau khi hạ cánh.</t>
         </is>
       </c>
     </row>
@@ -14282,7 +14282,7 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>Vung xe và đâm mạnh vào các mục tiêu gần đó, gây Sát Thương Physical bằng 200% Tấn Công, sau đó nhảy khỏi xe, gây Sát Thương Physical bằng 1500% Tấn Công lên các mục tiêu trong phạm vi và tăng nhẹ Mức Độ Mistune của chúng. Hồi chiêu: 10 giây.</t>
+          <t>Vung xe và đâm mạnh vào các mục tiêu gần đó, gây Sát Thương Vật Lý bằng 200% ATK, sau đó nhảy khỏi xe, gây Sát Thương Vật Lý bằng 1500% ATK lên các mục tiêu trong phạm vi và tăng nhẹ Mức Độ Lệch Tần của chúng. Hồi chiêu: 10 giây.</t>
         </is>
       </c>
     </row>
@@ -14347,7 +14347,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>Vung xe và đâm mạnh vào các mục tiêu gần đó, gây Sát Thương Physical bằng 300% Tấn Công, sau đó nhảy khỏi xe, gây Sát Thương Physical bằng 2000% Tấn Công lên các mục tiêu trong phạm vi và tăng nhẹ Mức Độ Mistune của chúng. Hồi chiêu: 10 giây.</t>
+          <t>Vung xe và đâm mạnh vào các mục tiêu gần đó, gây Sát Thương Vật Lý bằng 300% ATK, sau đó nhảy khỏi xe, gây Sát Thương Vật Lý bằng 2000% ATK lên các mục tiêu trong phạm vi và tăng nhẹ Mức Độ Lệch Tần của chúng. Hồi chiêu: 10 giây.</t>
         </is>
       </c>
     </row>
@@ -14412,7 +14412,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>Vung xe và đâm mạnh vào các mục tiêu gần đó, gây Sát Thương Physical bằng 400% Tấn Công, sau đó nhảy khỏi xe, gây Sát Thương Physical bằng 2400% Tấn Công lên các mục tiêu trong phạm vi và tăng nhẹ Mức Độ Mistune của chúng. Hồi chiêu: 10 giây.</t>
+          <t>Vung xe và đâm mạnh vào các mục tiêu gần đó, gây Sát Thương Vật Lý bằng 400% ATK, sau đó nhảy khỏi xe, gây Sát Thương Vật Lý bằng 2400% ATK lên các mục tiêu trong phạm vi và tăng nhẹ Mức Độ Lệch Tần của chúng. Hồi chiêu: 10 giây.</t>
         </is>
       </c>
     </row>
@@ -14477,7 +14477,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>Khi bị ảnh hưởng bởi Void Storm, Resonators trong đội sẽ hồi 5% HP mỗi khi tiêu diệt mục tiêu.</t>
+          <t>Khi bị ảnh hưởng bởi Bão Hư Không, các Resonator trong đội sẽ hồi 5% HP mỗi khi tiêu diệt mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -14542,7 +14542,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>Khi chịu ảnh hưởng của Void Storm, Resonators trong đội sẽ hồi 5% HP khi tiêu diệt mục tiêu. Resonators trong đội sẽ chịu ít hơn 20% sát thương khi HP dưới 30%.</t>
+          <t>Khi chịu ảnh hưởng của Bão Hư Không, Resonator trong đội sẽ hồi 5% HP khi tiêu diệt mục tiêu. Resonator trong đội sẽ chịu ít hơn 20% DMG khi HP dưới 30%.</t>
         </is>
       </c>
     </row>
@@ -14607,7 +14607,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>Khi chịu ảnh hưởng của Void Storm, Resonators trong đội sẽ hồi 20 điểm Resonance Energy khi tiêu diệt mục tiêu.</t>
+          <t>Khi chịu ảnh hưởng của Bão Hư Không, Resonator trong đội sẽ hồi 20 điểm Resonance Energy khi tiêu diệt mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -14672,7 +14672,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>Khi chịu ảnh hưởng của Void Storm, Resonators trong đội sẽ hồi 20 điểm Resonance Energy khi tiêu diệt mục tiêu và nhận 10% DMG Amplification Toàn Bộ Sau Khi Thi Triển Resonance Liberation. Hiệu ứng này có thể chồng chất tối đa 4 lần và kéo dài 120 giây. Thời gian hiệu ứng sẽ được làm mới khi kích hoạt lại.</t>
+          <t>Khi chịu ảnh hưởng của Bão Hư Không, Resonator trong đội sẽ hồi 20 điểm Resonance Energy khi tiêu diệt mục tiêu và nhận 10% Khuếch Đại Sát Thương Toàn Bộ Sau Khi Thi Triển Resonance Liberation. Hiệu ứng này có thể chồng chất tối đa 4 lần và kéo dài 120 giây. Thời gian hiệu ứng sẽ được làm mới khi kích hoạt lại.</t>
         </is>
       </c>
     </row>
@@ -14737,7 +14737,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>Sau khi sử dụng Steelwing Comet, Resonators trong đội sẽ nhận thêm 20% Tăng Sát Thương Toàn Bộ Thuộc Tính trong 120 giây.</t>
+          <t>Sau khi sử dụng Steelwing Comet, các Resonator trong đội sẽ nhận thêm 20% Tăng Sát Thương Toàn Bộ Thuộc Tính trong 120 giây.</t>
         </is>
       </c>
     </row>
@@ -14802,7 +14802,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>Resonators trong đội tăng 15% Hồi Phục Năng Lượng.</t>
+          <t>Resonator trong đội tăng 15% Hồi Phục Năng Lượng.</t>
         </is>
       </c>
     </row>
@@ -14867,7 +14867,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>Resonators trong đội tăng 30% Hồi Phục Năng Lượng.</t>
+          <t>Resonator trong đội tăng 30% Hồi Phục Năng Lượng.</t>
         </is>
       </c>
     </row>
@@ -14932,7 +14932,7 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>Sau khi sử dụng Steelwing Comet, Resonators trong đội sẽ nhận thêm 20% Tăng Sát Thương Toàn Bộ Thuộc Tính đối với mục tiêu cấp Thảm Họa trong 120 giây.</t>
+          <t>Sau khi sử dụng Steelwing Comet, các Resonator trong đội sẽ nhận thêm 20% Tăng Sát Thương Toàn Bộ Thuộc Tính đối với mục tiêu cấp Thảm Họa trong 120 giây.</t>
         </is>
       </c>
     </row>
@@ -15062,7 +15062,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>Khi bị ảnh hưởng bởi Void Storm, Resonator đang hoạt động sẽ hồi HP mỗi khi tiêu diệt mục tiêu.</t>
+          <t>Khi bị ảnh hưởng bởi Bão Hư Không, Resonator đang hoạt động sẽ hồi HP mỗi khi tiêu diệt mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -15127,7 +15127,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>Khi chịu ảnh hưởng của Void Storm, hồi Resonance Energy khi tiêu diệt mục tiêu.</t>
+          <t>Khi chịu ảnh hưởng của Bão Hư Không, hồi Resonance Energy khi tiêu diệt mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -15257,7 +15257,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>Resonators trong đội tăng Hồi Phục Năng Lượng.</t>
+          <t>Resonator trong đội tăng Hồi Phục Năng Lượng.</t>
         </is>
       </c>
     </row>
@@ -15389,7 +15389,7 @@
       <c r="M223" t="inlineStr">
         <is>
           <t>Hiệu ứng Nâng cấp:
-Vung xe và đập mạnh vào các mục tiêu gần đó, gây Sát Thương Physical bằng 200% Tấn Công, sau đó xuống xe và gây Sát Thương Physical bằng 1500% Tấn Công lên các mục tiêu trong phạm vi, đồng thời tăng nhẹ Mức Độ Mistune của mục tiêu. Cooldown chiêu: 10 giây.</t>
+Vung xe và đập mạnh vào các mục tiêu gần đó, gây Sát Thương Vật Lý bằng 200% ATK, sau đó xuống xe và gây Sát Thương Vật Lý bằng 1500% ATK lên các mục tiêu trong phạm vi, đồng thời tăng nhẹ Mức Độ Lệch Tần của mục tiêu. Thời gian hồi chiêu: 10 giây.</t>
         </is>
       </c>
     </row>
@@ -15456,7 +15456,7 @@
       <c r="M224" t="inlineStr">
         <is>
           <t>Hiệu ứng nâng cấp:
-Khi chịu ảnh hưởng của Void Storm, Resonators trong đội phục hồi 5% HP khi đánh bại mục tiêu.</t>
+Khi chịu ảnh hưởng của Bão Hư Không, Resonator trong đội phục hồi 5% HP khi đánh bại mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -15523,7 +15523,7 @@
       <c r="M225" t="inlineStr">
         <is>
           <t>Hiệu ứng nâng cấp:
-Khi chịu ảnh hưởng của Void Storm, Resonators trong đội phục hồi 20 điểm Resonance Energy khi đánh bại mục tiêu.</t>
+Khi chịu ảnh hưởng của Bão Hư Không, Resonator trong đội phục hồi 20 điểm Resonance Energy khi đánh bại mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -15657,7 +15657,7 @@
       <c r="M227" t="inlineStr">
         <is>
           <t>Hiệu ứng Nâng cấp:
-Resonators trong đội nhận thêm 15% Tăng Tái Tạo Năng Lượng.</t>
+Resonator trong đội nhận thêm 15% Tăng Tái Tạo Năng Lượng.</t>
         </is>
       </c>
     </row>
@@ -15724,7 +15724,7 @@
       <c r="M228" t="inlineStr">
         <is>
           <t>Hiệu ứng nâng cấp:
-Sau khi sử dụng Steelwing Comet, Resonators trong đội nhận thêm 20% Tăng Sát Thương Toàn Thuộc Tính đối với mục tiêu Loại Calamity trong 120 giây.</t>
+Sau khi sử dụng Steelwing Comet, Resonator trong đội nhận thêm 20% Tăng Sát Thương Toàn Thuộc Tính đối với mục tiêu Loại Tai Họa trong 120 giây.</t>
         </is>
       </c>
     </row>
@@ -15919,7 +15919,7 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>Echo Skill DMG</t>
+          <t>Sát Thương Kỹ Năng Âm Hưởng</t>
         </is>
       </c>
     </row>
@@ -16126,7 +16126,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>[&lt;te href=851071&gt;Spacetrek Collective&lt;/te&gt;: Archive Mật]
+          <t>[&lt;te href=851071&gt;Tập Đoàn Spacetrek&lt;/te&gt;: Lưu Trữ Mật]
 Hồ sơ Phỏng vấn: Hiyuki
 Do nhiều yếu tố phức tạp, chúng tôi đã bỏ qua đánh giá toàn diện đối với đại diện đến từ &lt;te href=851074&gt;Ashinohara&lt;/te&gt;—Miko của Hoa Anh Đào Lửa.
 Phần lớn thông tin thu thập ở đây dựa trên lời khai cá nhân của cô. Theo đánh giá chuyên môn của người ghi chép, sau khi đối chiếu với các nguồn khác, cô dường như không có ý định che giấu bất kỳ thông tin nào về quá khứ của mình.
@@ -16211,14 +16211,14 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>[Hồ sơ do &lt;te href=851071&gt;Spacetrek Collective&lt;/te&gt; nộp: Hồ sơ học viên &lt;te href=851069&gt;Startorch Academy&lt;/te&gt;]
-[Report Test Forte: RA2499-G]
-Name học viên: Denia
+          <t>[Hồ sơ do &lt;te href=851071&gt;Spacetrek Collective&lt;/te&gt; nộp: Hồ sơ học viên &lt;te href=851069&gt;Học viện Startorch&lt;/te&gt;]
+[Báo cáo Kiểm tra Forte: RA2499-G]
+Tên học viên: Denia
 Kết quả kiểm tra &lt;te href=700009&gt;Synchronist&lt;/te&gt;: Âm tính
-Overview về Forte:Kết quả kiểm tra cho thấy dạng sóng &lt;te href=850067&gt;Rabelle's Curve&lt;/te&gt; có tính chu kỳ rõ rệt. Do đó, học viên này được xếp vào loại &lt;te href=850068&gt;Congenital Resonator&lt;/te&gt;. &lt;te href=850072&gt;Tacet Mark&lt;/te&gt; của cô nằm ở ngực.
+Tổng quan về Forte:Kết quả kiểm tra cho thấy dạng sóng &lt;te href=850067&gt;Rabelle's Curve&lt;/te&gt; có tính chu kỳ rõ rệt. Do đó, học viên này được xếp vào loại &lt;te href=850068&gt;Resonator Bẩm Sinh&lt;/te&gt;. &lt;te href=850072&gt;Dấu Tacet&lt;/te&gt; của cô nằm ở ngực.
 Theo hồ sơ từ người giới thiệu, đối tượng có thể tạo ra những bong bóng chứa Năng lượng Tàn Dư, có thể dùng để phòng thủ hoặc hỗ trợ trong chiến đấu. Năng lượng Tàn Dư trong bong bóng cũng có thể được kích nổ theo lệnh khi cần.
 Kết quả kiểm tra còn cho thấy cấu trúc chất lỏng đặc biệt của bong bóng cho phép chúng ngăn chặn Vật chất Hư Không ở cấp độ tương đương với lớp phủ Exostrider.
-&lt;i&gt;"Khoan, đó chẳng phải là cô bé thổi bong bóng trong mấy quảng cáo Lollo Logistics sao? Cháu gái tôi còn có đồ chơi giống y chang thế! Làm sao mà ngăn được Vật chất Hư Không bằng những quả bong bóng như thế được?"&lt;/i&gt;
+&lt;i&gt;"Đợi đã, đó chẳng phải là cô bé thổi bong bóng trong mấy quảng cáo Lollo Logistics sao? Cháu gái tôi còn có đồ chơi giống y chang thế! Làm sao mà ngăn được Vật chất Hư Không bằng những quả bong bóng như thế được?"&lt;/i&gt;
 &lt;i&gt;"Làm sao cái này lại lọt vào hồ sơ được nhỉ?! Trời ơi... Có gì trong báo cáo này là thật không vậy?"&lt;/i&gt;</t>
         </is>
       </c>
@@ -16394,7 +16394,7 @@
           <t>Người dân &lt;te href=851074&gt;Ashinohara&lt;/te&gt; từ lâu đã quen với những biến dạng do &lt;te href=850074&gt;Threnodian&lt;/te&gt; gây ra. Sống sót trở thành chuyện thường ngày: tìm chỗ trú ẩn, đợi miko địa phương triển khai, và nếu tình hình vượt tầm kiểm soát, thì đợi đội cứu hộ cùng Miko Hoa Anh Đào Lửa đến.
 Với Hiyuki, đây chỉ là một trận chiến nữa trong hàng ngàn trận. Cô chém xuyên qua lũ quái vật với hiệu suất thuần thục, kiểm tra tính toàn vẹn của lá chắn như thường lệ. Khi dân thường rời khỏi nơi trú ẩn, các bậc phụ huynh chỉ tay về phía cô với vẻ kính cẩn và nhẹ nhõm. "Nhìn kìa, đó là Miko Hoa Anh Đào Lửa đấy."
 Hiyuki khẽ gật đầu đáp lại. Cô bước qua tấm biển "Cấm Vào" đổ gãy và quay lại phía lá chắn để hoàn tất việc kiểm tra.
-Focus. Vung kiếm. Nhập vỏ... Hửm?
+Tập trung. Vung kiếm. Nhập vỏ... Hửm?
 Lưỡi kiếm lướt qua không khí như mọi khi. Nhưng có gì đó khác lạ. Tinh tế, nhưng không thể nhầm lẫn.
 Hiyuki kiểm tra lại toàn bộ lá chắn. Mọi thứ có vẻ nguyên vẹn, nhưng một cảm giác sai trái, ghê rợn vẫn bám chặt vào đầu ngón tay cô. Cô buông chuôi kiếm. Vặn cổ tay. Ép các ngón tay vào nhau—
 Một giọt nhớt đen óng ánh rỉ ra từ làn da cô. Nó đọng lại trong các nếp gấp lòng bàn tay trước khi nhỏ xuống đất, lan rộng âm thầm dưới chân cô.
@@ -16409,7 +16409,7 @@
 Dĩ nhiên là lỗi của cô. Là Miko Hoa Anh Đào Lửa, cô đã thất bại trong việc bảo vệ Honami.
 Và dĩ nhiên, đó không phải lỗi của cô. Trước sức mạnh của Threnodian, một cá nhân chẳng là gì—dù đó là người có thể vẽ ra triệu tương lai để bảo vệ hiện tại.
 Hiyuki trở về Hoa Anh Đào Lửa. Cô nhận tấm bùa hộ mệnh từ đứa trẻ ở cổng, cố nở một nụ cười mờ nhạt. Rồi cô bước chậm về phòng mình và đẩy cửa ra. Ở đó, trên bàn làm việc, là phong thư mà cô đã xé nát.
-"Hiyuki à, Hiyuki. Liệu con đường này có đích đến thật không?"</t>
+"Hiyuki à, Hiyuki... Liệu con đường này có đích đến thật không?"</t>
         </is>
       </c>
     </row>
@@ -16497,18 +16497,18 @@
 Giác quan của cô mờ dần. Thời gian như kéo dài vô tận.
 Cô cảm thấy mọi thứ tạo nên con người mình đang bị xé nát. Tần số của cô vỡ vụn thành vô số sợi chỉ. Thân thể tan thành bụi bặm, cuốn trôi vào đại dương. Rồi cô lại trỗi dậy, như một làn sương mù trôi dạt khắp thế gian, từ đầu này sang đầu kia như gió, lướt qua những vùng đất hoang màu xám xịt cho đến khi chạm tới dải trời quen thuộc, mục nát.
 Và thế giới im lặng ấy nhìn xuống cô, như bao lần trước, không một lời.
-Khi Grand Architect chọn Denia làm "khoang chứa" sức mạnh của Aleph-1, quyết định ấy không chỉ dựa trên sự tương thích về thể chất và tần số. Khác với những Resonators khác—những người được định hình bởi cuộc sống phong phú và cảm xúc sâu sắc—Denia chỉ là một cái vỏ trống rỗng. Một chiếc vỏ rỗng tuếch. Và điều duy nhất mà một chiếc vỏ rỗng cảm nhận được về bản thân và thế giới, hơn bất cứ thứ gì khác, chính là "sự hư vô". Một đặc tính hoàn toàn phù hợp với logic tồn tại của Aleph-1.
+Khi Kiến Trúc Sư Vĩ Đại chọn Denia làm "khoang chứa" sức mạnh của Aleph-1, quyết định ấy không chỉ dựa trên sự tương thích về thể chất và tần số. Khác với những Resonator khác—những người được định hình bởi cuộc sống phong phú và cảm xúc sâu sắc—Denia chỉ là một cái vỏ trống rỗng. Một chiếc vỏ rỗng tuếch. Và điều duy nhất mà một chiếc vỏ rỗng cảm nhận được về bản thân và thế giới, hơn bất cứ thứ gì khác, chính là "sự hư vô". Một đặc tính hoàn toàn phù hợp với logic tồn tại của Aleph-1.
 Và đúng như dự đoán, Denia đã tiếp nhận được sức mạnh ấy. Trong khoảnh khắc ngắn ngủi ở &lt;te href=750040&gt;Voidspace&lt;/te&gt;, mắt cô chạm ánh nhìn của Aleph-1. Một thoáng chớp nhoáng, nhưng đủ để Voidmatter tràn vào huyết quản và nội tạng cô. Nó ban cho cô khả năng điều khiển các hạt Voidmatter và tạo nên mối liên kết với chính Voidspace.
 Lúc đó, cô chỉ cảm nhận được sự im lặng quen thuộc trong hư vô, cùng với sự bình yên đi kèm.
-Nhưng khi kế hoạch tiến triển, Fractsidus nhận thấy Sự Resonance giữa Denia và Voidborne Threnodian đang suy giảm nhanh chóng.
+Nhưng khi kế hoạch tiến triển, Fractsidus nhận thấy Sự Cộng Hưởng giữa Denia và Voidborne Threnodian đang suy giảm nhanh chóng.
 Sức mạnh vẫn nguyên vẹn. Có điều gì đó đã sai. Chiếc khoang chứa lẽ ra phải trống rỗng... lại không còn như vậy. Không còn nghi ngờ gì nữa, Denia đã thất bại trong việc đạt tới sự hoàn hảo mà họ mong muốn.
 Trong nỗ lực bắt chước hành vi con người, mô phỏng những cảm xúc mà cô chưa từng được trải nghiệm, trái tim mỏng manh, đau đớn đã dần hình thành trong cô.
 Trái tim của kẻ yếu đuối.
-Và với trái tim ấy, cô sẽ không bao giờ thực sự trở thành hiện thân của Aleph-1. Vì vậy, Fractsidus cần phải lấp đầy chiếc khoang chứa này bằng thứ gì đó đủ mạnh mẽ để điều khiển "hư vô" và hoàn tất bước cuối cùng trong việc tạo ra Resonators của Aleph-1.
+Và với trái tim ấy, cô sẽ không bao giờ thực sự trở thành hiện thân của Aleph-1. Vì vậy, Fractsidus cần phải lấp đầy chiếc khoang chứa này bằng thứ gì đó đủ mạnh mẽ để điều khiển "hư vô" và hoàn tất bước cuối cùng trong việc tạo ra Resonator của Aleph-1.
 Denia luôn biết ngày này sẽ đến.
 Nhưng khi ngày ấy thực sự tới, cô sẽ phán xét cuộc đời mình như thế nào?
 Một con rối. Một con quái vật méo mó... Hay chỉ là một giọt nước nhỏ trong đại dương mà chẳng ai nhớ tới.
-Đôi khi cô nghĩ về khoảng thời gian ở Startorch Academy. Cô gái giữa đám đông với nụ cười bất ngờ. Cô gái có tiếng cười dịu dàng còn vương vấn trong ký ức của người khác. Cô gái lười biếng, đôi lúc còn luống cuống.
+Đôi khi cô nghĩ về khoảng thời gian ở Học viện Startorch. Cô gái giữa đám đông với nụ cười bất ngờ. Cô gái có tiếng cười dịu dàng còn vương vấn trong ký ức của người khác. Cô gái lười biếng, đôi lúc còn luống cuống.
 Đó có thật sự là cô không?
 Nhưng rồi, phải chăng cô không phải là cô gái ấy?</t>
         </is>
@@ -16900,7 +16900,7 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>Acolyte Lenore nhờ cậu tìm lại những Bản Giao Hưởng Nimbus đã thất lạc từ lâu. Cậu thu thập các mảnh vỡ của nó tại Nimbus Sanctum, nhưng Lenore tin rằng vẫn còn thiếu một đoạn cuối. Đúng lúc đó, Kho Archive Cấm Major bất ngờ tái xuất, và cô nhờ cậu bước vào để tìm mảnh cuối cùng.</t>
+          <t>Tín Đồ Lenore nhờ cậu tìm lại những Bản Giao Hưởng Nimbus đã thất lạc từ lâu. Cậu thu thập các mảnh vỡ của nó tại Nimbus Sanctum, nhưng Lenore tin rằng vẫn còn thiếu một đoạn cuối. Đúng lúc đó, Kho Lưu Trữ Cấm Major bất ngờ tái xuất, và cô nhờ cậu bước vào để tìm mảnh cuối cùng.</t>
         </is>
       </c>
     </row>
@@ -16965,7 +16965,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>Sâu trong Kho Archive, ngươi tìm lại được mảnh ghép thất lạc, chỉ để phát hiện rằng nó không ca ngợi Sentinel như Lenore mong đợi, mà là những con người cổ xưa của Rinascita. Cô tin điều này đi ngược lại giáo lý của Order, thế nhưng vẫn bị xúc động bởi những cảm xúc mà bản nhạc truyền tải. Trước khi giải tỏa được những nghi hoặc mà nó khơi gợi, cô quyết định chưa báo cáo việc này lên Order.</t>
+          <t>Sâu trong Kho Lưu Trữ, ngươi tìm lại được mảnh ghép thất lạc, chỉ để phát hiện rằng nó không ca ngợi Sentinel như Lenore mong đợi, mà là những con người cổ xưa của Rinascita. Cô tin điều này đi ngược lại giáo lý của Order, thế nhưng vẫn bị xúc động bởi những cảm xúc mà bản nhạc truyền tải. Trước khi giải tỏa được những nghi hoặc mà nó khơi gợi, cô quyết định chưa báo cáo việc này lên Order.</t>
         </is>
       </c>
     </row>
@@ -17225,7 +17225,7 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>Ngươi cứu một Aria Mummer sắp chết và hứa sẽ hoàn thành nguyện vọng cuối cùng của nó bằng cách trao những Chiếc Melody Box đến tay những người mà chúng thuộc về. Khi mang chúng băng qua thành phố, ngươi chứng kiến từng mảnh đời nhỏ bé ở Septimont. Qua những giai điệu, mọi người chợt nhận ra những khía cạnh chưa từng biết về người thân yêu của mình. Sau khi chiếc Melody Box cuối cùng được trao đi, Aria Mummer trở về với Resonance Nexus, chỉ để lại một khúc nhạc nhạt nhòa vang vọng trong lòng mọi người.</t>
+          <t>Ngươi cứu một Aria Mummer sắp chết và hứa sẽ hoàn thành nguyện vọng cuối cùng của nó bằng cách trao những Chiếc Hộp Giai Điệu đến tay những người mà chúng thuộc về. Khi mang chúng băng qua thành phố, ngươi chứng kiến từng mảnh đời nhỏ bé ở Septimont. Qua những giai điệu, mọi người chợt nhận ra những khía cạnh chưa từng biết về người thân yêu của mình. Sau khi chiếc Hộp Giai Điệu cuối cùng được trao đi, Aria Mummer trở về với Resonance Nexus, chỉ để lại một khúc nhạc nhạt nhòa vang vọng trong lòng mọi người.</t>
         </is>
       </c>
     </row>
@@ -17355,7 +17355,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>Cùng nhau, Dari của tộc Roya và cậu, người đến từ Startorch Academy, hãy khôi phục nguồn năng lượng của Tập thể Spacetrek và thắp sáng lại những bức tranh đá Roya để chúng lại tỏa sáng dưới bầu trời Lahai-Roi. Giờ đây, dưới ánh sáng của Tập thể, những bức tranh đá không chỉ là tác phẩm nghệ thuật của người Roya. Chúng đã trở thành biểu tượng cho sự đoàn kết của hai dân tộc cùng bảo vệ Lahai-Roi.</t>
+          <t>Cùng nhau, Dari của tộc Roya và cậu, người đến từ Học viện Startorch, hãy khôi phục nguồn năng lượng của Tập thể Spacetrek và thắp sáng lại những bức tranh đá Roya để chúng lại tỏa sáng dưới bầu trời Lahai-Roi. Giờ đây, dưới ánh sáng của Tập thể, những bức tranh đá không chỉ là tác phẩm nghệ thuật của người Roya. Chúng đã trở thành biểu tượng cho sự đoàn kết của hai dân tộc cùng bảo vệ Lahai-Roi.</t>
         </is>
       </c>
     </row>
@@ -17519,32 +17519,32 @@
 Người nhận: Ủy ban Đánh giá Rủi ro Chiến lược, Tập đoàn Spacetrek
 I. Bối cảnh và Mục tiêu Điều tra
 Kể từ tuần thứ ba của năm tài chính này, các hiện tượng dị thường sau đã được ghi nhận trên khắp Lahai-Roi:
-1. Chu kỳ hoạt động của Void Storm đột ngột rút ngắn xuống còn 72 giờ tiêu chuẩn, tần suất tăng khoảng 40%.
+1. Chu kỳ hoạt động của Bão Hư Không đột ngột rút ngắn xuống còn 72 giờ tiêu chuẩn, tần suất tăng khoảng 40%.
 2. Nồng độ Vật Chất Hư Không trong khu vực tăng 31,7% so với cùng kỳ năm ngoái, và đường cong tăng trưởng không có dấu hiệu chững lại.
 3. Hiện tượng nhiễu sóng Threnodian tần số thấp xuất hiện thường xuyên, một số trạm giám sát ghi nhận dao động hài hòa từ nguồn gốc chưa xác định.
-Theo "Quy định Bảo vệ và An toàn Vật Chất Hư Không Lahai-Roi", và do các chỉ số dị thường trên trùng khớp với đặc điểm tiền đề của sự kiện tràn Vật Chất Threnodian, một chuyên gia tư vấn đặc biệt đã được ủy nhiệm tiến hành kiểm tra khẩn cấp lại địa điểm Khe Nứt Niêm Phong tại Dimmr Plains.
+Theo "Quy định Bảo vệ và An toàn Vật Chất Hư Không Lahai-Roi", và do các chỉ số dị thường trên trùng khớp với đặc điểm tiền đề của sự kiện tràn Vật Chất Threnodian, một chuyên gia tư vấn đặc biệt đã được ủy nhiệm tiến hành kiểm tra khẩn cấp lại địa điểm Khe Nứt Niêm Phong tại Đồng bằng Dimmr.
 Người điều hành: Hiyuki (Chuyên gia Lực lượng Đối phó Threnodian)
-Địa điểm điều tra: Khe Nứt Niêm Phong Dimmr Plains - Tòa Án Đã Ngừng
+Địa điểm điều tra: Khe Nứt Niêm Phong Đồng bằng Dimmr - Tòa Án Đã Ngừng
 II. Biên bản Điều tra của Người điều hành
-Nội dung sau được tổng hợp từ lời kể của Hiyuki và dữ liệu Terminal:
+Nội dung sau được tổng hợp từ lời kể của Hiyuki và dữ liệu Thiết bị đầu cuối:
 Lưỡi kiếm tại Tòa Án Đã Ngừng vẫn còn nguyên vị trí, nhưng mặt đất nơi lưỡi kiếm tiếp xúc có dấu hiệu nhiễm Vật Chất Hư Không.
 Đúng vậy. Thực thể bên kia Cổng Strider đang tăng cường tích lũy năng lượng, nhưng ta không thể xác định được thời điểm nó sẽ hành động.
 ...Ta đã tái truyền tần số của mình vào lưỡi kiếm. Ít nhất, sức mạnh của Aleph-1 không thể vượt qua điểm này trong thời điểm hiện tại.
-End biên bản.
+Kết thúc biên bản.
 III. Kết luận Điều tra
-Dựa trên khảo sát thực địa của Hiyuki và phân tích dữ liệu phổ tiếp theo, kết luận sau đã được đưa ra về tình trạng Khe Nứt Niêm Phong tại Dimmr Plains:
-Cấu trúc chính của niêm phong vẫn còn nguyên vẹn, không có dấu hiệu vỡ hoặc tràn lớn. Tuy nhiên, hoạt động của Vật Chất Hư Không bên dưới khe nứt đang có xu hướng tăng liên tục, tương quan thuận với sự gia tăng gần đây về tần suất và nồng độ Void Storm. Từ những điều trên, khoảng thời gian trước khi niêm phong của Threnodian Aleph-1 thất bại đang dần thu hẹp.
+Dựa trên khảo sát thực địa của Hiyuki và phân tích dữ liệu phổ tiếp theo, kết luận sau đã được đưa ra về tình trạng Khe Nứt Niêm Phong tại Đồng bằng Dimmr:
+Cấu trúc chính của niêm phong vẫn còn nguyên vẹn, không có dấu hiệu vỡ hoặc tràn lớn. Tuy nhiên, hoạt động của Vật Chất Hư Không bên dưới khe nứt đang có xu hướng tăng liên tục, tương quan thuận với sự gia tăng gần đây về tần suất và nồng độ Bão Hư Không. Từ những điều trên, khoảng thời gian trước khi niêm phong của Threnodian Aleph-1 thất bại đang dần thu hẹp.
 IV. Khuyến nghị và Vấn đề Cần Xem xét
 Trước tình hình hiện tại, tôi kính trình lên Ủy ban Vật Chất Hư Không của Tập đoàn Spacetrek những vấn đề sau để xem xét:
 • Ngay lập tức kích hoạt giai đoạn chuẩn bị của Duskveil và nâng mức cảnh báo sớm thảm họa Vật Chất Hư Không trên toàn Lahai-Roi lên Cấp Hai.
 • Tăng tốc quá trình hiệu chuẩn cho các Mechascout chiến đấu và chống Vật Chất Hư Không, ưu tiên hoàn thành sửa chữa khung cơ bản của Exostrider và thử nghiệm tải trọng động.
-• Cho phép thành lập Đội Ứng phó Nhanh Vật Chất Hư Không, với Hiyuki đảm nhiệm vị trí Giám đốc Chiến thuật, chịu trách nhiệm giám sát động và ứng phó khẩn cấp tại khu vực Dimmr Plains.
+• Cho phép thành lập Đội Ứng phó Nhanh Vật Chất Hư Không, với Hiyuki đảm nhiệm vị trí Giám đốc Chiến thuật, chịu trách nhiệm giám sát động và ứng phó khẩn cấp tại khu vực Đồng bằng Dimmr.
 Những kết luận và khuyến nghị điều tra trên được trình lên để xem xét chung.
 Người nộp đơn: Lucilla
 [Phụ lục] Bảng dữ liệu
 Bảng 1: Xu hướng Nồng độ Vật Chất Hư Không trong 30 ngày quan sát gần nhất
-Bảng 2: Tổng hợp Hồ sơ Nhiễu sóng Threnodian Tần số Low
-Bảng 3: Ghi âm Terminal của Hiyuki (Đã mã hóa)
+Bảng 2: Tổng hợp Hồ sơ Nhiễu sóng Threnodian Tần số Thấp
+Bảng 3: Ghi âm Thiết bị đầu cuối của Hiyuki (Đã mã hóa)
 (Các bảng trên được đính kèm với tài liệu này, tổng cộng 17 trang.)</t>
         </is>
       </c>
@@ -17623,20 +17623,20 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>Trong quá trình khảo sát tiếp theo tại Dimmr Plains, đội điều tra đã phát hiện một khu vực tích tụ vật liệu quy mô lớn bên dưới Vách Đá Im Lặng.
+          <t>Trong quá trình khảo sát tiếp theo tại Đồng Bằng Dimmr, đội điều tra đã phát hiện một khu vực tích tụ vật liệu quy mô lớn bên dưới Vách Đá Im Lặng.
 Nhận dạng sơ bộ cho thấy các mảng trầm tích ở khu vực này thuộc hai loại chính:
 1. Những mảnh vỡ cấu trúc mang đặc điểm kiến trúc của Spacetrek Collective thời kỳ đầu – bao gồm nhưng không giới hạn ở các vách ngăn hợp kim đúc sẵn, đường ống truyền năng lượng và khung mô-đun chức năng còn sót lại.
 2. Các mảnh vỡ của Exoswarm ở nhiều dạng khác nhau, hoạt động sinh học đã hoàn toàn ngừng lại và được xác nhận đang ở trạng thái ngủ đông.
-Những phát hiện này đặt ra một câu hỏi cấp bách: làm thế nào lô vật liệu này lại xuất hiện ở Dimmr Plains cằn cỗi, cách xa mọi khu vực hạ tầng quy hoạch?
-Trong quá trình truy xuất mã số linh kiện của những tài sản bị bỏ lại này, đội điều tra đã phát hiện một hồ sơ lưu trữ từng bị bỏ sót. Trong giai đoạn đầu thành lập Startorch Academy, một chuyến hàng vật liệu từ Liên bang New đã cập bến Lahai-Roi. Theo báo cáo điều vận thời điểm đó, đoàn vận tải đã gặp phải một cơn Void Storm đột ngột gần Sundermere. Hồ sơ kiểm kê sau đó cho thấy Void Storm đã gây thất thoát nghiêm trọng về tài sản và vật liệu xây dựng, sau đó được ghi nhận là "thất thoát vĩnh viễn".
-Tuy nhiên, khi cuộc điều tra tiến triển, một số điểm bất nhất đã xuất hiện trong hồ sơ về cơn Void Storm đó:
+Những phát hiện này đặt ra một câu hỏi cấp bách: làm thế nào lô vật liệu này lại xuất hiện ở Đồng Bằng Dimmr cằn cỗi, cách xa mọi khu vực hạ tầng quy hoạch?
+Trong quá trình truy xuất mã số linh kiện của những tài sản bị bỏ lại này, đội điều tra đã phát hiện một hồ sơ lưu trữ từng bị bỏ sót. Trong giai đoạn đầu thành lập Học viện Startorch, một chuyến hàng vật liệu từ Liên bang Mới đã cập bến Lahai-Roi. Theo báo cáo điều vận thời điểm đó, đoàn vận tải đã gặp phải một cơn Bão Hư Không đột ngột gần Sundermere. Hồ sơ kiểm kê sau đó cho thấy Bão Hư Không đã gây thất thoát nghiêm trọng về tài sản và vật liệu xây dựng, sau đó được ghi nhận là "thất thoát vĩnh viễn".
+Tuy nhiên, khi cuộc điều tra tiến triển, một số điểm bất nhất đã xuất hiện trong hồ sơ về cơn Bão Hư Không đó:
 1. Trong các báo cáo sự cố được lưu giữ bởi các bộ phận khác nhau, danh mục, số lượng và mã số cụ thể của các vật liệu thất thoát có nhiều điểm mâu thuẫn. Một số dữ liệu trái ngược nhau đến mức không thể hình thành cơ sở ghi nhận tổn thất thống nhất.
-2. Dữ liệu từ các trạm giám sát Vật Chất Hư Không cùng thời kỳ cho thấy cường độ và thời gian của cơn Void Storm không đủ để phân hủy hoàn toàn các vật liệu công nghiệp. Hơn nữa, ghi chú trong bản kê khai vận chuyển ngày hôm đó cho thấy một số tài sản trong lô hàng này đã được xử lý bằng lớp phủ kháng Vật Chất Hư Không.
-3. Nếu các vật liệu trong khu tích tụ này từng bị phân hủy bởi Vật Chất Hư Không và bị bỏ lại ở Dimmr Plains, tần số Vật Chất Hư Không còn sót lại lẽ ra phải phân tán đều, chứ không tập trung trên lớp bảo vệ bề mặt.
-Những mâu thuẫn này chỉ ra một khả năng: sự thất thoát vật liệu được ghi nhận là "tai nạn" năm đó có thể không phải do Void Storm gây ra. Rất có thể, sau khi cập bến Lahai-Roi, lô vật liệu này đã bị chuyển hướng bằng một phương thức nào đó, và cơn Void Storm chỉ là vỏ bọc tự nhiên cho vụ chuyển giao.
-Đội điều tra hiện đã đánh dấu tọa độ của khu vực này và thu thập mẫu vật. Vì các mảnh vỡ Exoswarm thời kỳ đầu vẫn còn giá trị tham khảo trong việc nghiên cứu giới hạn biệt hóa và cơ chế thoái hóa của Exoswarm, nên khuyến nghị đưa chúng vào danh mục thu hồi tiếp theo. Còn về việc lô vật liệu này đã đến Dimmr Plains bằng cách nào, và những con số không khớp trong hồ sơ Void Storm cuối cùng có ý nghĩa gì, những câu hỏi đó có lẽ sẽ phải để lại cho các cuộc xác minh sau này.
+2. Dữ liệu từ các trạm giám sát Vật Chất Hư Không cùng thời kỳ cho thấy cường độ và thời gian của cơn Bão Hư Không không đủ để phân hủy hoàn toàn các vật liệu công nghiệp. Hơn nữa, ghi chú trong bản kê khai vận chuyển ngày hôm đó cho thấy một số tài sản trong lô hàng này đã được xử lý bằng lớp phủ kháng Vật Chất Hư Không.
+3. Nếu các vật liệu trong khu tích tụ này từng bị phân hủy bởi Vật Chất Hư Không và bị bỏ lại ở Đồng Bằng Dimmr, tần số Vật Chất Hư Không còn sót lại lẽ ra phải phân tán đều, chứ không tập trung trên lớp bảo vệ bề mặt.
+Những mâu thuẫn này chỉ ra một khả năng: sự thất thoát vật liệu được ghi nhận là "tai nạn" năm đó có thể không phải do Bão Hư Không gây ra. Rất có thể, sau khi cập bến Lahai-Roi, lô vật liệu này đã bị chuyển hướng bằng một phương thức nào đó, và cơn Bão Hư Không chỉ là vỏ bọc tự nhiên cho vụ chuyển giao.
+Đội điều tra hiện đã đánh dấu tọa độ của khu vực này và thu thập mẫu vật. Vì các mảnh vỡ Exoswarm thời kỳ đầu vẫn còn giá trị tham khảo trong việc nghiên cứu giới hạn biệt hóa và cơ chế thoái hóa của Exoswarm, nên khuyến nghị đưa chúng vào danh mục thu hồi tiếp theo. Còn về việc lô vật liệu này đã đến Đồng Bằng Dimmr bằng cách nào, và những con số không khớp trong hồ sơ Bão Hư Không cuối cùng có ý nghĩa gì, những câu hỏi đó có lẽ sẽ phải để lại cho các cuộc xác minh sau này.
 Ghi chú Nhóm Nghiên cứu:
-Về thời điểm hình thành của khu tích tụ này, trình tự địa tầng và mối tương quan với hoạt động Void Storm cùng thời kỳ, vẫn cần so sánh dữ liệu liên bộ phận thêm. Khuyến nghị phối hợp thu thập tất cả hồ sơ gốc từ những người tham gia vận chuyển và kiểm kê năm đó, nhằm khôi phục bức tranh toàn cảnh của sự kiện càng nhiều càng tốt.</t>
+Về thời điểm hình thành của khu tích tụ này, trình tự địa tầng và mối tương quan với hoạt động Bão Hư Không cùng thời kỳ, vẫn cần so sánh dữ liệu liên bộ phận thêm. Khuyến nghị phối hợp thu thập tất cả hồ sơ gốc từ những người tham gia vận chuyển và kiểm kê năm đó, nhằm khôi phục bức tranh toàn cảnh của sự kiện càng nhiều càng tốt.</t>
         </is>
       </c>
     </row>
@@ -17728,12 +17728,12 @@
 ...
 ...
 Còn những gì xảy ra sau đó, tôi tin rằng mọi người ở đây đều đã biết. Chúng ta vẫn đang đứng đây. Ngay cả khi hư vô cố nuốt trọn Lahai-Roi, chúng ta vẫn đứng vững.
-Yes. Chúng ta đã mất mát quá nhiều.
+Đúng vậy. Chúng ta đã mất mát quá nhiều.
 Nhưng ngay lúc này, chúng ta vẫn đang đứng đây. Và chúng ta sẽ tiếp tục tiến về phía trước.
 Aleph-One đã cố khiến chúng ta tin rằng mọi thứ cuối cùng đều trở về hư vô. Nhưng nó đã sai. Tín hiệu đó, được gửi đi từ một tàu thăm dò mà các nhà thám hiểm Solaris phóng lên cách đây nhiều năm, không phải là tiếng ồn trắng. Không phải bức xạ nền vũ trụ.
 Đó là tiếng nói của khởi đầu. Ánh sáng sau vụ nổ Big Bang. Và chúng ta vẫn có thể nghe thấy nó, xuyên qua hàng tỷ năm.
 Vì vậy, hãy ghi nhớ điều này: mọi thứ từng tồn tại đều để lại dấu vết.
-Spacetrek Collective sẽ không dừng lại. Một ngày nào đó, chúng ta sẽ vượt qua Etheric Seaic. Chúng ta sẽ tiến vào một thế giới rộng lớn hơn.
+Spacetrek Collective sẽ không dừng lại. Một ngày nào đó, chúng ta sẽ vượt qua Biển Etheric. Chúng ta sẽ tiến vào một thế giới rộng lớn hơn.
 Và như Exostrider từng nói:
 Nguyện chúng ta gặp lại nhau trong biển sao vô tận!</t>
         </is>
@@ -17888,25 +17888,25 @@
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Sawring - Blitz&lt;/color&gt;&lt;/size&gt;
 &lt;color=Highlight&gt;Sawring - Blitz&lt;/color&gt; có thể thực hiện liên tiếp 3 đòn tấn công, gây &lt;color=Dark&gt;Havoc DMG&lt;/color&gt;.
-{Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; để bắt đầu chuỗi từ &lt;color=Highlight&gt;Sawring - Blitz Stage 1&lt;/color&gt;. Giữ &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; để bắt đầu từ &lt;color=Highlight&gt;Sawring - Blitz Stage 2&lt;/color&gt;.
+{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; để bắt đầu chuỗi từ &lt;color=Highlight&gt;Sawring - Blitz Stage 1&lt;/color&gt;. Giữ &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; để bắt đầu từ &lt;color=Highlight&gt;Sawring - Blitz Stage 2&lt;/color&gt;.
 Giữ &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; khi đang thực hiện &lt;color=Highlight&gt;Sawring - Blitz Stage 2&lt;/color&gt; để tấn công liên tục. &lt;color=Highlight&gt;Sawring - Blitz Stage 2&lt;/color&gt; sẽ tự động chuyển sang &lt;color=Highlight&gt;Sawring - Blitz Stage 3&lt;/color&gt;.
 Trong khi thực hiện &lt;color=Highlight&gt;Sawring - Blitz Stage 2&lt;/color&gt;, thả nút &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; hoặc &lt;color=Highlight&gt;Dodge&lt;/color&gt; không có hướng di chuyển để tự động thực hiện &lt;color=Highlight&gt;Sawring - Blitz Stage 2: Discordance&lt;/color&gt;, gây &lt;color=Dark&gt;Havoc DMG&lt;/color&gt;. Ngay sau khi thực hiện &lt;color=Highlight&gt;Sawring - Blitz Stage 2: Discordance&lt;/color&gt;, có thể kích hoạt Dodge thành công.
-{Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau khi thực hiện &lt;color=Highlight&gt;Sawring - Blitz Stage 2: Discordance&lt;/color&gt; để thực hiện &lt;color=Highlight&gt;Sawring - Blitz Stage 3&lt;/color&gt;.
+{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau khi thực hiện &lt;color=Highlight&gt;Sawring - Blitz Stage 2: Discordance&lt;/color&gt; để thực hiện &lt;color=Highlight&gt;Sawring - Blitz Stage 3&lt;/color&gt;.
 Trong khi thực hiện &lt;color=Highlight&gt;Sawring - Blitz Stage 3&lt;/color&gt;, giữ &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; để tấn công liên tục. &lt;color=Highlight&gt;Sawring - Blitz Stage 3&lt;/color&gt; sẽ tự động chuyển sang &lt;color=Highlight&gt;Sawring - Eradication&lt;/color&gt;.
 Thả &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; trong &lt;color=Highlight&gt;Sawring - Blitz Stage 3&lt;/color&gt; để tự động thực hiện &lt;color=Highlight&gt;Sawring - Blitz Stage 3: Falltone&lt;/color&gt;, gây &lt;color=Dark&gt;Havoc DMG&lt;/color&gt;.
 Sát thương của &lt;color=Highlight&gt;Sawring - Blitz&lt;/color&gt; được tính là &lt;color=Highlight&gt;Resonance Liberation DMG&lt;/color&gt;.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Chainsaw Mode - Dodge Counter&lt;/color&gt;&lt;/size&gt;
-Khi ở &lt;color=Highlight&gt;Chainsaw Mode&lt;/color&gt;, {Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; sau khi &lt;color=Highlight&gt;Dodge&lt;/color&gt; thành công để thực hiện &lt;color=Highlight&gt;Chainsaw Mode - Dodge Counter&lt;/color&gt;, gây &lt;color=Dark&gt;Havoc DMG&lt;/color&gt;.
-{Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; sau khi thực hiện &lt;color=Highlight&gt;Chainsaw Mode - Dodge Counter&lt;/color&gt; để thực hiện &lt;color=Highlight&gt;Sawring - Blitz Stage 3&lt;/color&gt;.
+Khi ở &lt;color=Highlight&gt;Chainsaw Mode&lt;/color&gt;, {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; sau khi &lt;color=Highlight&gt;Dodge&lt;/color&gt; thành công để thực hiện &lt;color=Highlight&gt;Chainsaw Mode - Dodge Counter&lt;/color&gt;, gây &lt;color=Dark&gt;Havoc DMG&lt;/color&gt;.
+{Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; sau khi thực hiện &lt;color=Highlight&gt;Chainsaw Mode - Dodge Counter&lt;/color&gt; để thực hiện &lt;color=Highlight&gt;Sawring - Blitz Stage 3&lt;/color&gt;.
 Giữ &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; khi đang thực hiện &lt;color=Highlight&gt;Chainsaw Mode - Dodge Counter&lt;/color&gt; để duy trì tấn công. Khi &lt;color=Highlight&gt;Chainsaw Mode - Dodge Counter&lt;/color&gt; kết thúc, sẽ tự động thực hiện &lt;color=Highlight&gt;Sawring - Blitz Stage 3&lt;/color&gt;.
 Thả nút &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; hoặc &lt;color=Highlight&gt;Dodge&lt;/color&gt; không có hướng di chuyển khi đang thực hiện &lt;color=Highlight&gt;Chainsaw Mode - Dodge Counter&lt;/color&gt; để tự động thực hiện &lt;color=Highlight&gt;Sawring - Blitz Stage 2: Discordance&lt;/color&gt;.
 &lt;color=Highlight&gt;Chainsaw Mode - Dodge Counter&lt;/color&gt; gây &lt;color=Highlight&gt;Resonance Liberation DMG&lt;/color&gt;.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Sawring - Eradication&lt;/color&gt;&lt;/size&gt;
 Khi ở &lt;color=Highlight&gt;Chainsaw Mode&lt;/color&gt;, Chisa thực hiện &lt;color=Highlight&gt;Sawring - Eradication&lt;/color&gt; theo 2 cách sau:
-- {Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; sau khi thực hiện &lt;color=Highlight&gt;Sawring - Blitz Stage 3: Falltone&lt;/color&gt;.
-- {Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; sau khi tiêu hao hết &lt;color=Highlight&gt;&lt;te href=150803&gt;Ring of Chainsaw&lt;/te&gt;&lt;/color&gt; bằng &lt;color=Highlight&gt;Sawring - Blitz&lt;/color&gt; hoặc &lt;color=Highlight&gt;Chainsaw Mode - Dodge Counter&lt;/color&gt;.
+- {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; sau khi thực hiện &lt;color=Highlight&gt;Sawring - Blitz Stage 3: Falltone&lt;/color&gt;.
+- {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; sau khi tiêu hao hết &lt;color=Highlight&gt;&lt;te href=150803&gt;Ring of Chainsaw&lt;/te&gt;&lt;/color&gt; bằng &lt;color=Highlight&gt;Sawring - Blitz&lt;/color&gt; hoặc &lt;color=Highlight&gt;Chainsaw Mode - Dodge Counter&lt;/color&gt;.
 Tấn công mục tiêu bằng &lt;color=Highlight&gt;Sawring - Eradication&lt;/color&gt; gây &lt;color=Dark&gt;Havoc DMG&lt;/color&gt; và tạo Khiên cho tất cả Resonators gần đó trong đội trong {5}s.
 Sát thương của kỹ năng được tính là &lt;color=Highlight&gt;Resonance Liberation DMG&lt;/color&gt;.
 Mỗi {6} điểm &lt;color=Highlight&gt;&lt;te href=150803&gt;Ring of Chainsaw&lt;/te&gt;&lt;/color&gt; tiêu hao bởi &lt;color=Highlight&gt;Sawring - Blitz&lt;/color&gt; và &lt;color=Highlight&gt;Chainsaw Mode - Dodge Counter&lt;/color&gt; sẽ tăng Hệ Số Sát Thương của &lt;color=Highlight&gt;Sawring - Eradication&lt;/color&gt; tiếp theo. Tối đa {7} điểm sẽ được tính cho hiệu ứng này.
@@ -17922,11 +17922,11 @@
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Lifethread - Glide&lt;/color&gt;&lt;/size&gt;
 Khi Chisa không ở &lt;color=Highlight&gt;Chainsaw Mode&lt;/color&gt; và có hơn {3} điểm &lt;color=Highlight&gt;&lt;te href=150804&gt;Lifethread - Jetstream&lt;/te&gt;&lt;/color&gt;, cô ấy có thể tiêu hao {8} điểm &lt;color=Highlight&gt;&lt;te href=150804&gt;Lifethread - Jetstream&lt;/te&gt;&lt;/color&gt; để thực hiện &lt;color=Highlight&gt;Lifethread - Glide&lt;/color&gt; theo 5 cách sau:
-- {Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Dodge&lt;/color&gt; trên không trước khi hạ cánh sau khi sử dụng &lt;color=Highlight&gt;Heavy Attack&lt;/color&gt;.
-- Khi đang trên không, {Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Dodge&lt;/color&gt; trước khi hạ cánh sau khi sử dụng Resonance Skill &lt;color=Highlight&gt;Eye of Unraveling&lt;/color&gt; hoặc &lt;color=Highlight&gt;Rending Lunge&lt;/color&gt;.
+- {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Dodge&lt;/color&gt; trên không trước khi hạ cánh sau khi sử dụng &lt;color=Highlight&gt;Heavy Attack&lt;/color&gt;.
+- Khi đang trên không, {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Dodge&lt;/color&gt; trước khi hạ cánh sau khi sử dụng Resonance Skill &lt;color=Highlight&gt;Eye of Unraveling&lt;/color&gt; hoặc &lt;color=Highlight&gt;Rending Lunge&lt;/color&gt;.
 - &lt;color=Highlight&gt;Dodge&lt;/color&gt; về phía trước ngay sau khi sử dụng &lt;color=Highlight&gt;Thread Withdrawn&lt;/color&gt;.
-- {Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Dodge&lt;/color&gt; trước khi hạ cánh khi bị tung lên không.
-- {Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Dodge&lt;/color&gt; trước khi hạ cánh sau khi sử dụng &lt;color=Highlight&gt;Lifethread - Glide&lt;/color&gt;.
+- {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Dodge&lt;/color&gt; trước khi hạ cánh khi bị tung lên không.
+- {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Dodge&lt;/color&gt; trước khi hạ cánh sau khi sử dụng &lt;color=Highlight&gt;Lifethread - Glide&lt;/color&gt;.
 Sử dụng kỹ năng này có thể kéo những kẻ địch gần đó bị đánh dấu bởi &lt;color=Highlight&gt;&lt;te href=150801&gt;Unseen Snare&lt;/te&gt;&lt;/color&gt; về phía mình.
 Trong khi sử dụng kỹ năng, giữ &lt;color=Highlight&gt;Dodge&lt;/color&gt; để lướt một đoạn ngắn trên vũ khí.
 Có thể kích hoạt Dodge thành công trong một khoảng thời gian nhất định sau khi sử dụng kỹ năng này.
@@ -18062,14 +18062,14 @@
 Khi sử dụng &lt;color=Highlight&gt;Basic Attack - Aemeath Stage 4&lt;/color&gt; hoặc &lt;color=Highlight&gt;Basic Attack - Mech Stage 4&lt;/color&gt;, sẽ bước vào trạng thái &lt;color=Highlight&gt;Seraphic Duo&lt;/color&gt; trong {1} giây.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Resonance Skill - Seraphic Duet: Overture&lt;/color&gt;&lt;/size&gt;
-Khi Aemeath đang ở trạng thái &lt;color=Highlight&gt;Seraphic Duo&lt;/color&gt; và &lt;color=Highlight&gt;&lt;te href=121004&gt;Synchronization Rate&lt;/te&gt;&lt;/color&gt; không thấp hơn {0} điểm, {Cus:Ipt,Touch=tấn PC=press Gamepad=press} &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; để sử dụng Resonance Skill &lt;color=Highlight&gt;Seraphic Duet: Overture&lt;/color&gt; với chi phí {29} điểm &lt;color=Highlight&gt;&lt;te href=121004&gt;Synchronization Rate&lt;/te&gt;&lt;/color&gt;, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;, được tính là &lt;color=Highlight&gt;Resonance Liberation DMG&lt;/color&gt;.
+Khi Aemeath đang ở trạng thái &lt;color=Highlight&gt;Seraphic Duo&lt;/color&gt; và &lt;color=Highlight&gt;&lt;te href=121004&gt;Synchronization Rate&lt;/te&gt;&lt;/color&gt; không thấp hơn {0} điểm, {Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; để sử dụng Resonance Skill &lt;color=Highlight&gt;Seraphic Duet: Overture&lt;/color&gt; với chi phí {29} điểm &lt;color=Highlight&gt;&lt;te href=121004&gt;Synchronization Rate&lt;/te&gt;&lt;/color&gt;, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;, được tính là &lt;color=Highlight&gt;Resonance Liberation DMG&lt;/color&gt;.
 Có thể sử dụng khi đang ở gần mặt đất trên không.
-Chuyển sang dạng Mech sau khi sử dụng kỹ năng này và thoát khỏi trạng thái &lt;color=Highlight&gt;Seraphic Duo&lt;/color&gt;. {Cus:Ipt,Touch=Tấn PC=press Gamepad=press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; trong khoảng thời gian nhất định để sử dụng &lt;color=Highlight&gt;Basic Attack - Mech Stage 2&lt;/color&gt;.
+Chuyển sang dạng Mech sau khi sử dụng kỹ năng này và thoát khỏi trạng thái &lt;color=Highlight&gt;Seraphic Duo&lt;/color&gt;. {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; trong khoảng thời gian nhất định để sử dụng &lt;color=Highlight&gt;Basic Attack - Mech Stage 2&lt;/color&gt;.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Resonance Skill - Seraphic Duet: Encore&lt;/color&gt;&lt;/size&gt;
-Ở dạng Mech, khi đang ở trạng thái &lt;color=Highlight&gt;Seraphic Duo&lt;/color&gt; và &lt;color=Highlight&gt;&lt;te href=121004&gt;Synchronization Rate&lt;/te&gt;&lt;/color&gt; không thấp hơn {0} điểm, {Cus:Ipt,Touch=tấn PC=press Gamepad=press} &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; để sử dụng Resonance Skill &lt;color=Highlight&gt;Seraphic Duet: Encore&lt;/color&gt; với chi phí {29} điểm &lt;color=Highlight&gt;&lt;te href=121004&gt;Synchronization Rate&lt;/te&gt;&lt;/color&gt;, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;, được tính là &lt;color=Highlight&gt;Resonance Liberation DMG&lt;/color&gt;.
+Ở dạng Mech, khi đang ở trạng thái &lt;color=Highlight&gt;Seraphic Duo&lt;/color&gt; và &lt;color=Highlight&gt;&lt;te href=121004&gt;Synchronization Rate&lt;/te&gt;&lt;/color&gt; không thấp hơn {0} điểm, {Cus:Ipt,Touch=tap PC=press Gamepad=press} &lt;color=Highlight&gt;Resonance Skill&lt;/color&gt; để sử dụng Resonance Skill &lt;color=Highlight&gt;Seraphic Duet: Encore&lt;/color&gt; với chi phí {29} điểm &lt;color=Highlight&gt;&lt;te href=121004&gt;Synchronization Rate&lt;/te&gt;&lt;/color&gt;, gây &lt;color=Fire&gt;Fusion DMG&lt;/color&gt;, được tính là &lt;color=Highlight&gt;Resonance Liberation DMG&lt;/color&gt;.
 Có thể sử dụng khi đang ở gần mặt đất trên không.
-Switch về dạng Aemeath và thoát khỏi trạng thái &lt;color=Highlight&gt;Seraphic Duo&lt;/color&gt;. {Cus:Ipt,Touch=Tấn PC=press Gamepad=press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau đó để sử dụng &lt;color=Highlight&gt;Basic Attack - Aemeath Stage 2&lt;/color&gt;.
+Switch về dạng Aemeath và thoát khỏi trạng thái &lt;color=Highlight&gt;Seraphic Duo&lt;/color&gt;. {Cus:Ipt,Touch=Tap PC=Press Gamepad=Press} &lt;color=Highlight&gt;Normal Attack&lt;/color&gt; ngay sau đó để sử dụng &lt;color=Highlight&gt;Basic Attack - Aemeath Stage 2&lt;/color&gt;.
 &lt;size=10&gt;&lt;/size&gt;
 &lt;size=40&gt;&lt;color=Title&gt;Resonance Mode&lt;/color&gt;&lt;/size&gt;
 - Trong &lt;color=Highlight&gt;Resonance Mode - Tune Rupture&lt;/color&gt;, khi Resonators trong đội phản ứng với &lt;color=Highlight&gt;&lt;te href=100004&gt;Tune Rupture - Interfered&lt;/te&gt;&lt;/color&gt;, sẽ gây &lt;SapTag=2&gt;{2}&lt;/SapTag&gt; {Cus:Sap,S=lớp P=lớp SapTag=2} &lt;color=Highlight&gt;&lt;te href=121012&gt;Rupturous Trail&lt;/te&gt;&lt;/color&gt; lên mục tiêu trong {4} giây, có thể chồng chất tối đa {3} lần.
@@ -18174,7 +18174,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>Trigger tổng cộng 20 Skills Giới Thiệu</t>
+          <t>Kích hoạt tổng cộng 20 Kỹ Năng Giới Thiệu</t>
         </is>
       </c>
     </row>
@@ -18239,7 +18239,7 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>Finish Bell-Borne Geochelone bằng Kỹ Năng Echo của nó</t>
+          <t>Hoàn thành Bell-Borne Geochelone bằng Kỹ Năng Tiếng Vọng của nó</t>
         </is>
       </c>
     </row>
@@ -18304,7 +18304,7 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>Tiêu diệt Inferno Rider bằng Kỹ Năng Echo của chính hắn.</t>
+          <t>Tiêu diệt Kỵ Sĩ Hỏa Ngục bằng Kỹ Năng Tiếng Vọng của chính hắn.</t>
         </is>
       </c>
     </row>
@@ -18369,7 +18369,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>Hạ gục Tempest Mephis bằng Kỹ Năng Echo của chính nó.</t>
+          <t>Hạ gục Tempest Mephis bằng Kỹ Năng Tiếng Vọng của chính nó.</t>
         </is>
       </c>
     </row>
@@ -18434,7 +18434,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>Tiêu diệt Mourning Aix bằng Kỹ Năng Echo của chính hắn.</t>
+          <t>Tiêu diệt Mourning Aix bằng Kỹ Năng Tiếng Vọng của chính hắn.</t>
         </is>
       </c>
     </row>
@@ -18629,7 +18629,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>Gây tổng cộng 100.000 Crit. DMG.</t>
+          <t>Gây tổng cộng 100.000 Sát Thương Bạo Kích.</t>
         </is>
       </c>
     </row>
@@ -18824,7 +18824,7 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>Gây tổng cộng trên 10.000 sát thương</t>
+          <t>Gây tổng cộng trên 10.000 DMG</t>
         </is>
       </c>
     </row>
@@ -18889,7 +18889,7 @@
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>Gây tổng cộng trên 100.000 sát thương</t>
+          <t>Gây tổng cộng trên 100.000 DMG</t>
         </is>
       </c>
     </row>
@@ -18954,7 +18954,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>Gây tổng cộng trên 1.000.000 sát thương</t>
+          <t>Gây tổng cộng trên 1.000.000 DMG</t>
         </is>
       </c>
     </row>
@@ -19019,7 +19019,7 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>Gây tổng cộng trên 10.000.000 sát thương</t>
+          <t>Gây tổng cộng trên 10.000.000 DMG</t>
         </is>
       </c>
     </row>
@@ -19149,7 +19149,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>Hạ gục 10 kẻ địch bằng Heavy Attack của Chixia từ khoảng cách 7m trở lên</t>
+          <t>Hạ gục 10 kẻ địch bằng Đòn Tấn Công Mạnh của Chixia từ khoảng cách 7m trở lên</t>
         </is>
       </c>
     </row>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>Hạ gục 10 kẻ địch bằng Heavy Attack của Chixia từ khoảng cách 1m trở xuống</t>
+          <t>Hạ gục 10 kẻ địch bằng Đòn Tấn Công Mạnh của Chixia từ khoảng cách 1m trở xuống</t>
         </is>
       </c>
     </row>
@@ -19344,7 +19344,7 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>Bị hạ gục bằng một đòn Glacio DMG khi HP trên 50%</t>
+          <t>Bị hạ gục bằng một đòn DMG Glacio khi HP trên 50%</t>
         </is>
       </c>
     </row>
@@ -19409,7 +19409,7 @@
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>Bị hạ gục bằng một đòn Fusion DMG khi HP trên 50%</t>
+          <t>Bị hạ gục bằng một đòn DMG Fusion khi HP trên 50%</t>
         </is>
       </c>
     </row>
@@ -19474,7 +19474,7 @@
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>Bị hạ gục bằng một đòn Electro DMG khi HP trên 50%</t>
+          <t>Bị hạ gục bằng một đòn DMG Electro khi HP trên 50%</t>
         </is>
       </c>
     </row>
@@ -19539,7 +19539,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>Bị hạ gục bằng một đòn Aero DMG khi HP trên 50%</t>
+          <t>Bị hạ gục bằng một đòn DMG Aero khi HP trên 50%</t>
         </is>
       </c>
     </row>
@@ -19604,7 +19604,7 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>Tiêu diệt bằng một đòn Havoc DMG khi HP trên 50%</t>
+          <t>Tiêu diệt bằng một đòn Sát Thương Havoc khi HP trên 50%</t>
         </is>
       </c>
     </row>
@@ -19669,7 +19669,7 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>Tiêu diệt bằng một đòn Spectro DMG khi HP trên 50%</t>
+          <t>Tiêu diệt bằng một đòn Sát Thương Spectro khi HP trên 50%</t>
         </is>
       </c>
     </row>
@@ -20644,7 +20644,7 @@
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>Kiểm tra xem Resonance Nexus tại Central Plains đã được mở khóa chưa</t>
+          <t>Kiểm tra xem Mạng Lưới Cộng Hưởng Trung Nguyên đã mở khóa chưa</t>
         </is>
       </c>
     </row>
@@ -20709,7 +20709,7 @@
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>Kiểm tra xem Resonance Nexus tại Tacetite Highlands đã được mở khóa chưa</t>
+          <t>Kiểm tra xem Tổ Tắc Cộng Hưởng ở Cao Nguyên Tacetite đã được mở khóa chưa</t>
         </is>
       </c>
     </row>
@@ -20774,7 +20774,7 @@
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>Kiểm tra xem Resonance Nexus tại Black Shores đã được mở khóa chưa</t>
+          <t>Kiểm tra xem Mạng Lưới Cộng Hưởng ở Bờ Biển Đen đã mở khóa chưa</t>
         </is>
       </c>
     </row>
@@ -20839,7 +20839,7 @@
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>Kiểm tra xem Resonance Nexus tại Tacet Discord Valley đã được mở khóa chưa</t>
+          <t>Kiểm tra xem Tổ Tắc Cộng Hưởng ở Thung Lũng Tacet Discord đã được mở khóa chưa</t>
         </is>
       </c>
     </row>
@@ -20904,7 +20904,7 @@
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>Kiểm tra xem phiên bản Concerto Reaction đã được kích hoạt chưa</t>
+          <t>Kiểm tra xem phiên bản Phản Ứng Giao Hưởng đã kích hoạt chưa</t>
         </is>
       </c>
     </row>
@@ -20969,7 +20969,7 @@
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>Exiles Resonance</t>
+          <t>Những Kẻ Lưu Đày Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -21164,7 +21164,7 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>Resonance Cord Crownless làm mới quyết tâm</t>
+          <t>Dây Cộng Hưởng Crownless làm mới quyết tâm</t>
         </is>
       </c>
     </row>
@@ -21229,7 +21229,7 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>Resonance Cord Rùa làm mới quyết tâm</t>
+          <t>Dây Cộng Hưởng Rùa làm mới quyết tâm</t>
         </is>
       </c>
     </row>
@@ -21294,7 +21294,7 @@
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t>Resonance Cord Mephis làm mới quyết tâm</t>
+          <t>Dây Cộng Hưởng Mephis làm mới quyết tâm</t>
         </is>
       </c>
     </row>
@@ -21424,7 +21424,7 @@
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>Trigger nhiệm vụ phụ tại trại Exiles</t>
+          <t>Kích hoạt nhiệm vụ phụ tại trại Exiles</t>
         </is>
       </c>
     </row>
@@ -21489,7 +21489,7 @@
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>Dùng kỹ năng Discord để Dodgem</t>
+          <t>Dùng kỹ năng Tacet Discord để ném</t>
         </is>
       </c>
     </row>
@@ -21554,7 +21554,7 @@
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>Dùng kỹ năng Discord để túm lấy</t>
+          <t>Dùng kỹ năng Tacet Discord để túm lấy</t>
         </is>
       </c>
     </row>
@@ -21619,7 +21619,7 @@
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>Dùng kỹ năng Discord để bay lên</t>
+          <t>Dùng kỹ năng Tacet Discord để bay lên</t>
         </is>
       </c>
     </row>
@@ -21814,7 +21814,7 @@
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>Bạn có muốn tiêu thụ [{0}]*{1} để kích hoạt Waypoint không?</t>
+          <t>Bạn có muốn tiêu thụ [{0}]*{1} để kích hoạt Điểm Dẫn Đường không?</t>
         </is>
       </c>
     </row>
@@ -21879,7 +21879,7 @@
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>Đã đạt giới hạn số Waypoint. Bạn có muốn tiêu hao [{0}] x1 để đặt một Waypoint mới và thu hồi điểm đầu tiên không?</t>
+          <t>Đã đạt giới hạn số Điểm Dẫn Đường. Bạn có muốn tiêu hao [{0}] x1 để đặt một Điểm Dẫn Đường mới và thu hồi điểm đầu tiên không?</t>
         </is>
       </c>
     </row>
@@ -21944,7 +21944,7 @@
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>Mở khóa Echo mới hoặc các hạng hiếm cao hơn của Echo đã mở khóa để nhận EXP Data Bank và tăng cấp Data Bank.</t>
+          <t>Mở khóa Echo mới hoặc các Echo hiếm hơn đã mở khóa để nhận Kinh Nghiệm Kho Dữ Liệu và tăng cấp Kho Dữ Liệu.</t>
         </is>
       </c>
     </row>
@@ -22139,7 +22139,7 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>Vật liệu đã chọn &lt;color=#8c7e51&gt;{0}&lt;/color&gt; đã được nâng cấp. Xác nhận tiêu thụ để Syntonize vũ khí &lt;color=#8c7e51&gt;{1}&lt;/color&gt; lên Hạng &lt;color=#8c7e51&gt;{2}&lt;/color&gt;?</t>
+          <t>Vật liệu đã chọn &lt;color=#8c7e51&gt;{0}&lt;/color&gt; đã được nâng cấp. Xác nhận tiêu thụ để Đồng Điệu vũ khí &lt;color=#8c7e51&gt;{1}&lt;/color&gt; lên Hạng &lt;color=#8c7e51&gt;{2}&lt;/color&gt;?</t>
         </is>
       </c>
     </row>
@@ -22334,7 +22334,7 @@
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t>Dùng Rice Dango để thách đấu Neon Tower một lần nữa?</t>
+          <t>Dùng Bánh Dango Gạo để thách đấu Tháp Neon một lần nữa?</t>
         </is>
       </c>
     </row>
@@ -22464,7 +22464,7 @@
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>Insufficient {0} Bạn có muốn dùng {1} để đổi lấy số lượng {2} cần thiết không?</t>
+          <t>Không đủ {0}. Bạn có muốn dùng {1} để đổi lấy số lượng {2} cần thiết không?</t>
         </is>
       </c>
     </row>
@@ -22594,7 +22594,7 @@
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t>Gói lồng tiếng {0} có dung lượng {1}. Download sẽ tiêu tốn dữ liệu di động. Tiến hành tải?</t>
+          <t>Gói lồng tiếng {0} có dung lượng {1}. Tải xuống sẽ tiêu tốn dữ liệu di động. Tiến hành tải?</t>
         </is>
       </c>
     </row>
@@ -22724,7 +22724,7 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>Xác nhận tiêu hao &lt;color=#8c7e51&gt;{0} unlock points&lt;/color&gt; để bắt đầu nhiệm vụ nhân vật &lt;color=#8c7e51&gt;{1}&lt;/color&gt;?</t>
+          <t>Xác nhận tiêu hao &lt;color=#8c7e51&gt;{0} điểm mở khóa&lt;/color&gt; để bắt đầu nhiệm vụ nhân vật &lt;color=#8c7e51&gt;{1}&lt;/color&gt;?</t>
         </is>
       </c>
     </row>
@@ -22790,8 +22790,8 @@
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t>Resonators tích lũy Concerto Energy bằng cách gây sát thương hoặc sử dụng kỹ năng Echo.
-Khi Concerto Energy đầy, hãy chuyển sang Resonators khác, năng lượng sẽ được tiêu hao để kích hoạt Concerto Effect tương ứng.</t>
+          <t>Resonator tích lũy Concerto Energy bằng cách gây sát thương hoặc sử dụng kỹ năng Echo.
+Khi Concerto Energy đầy, hãy chuyển sang Resonator khác, năng lượng sẽ được tiêu hao để kích hoạt Hiệu Ứng Concerto tương ứng.</t>
         </is>
       </c>
     </row>
@@ -22856,7 +22856,7 @@
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>Hồi sinh tức thì sẽ tiêu hao 1 {0}, Cooldown chiêu ước tính là {1}. Tiếp tục?</t>
+          <t>Hồi sinh tức thì sẽ tiêu hao 1 {0}, thời gian hồi chiêu ước tính là {1}. Tiếp tục?</t>
         </is>
       </c>
     </row>
@@ -23311,7 +23311,7 @@
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t>Vật phẩm buff không đủ</t>
+          <t>Không đủ vật phẩm hỗ trợ</t>
         </is>
       </c>
     </row>
@@ -23376,7 +23376,7 @@
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t>Vật phẩm hiệu ứng không thể dùng lại khi chưa hết Cooldown</t>
+          <t>Vật phẩm hiệu ứng không thể dùng lại khi chưa hết thời gian hồi</t>
         </is>
       </c>
     </row>
@@ -23441,7 +23441,7 @@
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>Vật phẩm hiệu ứng chưa hết Cooldown</t>
+          <t>Vật phẩm hiệu ứng chưa hết thời gian hồi</t>
         </is>
       </c>
     </row>
@@ -23506,7 +23506,7 @@
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>Lỗi số lượng sử dụng vật phẩm buff</t>
+          <t>Lỗi số lần sử dụng vật phẩm hiệu ứng</t>
         </is>
       </c>
     </row>
@@ -23701,7 +23701,7 @@
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>Thẻ mục tiêu bay không khớp</t>
+          <t>Thẻ mục tiêu bay lơ lửng không khớp</t>
         </is>
       </c>
     </row>
@@ -23766,7 +23766,7 @@
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>Mục tiêu bay không trong phạm vi</t>
+          <t>Mục tiêu bay lơ lửng không trong phạm vi</t>
         </is>
       </c>
     </row>
@@ -23831,7 +23831,7 @@
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>Thẻ trạng thái mục tiêu bay không khớp</t>
+          <t>Thẻ trạng thái mục tiêu bay lơ lửng không khớp</t>
         </is>
       </c>
     </row>
@@ -23961,7 +23961,7 @@
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t>Không phải mục tiêu bay</t>
+          <t>Không phải mục tiêu bay lơ lửng</t>
         </is>
       </c>
     </row>
@@ -24026,7 +24026,7 @@
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>Mục tiêu bay đã bị loại bỏ</t>
+          <t>Mục tiêu bay lơ lửng đã bị loại bỏ</t>
         </is>
       </c>
     </row>
@@ -24091,7 +24091,7 @@
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t>Thiếu thời gian tháo rời cho mục tiêu Levitation</t>
+          <t>Thiếu thời gian tháo rời cho mục tiêu Bay Lơ Lửng</t>
         </is>
       </c>
     </row>
@@ -24351,7 +24351,7 @@
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>Đang Cooldown. Vui lòng kiểm tra lại sau.</t>
+          <t>Đang hồi chiêu. Vui lòng kiểm tra lại sau.</t>
         </is>
       </c>
     </row>
@@ -24611,7 +24611,7 @@
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>Mục tiêu đạn không tồn tại</t>
+          <t>Mục tiêu không tồn tại</t>
         </is>
       </c>
     </row>
@@ -24676,7 +24676,7 @@
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t>Resonance chưa kích hoạt</t>
+          <t>Cộng Hưởng Chưa Kích Hoạt</t>
         </is>
       </c>
     </row>
@@ -24741,7 +24741,7 @@
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t>Resonance đã kích hoạt</t>
+          <t>Kích hoạt Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -24806,7 +24806,7 @@
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t>Resonance tiên quyết chưa kích hoạt</t>
+          <t>Cộng hưởng Điều kiện tiên quyết chưa kích hoạt</t>
         </is>
       </c>
     </row>
@@ -24871,7 +24871,7 @@
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>Đã đạt cấp Resonance tối đa</t>
+          <t>Đã đạt cấp Cộng Hưởng tối đa</t>
         </is>
       </c>
     </row>
@@ -24936,7 +24936,7 @@
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>Không thể nhận Kỹ năng</t>
+          <t>Không nhận được Kỹ Năng</t>
         </is>
       </c>
     </row>
@@ -25001,7 +25001,7 @@
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t>Lỗi loại nút Kỹ năng</t>
+          <t>Lỗi loại nút Kỹ Năng</t>
         </is>
       </c>
     </row>
@@ -25066,7 +25066,7 @@
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t>Không đủ điểm Forte</t>
+          <t>Điểm Forte không đủ</t>
         </is>
       </c>
     </row>
@@ -25261,7 +25261,7 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>Cấu hình Kỹ năng không tồn tại</t>
+          <t>Cấu Hình Kỹ Năng không tồn tại</t>
         </is>
       </c>
     </row>
@@ -25456,7 +25456,7 @@
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>Cấp Kỹ năng bị khóa</t>
+          <t>Cấp kỹ năng bị khóa</t>
         </is>
       </c>
     </row>
@@ -25521,7 +25521,7 @@
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>Không thể gỡ Kỹ năng</t>
+          <t>Không thể gỡ Kỹ Năng</t>
         </is>
       </c>
     </row>
@@ -25586,7 +25586,7 @@
       </c>
       <c r="M372" t="inlineStr">
         <is>
-          <t>Kỹ Năng và Equipment bị giới hạn cho nhân vật này</t>
+          <t>Kỹ Năng và Trang Bị bị giới hạn cho nhân vật này</t>
         </is>
       </c>
     </row>
@@ -25651,7 +25651,7 @@
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>Lỗi thao tác với Kỹ năng Echo</t>
+          <t>Lỗi thao tác Kỹ Năng Echo</t>
         </is>
       </c>
     </row>
@@ -25716,7 +25716,7 @@
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>Bạn không thể chọn cùng một Kỹ Năng nhiều lần trên Wheel Kỹ Năng.</t>
+          <t>Bạn không thể chọn cùng một Kỹ Năng nhiều lần trên Bánh Xe Kỹ Năng.</t>
         </is>
       </c>
     </row>
@@ -25781,7 +25781,7 @@
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>Hồi sinh đang Cooldown</t>
+          <t>Hồi sinh đang hồi chiêu</t>
         </is>
       </c>
     </row>
@@ -25976,7 +25976,7 @@
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>Resonator này không sở hữu kỹ năng của Discord đó.</t>
+          <t>Resonator này không sở hữu kỹ năng của Tacet Discord đó.</t>
         </is>
       </c>
     </row>
@@ -26171,7 +26171,7 @@
       </c>
       <c r="M381" t="inlineStr">
         <is>
-          <t>Mục tiêu luyện tập đã mở khóa</t>
+          <t>Mục tiêu huấn luyện đã mở khóa</t>
         </is>
       </c>
     </row>
@@ -26236,7 +26236,7 @@
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t>Hoàn thành mục tiêu luyện tập</t>
+          <t>Mục tiêu huấn luyện đã hoàn thành</t>
         </is>
       </c>
     </row>
@@ -26496,7 +26496,7 @@
       </c>
       <c r="M386" t="inlineStr">
         <is>
-          <t>Vị trí mục tiêu không khả dụng</t>
+          <t>Không xác định được vị trí mục tiêu</t>
         </is>
       </c>
     </row>
@@ -26626,7 +26626,7 @@
       </c>
       <c r="M388" t="inlineStr">
         <is>
-          <t>Đã ở Solaris mục tiêu</t>
+          <t>Đã đến mục tiêu Solaris</t>
         </is>
       </c>
     </row>
@@ -26691,7 +26691,7 @@
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>Thiếu thành phần Trigger</t>
+          <t>Thiếu thành phần kích hoạt</t>
         </is>
       </c>
     </row>
@@ -27146,7 +27146,7 @@
       </c>
       <c r="M396" t="inlineStr">
         <is>
-          <t>Đánh bại tất cả kẻ địch trong {0} giây.</t>
+          <t>Tiêu diệt toàn bộ kẻ địch trong vòng {0} giây.</t>
         </is>
       </c>
     </row>
@@ -27341,7 +27341,7 @@
       </c>
       <c r="M399" t="inlineStr">
         <is>
-          <t>Mỗi lần trúng mục tiêu, Tấn Công của kẻ địch tăng thêm 10%, tối đa 50%.</t>
+          <t>Mỗi lần trúng mục tiêu, ATK của kẻ địch tăng thêm 10%, tối đa 50%.</t>
         </is>
       </c>
     </row>
@@ -27406,7 +27406,7 @@
       </c>
       <c r="M400" t="inlineStr">
         <is>
-          <t>Mỗi lần trúng mục tiêu, Tấn Công của kẻ địch tăng thêm 10%, tối đa 50%.</t>
+          <t>Mỗi lần trúng mục tiêu, ATK của kẻ địch tăng thêm 10%, tối đa 50%.</t>
         </is>
       </c>
     </row>
@@ -27731,7 +27731,7 @@
       </c>
       <c r="M405" t="inlineStr">
         <is>
-          <t>Increase Tấn Công của kẻ địch lên 50%. Increase Tốc Độ Hồi Phục Stamina cho đội của bạn.</t>
+          <t>Tăng ATK của kẻ địch lên 50%. Tăng Tốc Độ Hồi Phục Thể Lực cho đội của bạn.</t>
         </is>
       </c>
     </row>
@@ -27796,7 +27796,7 @@
       </c>
       <c r="M406" t="inlineStr">
         <is>
-          <t>Mỗi lần trúng mục tiêu, Tấn Công của kẻ địch tăng thêm 10%.</t>
+          <t>Mỗi lần trúng mục tiêu, ATK của kẻ địch tăng thêm 10%.</t>
         </is>
       </c>
     </row>
@@ -27991,7 +27991,7 @@
       </c>
       <c r="M409" t="inlineStr">
         <is>
-          <t>Increase Tấn Công của kẻ địch lên 50%. Increase Tốc Độ Hồi Phục Stamina cho đội của bạn.</t>
+          <t>Tăng ATK của kẻ địch lên 50%. Tăng Tốc Độ Hồi Phục Thể Lực cho đội của bạn.</t>
         </is>
       </c>
     </row>
@@ -28121,7 +28121,7 @@
       </c>
       <c r="M411" t="inlineStr">
         <is>
-          <t>Đánh bại tất cả kẻ địch trong {0} giây.</t>
+          <t>Tiêu diệt toàn bộ kẻ địch trong vòng {0} giây.</t>
         </is>
       </c>
     </row>
@@ -28251,7 +28251,7 @@
       </c>
       <c r="M413" t="inlineStr">
         <is>
-          <t>Đánh bại kẻ địch để nhận điểm</t>
+          <t>Tiêu diệt kẻ địch để nhận điểm</t>
         </is>
       </c>
     </row>
@@ -28316,7 +28316,7 @@
       </c>
       <c r="M414" t="inlineStr">
         <is>
-          <t>HP mục tiêu 100%</t>
+          <t>HP Mục Tiêu: 100%</t>
         </is>
       </c>
     </row>
@@ -28446,7 +28446,7 @@
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>HP phục hồi</t>
+          <t>HP đã hồi phục</t>
         </is>
       </c>
     </row>
@@ -28576,7 +28576,7 @@
       </c>
       <c r="M418" t="inlineStr">
         <is>
-          <t>Đã tìm thấy mục tiêu dò tìm</t>
+          <t>Đã phát hiện mục tiêu thăm dò</t>
         </is>
       </c>
     </row>
@@ -28641,7 +28641,7 @@
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t>Terminal Resonance chưa mở khóa</t>
+          <t>Thiết bị đầu cuối Cộng Hưởng chưa mở khóa</t>
         </is>
       </c>
     </row>
@@ -28706,7 +28706,7 @@
       </c>
       <c r="M420" t="inlineStr">
         <is>
-          <t>Kinh nghiệm Terminal Resonance +{0}</t>
+          <t>Kinh nghiệm Thiết bị đầu cuối Cộng Hưởng +{0}</t>
         </is>
       </c>
     </row>
@@ -28836,7 +28836,7 @@
       </c>
       <c r="M422" t="inlineStr">
         <is>
-          <t>Thời gian cộng hưởng</t>
+          <t>Thời Gian Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -28966,7 +28966,7 @@
       </c>
       <c r="M424" t="inlineStr">
         <is>
-          <t>Tất cả Hiệu ứng Concerto</t>
+          <t>Tất Cả Hiệu Ứng Concerto</t>
         </is>
       </c>
     </row>
@@ -29031,7 +29031,7 @@
       </c>
       <c r="M425" t="inlineStr">
         <is>
-          <t>Vật phẩm hồi sinh đang Cooldown. Sử dụng sau {0} giây.</t>
+          <t>Vật phẩm hồi sinh đang hồi chiêu. Sử dụng sau {0} giây.</t>
         </is>
       </c>
     </row>
@@ -29096,7 +29096,7 @@
       </c>
       <c r="M426" t="inlineStr">
         <is>
-          <t>Tấn công &amp; Chiến đấu</t>
+          <t>ATK &amp; Chiến Đấu</t>
         </is>
       </c>
     </row>
@@ -29291,7 +29291,7 @@
       </c>
       <c r="M429" t="inlineStr">
         <is>
-          <t>Thông tin kẻ địch mạnh</t>
+          <t>Thông tin về kẻ địch cứng đầu</t>
         </is>
       </c>
     </row>
@@ -29356,7 +29356,7 @@
       </c>
       <c r="M430" t="inlineStr">
         <is>
-          <t>Đang điều chỉnh Terminal Resonance</t>
+          <t>Đang điều chỉnh Thiết bị đầu cuối Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -29421,7 +29421,7 @@
       </c>
       <c r="M431" t="inlineStr">
         <is>
-          <t>Consume: {0}</t>
+          <t>Tiêu thụ: {0}</t>
         </is>
       </c>
     </row>
@@ -29486,7 +29486,7 @@
       </c>
       <c r="M432" t="inlineStr">
         <is>
-          <t>Phòng thủ &amp; Hồi phục</t>
+          <t>PHÒNG NGỤ &amp; HỒI PHỤC</t>
         </is>
       </c>
     </row>
@@ -29551,7 +29551,7 @@
       </c>
       <c r="M433" t="inlineStr">
         <is>
-          <t>Không thể đổi nhân vật khi đang Cooldown</t>
+          <t>Không thể đổi nhân vật khi đang hồi chiêu</t>
         </is>
       </c>
     </row>
@@ -29681,7 +29681,7 @@
       </c>
       <c r="M435" t="inlineStr">
         <is>
-          <t>Khi &lt;color=#ffd12f&gt;Concerto Energy&lt;/color&gt; đầy, chuyển đổi nhân vật để kích hoạt &lt;color=#ffd12f&gt;Outro Skills&lt;/color&gt; mang lại nhiều hiệu ứng và buff khác nhau.</t>
+          <t>Khi &lt;color=#ffd12f&gt;Concerto Energy&lt;/color&gt; đầy, chuyển đổi nhân vật để kích hoạt &lt;color=#ffd12f&gt;Kỹ Năng Outro&lt;/color&gt; mang lại nhiều hiệu ứng và buff khác nhau.</t>
         </is>
       </c>
     </row>
@@ -29746,7 +29746,7 @@
       </c>
       <c r="M436" t="inlineStr">
         <is>
-          <t>Khi &lt;color=#ffd12f&gt;Concerto Energy&lt;/color&gt; của thành viên trong đội đạt tối đa, hãy nhấn vào avatar của thành viên đó để kích hoạt hiệu ứng &lt;color=#ffd12f&gt;Outro Skill&lt;/color&gt; của họ.</t>
+          <t>Khi &lt;color=#ffd12f&gt;Concerto Energy&lt;/color&gt; của thành viên trong đội đạt tối đa, hãy nhấn vào avatar của thành viên đó để kích hoạt hiệu ứng &lt;color=#ffd12f&gt;Kỹ Năng Outro&lt;/color&gt; của họ.</t>
         </is>
       </c>
     </row>
@@ -29811,7 +29811,7 @@
       </c>
       <c r="M437" t="inlineStr">
         <is>
-          <t>Resonator sẽ tích lũy Năng Lượng Khúc Tấu khi sử dụng kỹ năng gây sát thương &lt;color=#1398ef&gt;in battle&lt;/color&gt;. Khi Năng Lượng Khúc Tấu đầy, bạn sẽ nhận được &lt;color=#1398ef&gt;Concerto Energy Orb&lt;/color&gt;. Khi chuyển đổi nhân vật, việc tiêu hao Quả Cầu Năng Lượng Khúc Tấu hiện có sẽ kích hoạt &lt;color=#1398ef&gt;Concerto Effect&lt;/color&gt;.</t>
+          <t>Resonator sẽ tích lũy Năng Lượng Khúc Tấu khi sử dụng kỹ năng gây sát thương &lt;color=#1398ef&gt;trong trận đấu&lt;/color&gt;. Khi Năng Lượng Khúc Tấu đầy, bạn sẽ nhận được &lt;color=#1398ef&gt;Quả Cầu Năng Lượng Khúc Tấu&lt;/color&gt;. Khi chuyển đổi nhân vật, việc tiêu hao Quả Cầu Năng Lượng Khúc Tấu hiện có sẽ kích hoạt &lt;color=#1398ef&gt;Hiệu Ứng Khúc Tấu&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
@@ -29941,7 +29941,7 @@
       </c>
       <c r="M439" t="inlineStr">
         <is>
-          <t>Chuyển đổi Resonance thành công</t>
+          <t>Chuyển Hóa Cộng Hưởng Thành Công</t>
         </is>
       </c>
     </row>
@@ -30071,7 +30071,7 @@
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t>Báo cáo Kiểm tra Forte</t>
+          <t>Báo Cáo Kiểm Tra Mạch Năng Lực</t>
         </is>
       </c>
     </row>
@@ -30136,7 +30136,7 @@
       </c>
       <c r="M442" t="inlineStr">
         <is>
-          <t>Mô tả bối cảnh Resonance</t>
+          <t>Mô tả nền Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -30201,7 +30201,7 @@
       </c>
       <c r="M443" t="inlineStr">
         <is>
-          <t>Chưa Chụp Chụp ảnh Mục Tiêu</t>
+          <t>Chưa Chụp Ảnh Mục Tiêu</t>
         </is>
       </c>
     </row>
@@ -30396,7 +30396,7 @@
       </c>
       <c r="M446" t="inlineStr">
         <is>
-          <t>Forte points obtained: {0}</t>
+          <t>Đã nhận Điểm Tần số: {0}</t>
         </is>
       </c>
     </row>
@@ -30526,7 +30526,7 @@
       </c>
       <c r="M448" t="inlineStr">
         <is>
-          <t>Độ toàn vẹn mục tiêu</t>
+          <t>Độ Nguyên Vẹn Mục Tiêu</t>
         </is>
       </c>
     </row>
@@ -30656,7 +30656,7 @@
       </c>
       <c r="M450" t="inlineStr">
         <is>
-          <t>Bộ sưu tập kẻ địch bị khóa</t>
+          <t>Kho dữ liệu kẻ địch đã bị khóa</t>
         </is>
       </c>
     </row>
@@ -30786,7 +30786,7 @@
       </c>
       <c r="M452" t="inlineStr">
         <is>
-          <t>Đạt thời gian tối đa</t>
+          <t>Đã đạt thời gian tối đa</t>
         </is>
       </c>
     </row>
@@ -30981,7 +30981,7 @@
       </c>
       <c r="M455" t="inlineStr">
         <is>
-          <t>Chưa nhận Forte</t>
+          <t>Chưa mở khóa Tần số</t>
         </is>
       </c>
     </row>
@@ -31111,7 +31111,7 @@
       </c>
       <c r="M457" t="inlineStr">
         <is>
-          <t>Chi tiết Forte</t>
+          <t>Thông Số Mạch Năng Lực</t>
         </is>
       </c>
     </row>
@@ -31631,7 +31631,7 @@
       </c>
       <c r="M465" t="inlineStr">
         <is>
-          <t>Sort theo Tấn Công</t>
+          <t>Sắp xếp theo ATK</t>
         </is>
       </c>
     </row>
@@ -31696,7 +31696,7 @@
       </c>
       <c r="M466" t="inlineStr">
         <is>
-          <t>Sort theo Phòng Ngự</t>
+          <t>Sắp xếp theo Phòng Ngự</t>
         </is>
       </c>
     </row>
@@ -31761,7 +31761,7 @@
       </c>
       <c r="M467" t="inlineStr">
         <is>
-          <t>Sort theo HP Tối Đa</t>
+          <t>Sắp xếp theo HP Tối Đa</t>
         </is>
       </c>
     </row>
@@ -31826,7 +31826,7 @@
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t>Sort theo Resonance</t>
+          <t>Sắp xếp theo Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -31891,7 +31891,7 @@
       </c>
       <c r="M469" t="inlineStr">
         <is>
-          <t>Materials Kỹ Năng</t>
+          <t>Vật Liệu Kỹ Năng</t>
         </is>
       </c>
     </row>
@@ -31956,7 +31956,7 @@
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>Đặt lại Points Tần số</t>
+          <t>Đặt lại Điểm Tần số</t>
         </is>
       </c>
     </row>
@@ -32021,7 +32021,7 @@
       </c>
       <c r="M471" t="inlineStr">
         <is>
-          <t>Resonance Nexus đã kích hoạt</t>
+          <t>Mạng Lưới Cộng Hưởng đã kích hoạt</t>
         </is>
       </c>
     </row>
@@ -32086,7 +32086,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>Đèn Hiệu Resonance Small đã được kích hoạt</t>
+          <t>Đèn Hiệu Cộng Hưởng Nhỏ đã được kích hoạt</t>
         </is>
       </c>
     </row>
@@ -32216,7 +32216,7 @@
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>Forte point(s): {0}</t>
+          <t>Điểm Tần số: {0}</t>
         </is>
       </c>
     </row>
@@ -32346,7 +32346,7 @@
       </c>
       <c r="M476" t="inlineStr">
         <is>
-          <t>Includes vật phẩm đã tinh chỉnh và nâng cấp. Dùng {0} để đồng điệu Vũ Khí {1} lên cấp {2} chứ?</t>
+          <t>Bao gồm vật phẩm đã tinh chỉnh và nâng cấp. Dùng {0} để đồng điệu Vũ Khí {1} lên cấp {2} chứ?</t>
         </is>
       </c>
     </row>
@@ -32411,7 +32411,7 @@
       </c>
       <c r="M477" t="inlineStr">
         <is>
-          <t>Includes vật phẩm upgraded. Dùng {0} để đồng điệu Vũ Khí {1} lên cấp {2} chứ?</t>
+          <t>Bao gồm vật phẩm đã nâng cấp. Dùng {0} để đồng điệu Vũ Khí {1} lên cấp {2} chứ?</t>
         </is>
       </c>
     </row>
@@ -32476,7 +32476,7 @@
       </c>
       <c r="M478" t="inlineStr">
         <is>
-          <t>Includes vật phẩm đã đồng điệu. Dùng {0} để đồng điệu Vũ Khí {1} lên cấp {2} chứ?</t>
+          <t>Bao gồm vật phẩm đã đồng điệu. Dùng {0} để đồng điệu Vũ Khí {1} lên cấp {2} chứ?</t>
         </is>
       </c>
     </row>
@@ -32541,7 +32541,7 @@
       </c>
       <c r="M479" t="inlineStr">
         <is>
-          <t>Bạn có muốn tiêu hao {0} để Syntonize vũ khí {1} lên Hạng {2} không?</t>
+          <t>Bạn có muốn tiêu hao {0} để Đồng Điệu vũ khí {1} lên Hạng {2} không?</t>
         </is>
       </c>
     </row>
@@ -32606,7 +32606,7 @@
       </c>
       <c r="M480" t="inlineStr">
         <is>
-          <t>Việc điều chỉnh SOL3 Giai đoạn sẽ ảnh hưởng đến cấp độ kẻ địch và nội dung phần thưởng.</t>
+          <t>Việc điều chỉnh Giai Đoạn SOL3 sẽ ảnh hưởng đến cấp độ kẻ địch và nội dung phần thưởng.</t>
         </is>
       </c>
     </row>
@@ -32736,7 +32736,7 @@
       </c>
       <c r="M482" t="inlineStr">
         <is>
-          <t>Đã đạt Cấp Resonance tối đa</t>
+          <t>Đã đạt Cấp Độ Cộng Hưởng tối đa</t>
         </is>
       </c>
     </row>
@@ -33516,7 +33516,7 @@
       </c>
       <c r="M494" t="inlineStr">
         <is>
-          <t>Chưa trang bị Kỹ năng ảo ảnh</t>
+          <t>Không trang bị kỹ năng ảo ảnh</t>
         </is>
       </c>
     </row>
@@ -33909,10 +33909,10 @@
       </c>
       <c r="M500" t="inlineStr">
         <is>
-          <t>Mỗi &lt;color=HighlightB&gt;10 Cấp Liên Minh&lt;/color&gt; sẽ tăng &lt;color=HighlightB&gt;SOL3 Giai đoạn&lt;/color&gt; của bạn lên 1.
-SOL3 Giai đoạn càng cao mang lại phần thưởng tốt hơn, nhưng cũng đối mặt với kẻ địch khó khăn hơn.
-Ở Cấp Liên Minh &lt;color=HighlightB&gt;20, 40 và 60&lt;/color&gt;, bạn phải hoàn thành &lt;color=HighlightB&gt;Nhiệm Vụ Thăng Tiến Pha SOL3&lt;/color&gt; để tiếp tục tăng Cấp Liên Minh và/hoặc SOL3 Giai đoạn.
-Bạn có thể hạ thấp hoặc tăng lại SOL3 Giai đoạn &lt;color=HighlightB&gt;mỗi 12 giờ&lt;/color&gt;.</t>
+          <t>Mỗi &lt;color=HighlightB&gt;10 Cấp Liên Minh&lt;/color&gt; sẽ tăng &lt;color=HighlightB&gt;Giai Đoạn SOL3&lt;/color&gt; của bạn lên 1.
+Giai Đoạn SOL3 càng cao mang lại phần thưởng tốt hơn, nhưng cũng đối mặt với kẻ địch khó khăn hơn.
+Ở Cấp Liên Minh &lt;color=HighlightB&gt;20, 40 và 60&lt;/color&gt;, bạn phải hoàn thành &lt;color=HighlightB&gt;Nhiệm Vụ Thăng Hoa Giai Đoạn SOL3&lt;/color&gt; để tiếp tục tăng Cấp Liên Minh và/hoặc Giai Đoạn SOL3.
+Bạn có thể hạ thấp hoặc tăng lại Giai Đoạn SOL3 &lt;color=HighlightB&gt;mỗi 12 giờ&lt;/color&gt;.</t>
         </is>
       </c>
     </row>
